--- a/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
+++ b/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LinWenTao\Desktop\Outbound_station\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FC631E-3CCE-43DC-B341-715FAEE31541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9297DE00-C584-43EE-BB95-56F319724729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="版本" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="750">
   <si>
     <t>版本</t>
   </si>
@@ -2951,6 +2951,10 @@
   </si>
   <si>
     <t>放货时候需要告诉出库工作站上位机ABR在哪一个工作站前，工作站编号为ABC</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>station_status</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -3517,17 +3521,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3541,56 +3560,38 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3608,10 +3609,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3626,37 +3639,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3693,21 +3678,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4255,50 +4259,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
     </row>
     <row r="2" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="95" t="s">
+      <c r="A3" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:8" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="95" t="s">
+      <c r="A4" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="96"/>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
       <c r="G4" s="21" t="s">
         <v>713</v>
       </c>
@@ -4307,14 +4311,14 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="95" t="s">
+      <c r="A5" s="108" t="s">
         <v>409</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
       <c r="G5" s="21" t="s">
         <v>712</v>
       </c>
@@ -4323,13 +4327,13 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="49" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="108" t="s">
         <v>714</v>
       </c>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
@@ -4345,26 +4349,26 @@
       <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="97" t="s">
+      <c r="A8" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="20"/>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="100"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="105"/>
       <c r="G9" s="22"/>
       <c r="H9" s="20"/>
     </row>
@@ -4379,10 +4383,10 @@
       <c r="D10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="99" t="s">
+      <c r="E10" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="100"/>
+      <c r="F10" s="105"/>
       <c r="G10" s="22"/>
       <c r="H10" s="20"/>
     </row>
@@ -4397,10 +4401,10 @@
       <c r="D11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="101" t="s">
+      <c r="E11" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="102"/>
+      <c r="F11" s="101"/>
       <c r="G11" s="22"/>
       <c r="H11" s="20"/>
     </row>
@@ -4415,10 +4419,10 @@
       <c r="D12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="102"/>
+      <c r="F12" s="101"/>
       <c r="G12" s="22"/>
       <c r="H12" s="20"/>
     </row>
@@ -4431,10 +4435,10 @@
       <c r="D13" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="101" t="s">
+      <c r="E13" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="102"/>
+      <c r="F13" s="101"/>
       <c r="G13" s="22"/>
       <c r="H13" s="20"/>
     </row>
@@ -4447,10 +4451,10 @@
       <c r="D14" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="104" t="s">
+      <c r="E14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="102"/>
+      <c r="F14" s="101"/>
       <c r="G14" s="22"/>
       <c r="H14" s="20"/>
     </row>
@@ -4463,10 +4467,10 @@
       <c r="D15" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="104" t="s">
+      <c r="E15" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="102"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="22"/>
       <c r="H15" s="20"/>
     </row>
@@ -4479,10 +4483,10 @@
       <c r="D16" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="104" t="s">
+      <c r="E16" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="102"/>
+      <c r="F16" s="101"/>
       <c r="G16" s="22"/>
       <c r="H16" s="20"/>
     </row>
@@ -4497,15 +4501,15 @@
       <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="102" t="s">
         <v>418</v>
       </c>
-      <c r="B18" s="105"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="105"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="102"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -4529,11 +4533,11 @@
       <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="103"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="29"/>
@@ -4609,11 +4613,11 @@
       <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="103"/>
-      <c r="B29" s="103"/>
-      <c r="C29" s="103"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="103"/>
+      <c r="A29" s="98"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
@@ -4729,17 +4733,29 @@
       <c r="H40" s="20"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="96"/>
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="96"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="99"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="99"/>
+      <c r="E41" s="99"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="99"/>
+      <c r="H41" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="E14:F14"/>
@@ -4747,18 +4763,6 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4776,13 +4780,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="114" t="s">
         <v>674</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -4791,11 +4795,11 @@
       <c r="B2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="96" t="s">
+      <c r="C2" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
@@ -4804,11 +4808,11 @@
       <c r="B3" s="19">
         <v>11000</v>
       </c>
-      <c r="C3" s="108" t="s">
+      <c r="C3" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
@@ -4817,11 +4821,11 @@
       <c r="B4" s="19">
         <v>11001</v>
       </c>
-      <c r="C4" s="108" t="s">
+      <c r="C4" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
@@ -4830,11 +4834,11 @@
       <c r="B5" s="19">
         <v>11002</v>
       </c>
-      <c r="C5" s="108" t="s">
+      <c r="C5" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
@@ -4843,11 +4847,11 @@
       <c r="B6" s="19">
         <v>11003</v>
       </c>
-      <c r="C6" s="112" t="s">
+      <c r="C6" s="110" t="s">
         <v>666</v>
       </c>
-      <c r="D6" s="113"/>
-      <c r="E6" s="113"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
@@ -4856,11 +4860,11 @@
       <c r="B7" s="19">
         <v>11004</v>
       </c>
-      <c r="C7" s="108" t="s">
+      <c r="C7" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
@@ -4869,11 +4873,11 @@
       <c r="B8" s="19">
         <v>11005</v>
       </c>
-      <c r="C8" s="108" t="s">
+      <c r="C8" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
@@ -4882,11 +4886,11 @@
       <c r="B9" s="19">
         <v>11006</v>
       </c>
-      <c r="C9" s="108" t="s">
+      <c r="C9" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
@@ -4895,27 +4899,27 @@
       <c r="B10" s="19">
         <v>11007</v>
       </c>
-      <c r="C10" s="112" t="s">
+      <c r="C10" s="110" t="s">
         <v>667</v>
       </c>
-      <c r="D10" s="113"/>
-      <c r="E10" s="113"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="19"/>
       <c r="B11" s="19"/>
-      <c r="C11" s="109"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="110" t="s">
+      <c r="A14" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="110"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="110"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -4925,11 +4929,11 @@
         <f t="shared" ref="B15:B16" si="0">A15+10000</f>
         <v>11100</v>
       </c>
-      <c r="C15" s="111" t="s">
+      <c r="C15" s="117" t="s">
         <v>668</v>
       </c>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
     </row>
     <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -4939,20 +4943,20 @@
         <f t="shared" si="0"/>
         <v>11101</v>
       </c>
-      <c r="C16" s="111" t="s">
+      <c r="C16" s="117" t="s">
         <v>669</v>
       </c>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="114" t="s">
         <v>675</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
@@ -4961,11 +4965,11 @@
       <c r="B20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="96" t="s">
+      <c r="C20" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
@@ -4974,11 +4978,11 @@
       <c r="B21" s="19">
         <v>12000</v>
       </c>
-      <c r="C21" s="108" t="s">
+      <c r="C21" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="108"/>
-      <c r="E21" s="108"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
     </row>
     <row r="22" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
@@ -4987,41 +4991,41 @@
       <c r="B22" s="19">
         <v>12001</v>
       </c>
-      <c r="C22" s="108" t="s">
+      <c r="C22" s="113" t="s">
         <v>673</v>
       </c>
-      <c r="D22" s="108"/>
-      <c r="E22" s="108"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
       <c r="B23" s="19"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
       <c r="B24" s="19"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
       <c r="B25" s="19"/>
-      <c r="C25" s="109"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="114" t="s">
         <v>689</v>
       </c>
-      <c r="B26" s="107"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
-      <c r="E26" s="107"/>
+      <c r="B26" s="115"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="115"/>
+      <c r="E26" s="115"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
@@ -5030,11 +5034,11 @@
       <c r="B27" s="19">
         <v>13000</v>
       </c>
-      <c r="C27" s="112" t="s">
+      <c r="C27" s="110" t="s">
         <v>692</v>
       </c>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="19">
@@ -5043,11 +5047,11 @@
       <c r="B28" s="19">
         <v>13001</v>
       </c>
-      <c r="C28" s="112" t="s">
+      <c r="C28" s="110" t="s">
         <v>693</v>
       </c>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19">
@@ -5056,11 +5060,11 @@
       <c r="B29" s="19">
         <v>13002</v>
       </c>
-      <c r="C29" s="112" t="s">
+      <c r="C29" s="110" t="s">
         <v>694</v>
       </c>
-      <c r="D29" s="109"/>
-      <c r="E29" s="109"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="19">
@@ -5069,11 +5073,11 @@
       <c r="B30" s="19">
         <v>13003</v>
       </c>
-      <c r="C30" s="112" t="s">
+      <c r="C30" s="110" t="s">
         <v>695</v>
       </c>
-      <c r="D30" s="112"/>
-      <c r="E30" s="112"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19">
@@ -5082,11 +5086,11 @@
       <c r="B31" s="19">
         <v>13004</v>
       </c>
-      <c r="C31" s="112" t="s">
+      <c r="C31" s="110" t="s">
         <v>701</v>
       </c>
-      <c r="D31" s="112"/>
-      <c r="E31" s="112"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
@@ -5095,11 +5099,11 @@
       <c r="B32" s="19">
         <v>13005</v>
       </c>
-      <c r="C32" s="112" t="s">
+      <c r="C32" s="110" t="s">
         <v>703</v>
       </c>
-      <c r="D32" s="112"/>
-      <c r="E32" s="112"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19">
@@ -5108,11 +5112,11 @@
       <c r="B33" s="19">
         <v>13006</v>
       </c>
-      <c r="C33" s="112" t="s">
+      <c r="C33" s="110" t="s">
         <v>705</v>
       </c>
-      <c r="D33" s="112"/>
-      <c r="E33" s="112"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="110"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="19">
@@ -5121,11 +5125,11 @@
       <c r="B34" s="19">
         <v>13007</v>
       </c>
-      <c r="C34" s="112" t="s">
+      <c r="C34" s="110" t="s">
         <v>706</v>
       </c>
-      <c r="D34" s="112"/>
-      <c r="E34" s="112"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
@@ -5134,11 +5138,11 @@
       <c r="B35" s="19">
         <v>13008</v>
       </c>
-      <c r="C35" s="112" t="s">
+      <c r="C35" s="110" t="s">
         <v>708</v>
       </c>
-      <c r="D35" s="112"/>
-      <c r="E35" s="112"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
@@ -5147,11 +5151,11 @@
       <c r="B36" s="19">
         <v>13009</v>
       </c>
-      <c r="C36" s="112" t="s">
+      <c r="C36" s="110" t="s">
         <v>711</v>
       </c>
-      <c r="D36" s="112"/>
-      <c r="E36" s="112"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="110"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
@@ -5160,9 +5164,9 @@
       <c r="B37" s="19">
         <v>13010</v>
       </c>
-      <c r="C37" s="109"/>
-      <c r="D37" s="109"/>
-      <c r="E37" s="109"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="111"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
@@ -5171,9 +5175,9 @@
       <c r="B38" s="19">
         <v>13011</v>
       </c>
-      <c r="C38" s="109"/>
-      <c r="D38" s="109"/>
-      <c r="E38" s="109"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
     </row>
     <row r="39" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
@@ -5204,13 +5208,13 @@
       <c r="E42" s="81"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="106" t="s">
+      <c r="A43" s="114" t="s">
         <v>690</v>
       </c>
-      <c r="B43" s="107"/>
-      <c r="C43" s="107"/>
-      <c r="D43" s="107"/>
-      <c r="E43" s="107"/>
+      <c r="B43" s="115"/>
+      <c r="C43" s="115"/>
+      <c r="D43" s="115"/>
+      <c r="E43" s="115"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="18" t="s">
@@ -5219,11 +5223,11 @@
       <c r="B44" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="96" t="s">
+      <c r="C44" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="96"/>
-      <c r="E44" s="96"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="19">
@@ -5232,11 +5236,11 @@
       <c r="B45" s="19">
         <v>14000</v>
       </c>
-      <c r="C45" s="109" t="s">
+      <c r="C45" s="111" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="109"/>
-      <c r="E45" s="109"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="111"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="19">
@@ -5245,11 +5249,11 @@
       <c r="B46" s="19">
         <v>14001</v>
       </c>
-      <c r="C46" s="112" t="s">
+      <c r="C46" s="110" t="s">
         <v>691</v>
       </c>
-      <c r="D46" s="109"/>
-      <c r="E46" s="109"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="111"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="19"/>
@@ -5273,6 +5277,30 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="C46:E46"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C28:E28"/>
@@ -5286,31 +5314,7 @@
     <mergeCell ref="C36:E36"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5331,16 +5335,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -5497,16 +5501,16 @@
     </row>
     <row r="11" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="105" t="s">
+      <c r="A13" s="102" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -5594,13 +5598,13 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="114" t="s">
+      <c r="A19" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="114"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
@@ -5671,13 +5675,13 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="115" t="s">
+      <c r="A26" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="115"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="115"/>
-      <c r="E26" s="115"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="120"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -5825,16 +5829,16 @@
       <c r="E36" s="17"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="96" t="s">
+      <c r="A37" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="96"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="96"/>
-      <c r="G37" s="96"/>
-      <c r="H37" s="96"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -5901,16 +5905,16 @@
       </c>
     </row>
     <row r="48" spans="1:8" s="82" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="111" t="s">
+      <c r="A48" s="117" t="s">
         <v>660</v>
       </c>
-      <c r="B48" s="96"/>
-      <c r="C48" s="96"/>
-      <c r="D48" s="96"/>
-      <c r="E48" s="96"/>
-      <c r="F48" s="96"/>
-      <c r="G48" s="96"/>
-      <c r="H48" s="96"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
     </row>
     <row r="49" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
@@ -5998,8 +6002,8 @@
       </c>
     </row>
     <row r="54" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="61" t="s">
-        <v>626</v>
+      <c r="A54" s="85" t="s">
+        <v>749</v>
       </c>
       <c r="B54" s="61" t="s">
         <v>615</v>
@@ -6015,13 +6019,13 @@
       </c>
     </row>
     <row r="55" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="114" t="s">
+      <c r="A55" s="118" t="s">
         <v>665</v>
       </c>
-      <c r="B55" s="114"/>
-      <c r="C55" s="114"/>
-      <c r="D55" s="114"/>
-      <c r="E55" s="114"/>
+      <c r="B55" s="118"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
     </row>
     <row r="56" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
@@ -6041,8 +6045,8 @@
       </c>
     </row>
     <row r="57" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="61" t="s">
-        <v>617</v>
+      <c r="A57" s="85" t="s">
+        <v>747</v>
       </c>
       <c r="B57" s="61" t="s">
         <v>616</v>
@@ -6298,16 +6302,16 @@
     <row r="72" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="111" t="s">
+      <c r="A74" s="117" t="s">
         <v>661</v>
       </c>
-      <c r="B74" s="96"/>
-      <c r="C74" s="96"/>
-      <c r="D74" s="96"/>
-      <c r="E74" s="96"/>
-      <c r="F74" s="96"/>
-      <c r="G74" s="96"/>
-      <c r="H74" s="96"/>
+      <c r="B74" s="99"/>
+      <c r="C74" s="99"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="99"/>
+      <c r="G74" s="99"/>
+      <c r="H74" s="99"/>
     </row>
     <row r="75" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
@@ -6464,16 +6468,16 @@
     </row>
     <row r="84" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="86" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="111" t="s">
+      <c r="A86" s="117" t="s">
         <v>662</v>
       </c>
-      <c r="B86" s="96"/>
-      <c r="C86" s="96"/>
-      <c r="D86" s="96"/>
-      <c r="E86" s="96"/>
-      <c r="F86" s="96"/>
-      <c r="G86" s="96"/>
-      <c r="H86" s="96"/>
+      <c r="B86" s="99"/>
+      <c r="C86" s="99"/>
+      <c r="D86" s="99"/>
+      <c r="E86" s="99"/>
+      <c r="F86" s="99"/>
+      <c r="G86" s="99"/>
+      <c r="H86" s="99"/>
     </row>
     <row r="87" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
@@ -6561,13 +6565,13 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A92" s="114" t="s">
+      <c r="A92" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="B92" s="114"/>
-      <c r="C92" s="114"/>
-      <c r="D92" s="114"/>
-      <c r="E92" s="114"/>
+      <c r="B92" s="118"/>
+      <c r="C92" s="118"/>
+      <c r="D92" s="118"/>
+      <c r="E92" s="118"/>
     </row>
     <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
@@ -6638,13 +6642,13 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="116" t="s">
+      <c r="A99" s="119" t="s">
         <v>663</v>
       </c>
-      <c r="B99" s="115"/>
-      <c r="C99" s="115"/>
-      <c r="D99" s="115"/>
-      <c r="E99" s="115"/>
+      <c r="B99" s="120"/>
+      <c r="C99" s="120"/>
+      <c r="D99" s="120"/>
+      <c r="E99" s="120"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -6866,16 +6870,16 @@
       </c>
     </row>
     <row r="120" spans="1:8" s="82" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="111" t="s">
+      <c r="A120" s="117" t="s">
         <v>664</v>
       </c>
-      <c r="B120" s="96"/>
-      <c r="C120" s="96"/>
-      <c r="D120" s="96"/>
-      <c r="E120" s="96"/>
-      <c r="F120" s="96"/>
-      <c r="G120" s="96"/>
-      <c r="H120" s="96"/>
+      <c r="B120" s="99"/>
+      <c r="C120" s="99"/>
+      <c r="D120" s="99"/>
+      <c r="E120" s="99"/>
+      <c r="F120" s="99"/>
+      <c r="G120" s="99"/>
+      <c r="H120" s="99"/>
     </row>
     <row r="121" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
@@ -6980,13 +6984,13 @@
       </c>
     </row>
     <row r="127" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A127" s="114" t="s">
+      <c r="A127" s="118" t="s">
         <v>665</v>
       </c>
-      <c r="B127" s="114"/>
-      <c r="C127" s="114"/>
-      <c r="D127" s="114"/>
-      <c r="E127" s="114"/>
+      <c r="B127" s="118"/>
+      <c r="C127" s="118"/>
+      <c r="D127" s="118"/>
+      <c r="E127" s="118"/>
     </row>
     <row r="128" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
@@ -7263,16 +7267,16 @@
     <row r="144" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="145" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="146" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="111" t="s">
+      <c r="A146" s="117" t="s">
         <v>584</v>
       </c>
-      <c r="B146" s="96"/>
-      <c r="C146" s="96"/>
-      <c r="D146" s="96"/>
-      <c r="E146" s="96"/>
-      <c r="F146" s="96"/>
-      <c r="G146" s="96"/>
-      <c r="H146" s="96"/>
+      <c r="B146" s="99"/>
+      <c r="C146" s="99"/>
+      <c r="D146" s="99"/>
+      <c r="E146" s="99"/>
+      <c r="F146" s="99"/>
+      <c r="G146" s="99"/>
+      <c r="H146" s="99"/>
     </row>
     <row r="147" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
@@ -7564,13 +7568,13 @@
       </c>
     </row>
     <row r="164" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A164" s="114" t="s">
+      <c r="A164" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="B164" s="114"/>
-      <c r="C164" s="114"/>
-      <c r="D164" s="114"/>
-      <c r="E164" s="114"/>
+      <c r="B164" s="118"/>
+      <c r="C164" s="118"/>
+      <c r="D164" s="118"/>
+      <c r="E164" s="118"/>
     </row>
     <row r="165" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A165" s="6" t="s">
@@ -7658,13 +7662,13 @@
       </c>
     </row>
     <row r="170" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A170" s="114" t="s">
+      <c r="A170" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="B170" s="114"/>
-      <c r="C170" s="114"/>
-      <c r="D170" s="114"/>
-      <c r="E170" s="114"/>
+      <c r="B170" s="118"/>
+      <c r="C170" s="118"/>
+      <c r="D170" s="118"/>
+      <c r="E170" s="118"/>
     </row>
     <row r="171" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A171" s="6" t="s">
@@ -7752,13 +7756,13 @@
       </c>
     </row>
     <row r="176" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A176" s="114" t="s">
+      <c r="A176" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="B176" s="114"/>
-      <c r="C176" s="114"/>
-      <c r="D176" s="114"/>
-      <c r="E176" s="114"/>
+      <c r="B176" s="118"/>
+      <c r="C176" s="118"/>
+      <c r="D176" s="118"/>
+      <c r="E176" s="118"/>
     </row>
     <row r="177" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A177" s="6" t="s">
@@ -7832,13 +7836,13 @@
       </c>
     </row>
     <row r="181" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A181" s="114" t="s">
+      <c r="A181" s="118" t="s">
         <v>665</v>
       </c>
-      <c r="B181" s="114"/>
-      <c r="C181" s="114"/>
-      <c r="D181" s="114"/>
-      <c r="E181" s="114"/>
+      <c r="B181" s="118"/>
+      <c r="C181" s="118"/>
+      <c r="D181" s="118"/>
+      <c r="E181" s="118"/>
     </row>
     <row r="182" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A182" s="6" t="s">
@@ -8161,13 +8165,13 @@
       <c r="E201" s="91"/>
     </row>
     <row r="202" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="116" t="s">
+      <c r="A202" s="119" t="s">
         <v>585</v>
       </c>
-      <c r="B202" s="116"/>
-      <c r="C202" s="116"/>
-      <c r="D202" s="116"/>
-      <c r="E202" s="116"/>
+      <c r="B202" s="119"/>
+      <c r="C202" s="119"/>
+      <c r="D202" s="119"/>
+      <c r="E202" s="119"/>
     </row>
     <row r="203" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
@@ -8422,13 +8426,13 @@
       <c r="E218" s="43"/>
     </row>
     <row r="219" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A219" s="114" t="s">
+      <c r="A219" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="B219" s="114"/>
-      <c r="C219" s="114"/>
-      <c r="D219" s="114"/>
-      <c r="E219" s="114"/>
+      <c r="B219" s="118"/>
+      <c r="C219" s="118"/>
+      <c r="D219" s="118"/>
+      <c r="E219" s="118"/>
     </row>
     <row r="220" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A220" s="6" t="s">
@@ -8516,13 +8520,13 @@
       </c>
     </row>
     <row r="225" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A225" s="114" t="s">
+      <c r="A225" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="B225" s="114"/>
-      <c r="C225" s="114"/>
-      <c r="D225" s="114"/>
-      <c r="E225" s="114"/>
+      <c r="B225" s="118"/>
+      <c r="C225" s="118"/>
+      <c r="D225" s="118"/>
+      <c r="E225" s="118"/>
     </row>
     <row r="226" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A226" s="6" t="s">
@@ -8610,13 +8614,13 @@
       </c>
     </row>
     <row r="231" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A231" s="114" t="s">
+      <c r="A231" s="118" t="s">
         <v>70</v>
       </c>
-      <c r="B231" s="114"/>
-      <c r="C231" s="114"/>
-      <c r="D231" s="114"/>
-      <c r="E231" s="114"/>
+      <c r="B231" s="118"/>
+      <c r="C231" s="118"/>
+      <c r="D231" s="118"/>
+      <c r="E231" s="118"/>
     </row>
     <row r="232" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A232" s="6" t="s">
@@ -8687,13 +8691,13 @@
       </c>
     </row>
     <row r="236" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A236" s="114" t="s">
+      <c r="A236" s="118" t="s">
         <v>665</v>
       </c>
-      <c r="B236" s="114"/>
-      <c r="C236" s="114"/>
-      <c r="D236" s="114"/>
-      <c r="E236" s="114"/>
+      <c r="B236" s="118"/>
+      <c r="C236" s="118"/>
+      <c r="D236" s="118"/>
+      <c r="E236" s="118"/>
     </row>
     <row r="237" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A237" s="6" t="s">
@@ -9003,6 +9007,18 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A236:E236"/>
+    <mergeCell ref="A231:E231"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A225:E225"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A120:H120"/>
@@ -9014,18 +9030,6 @@
     <mergeCell ref="A86:H86"/>
     <mergeCell ref="A92:E92"/>
     <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A236:E236"/>
-    <mergeCell ref="A231:E231"/>
-    <mergeCell ref="A170:E170"/>
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="A202:E202"/>
-    <mergeCell ref="A219:E219"/>
-    <mergeCell ref="A225:E225"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9046,16 +9050,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="102" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -9146,19 +9150,19 @@
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" s="93" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="94" t="s">
         <v>747</v>
       </c>
-      <c r="B6" s="161" t="s">
+      <c r="B6" s="94" t="s">
         <v>616</v>
       </c>
-      <c r="C6" s="162" t="s">
+      <c r="C6" s="95" t="s">
         <v>228</v>
       </c>
-      <c r="D6" s="163" t="s">
+      <c r="D6" s="96" t="s">
         <v>243</v>
       </c>
-      <c r="E6" s="164" t="s">
+      <c r="E6" s="97" t="s">
         <v>748</v>
       </c>
       <c r="H6" s="4"/>
@@ -9234,13 +9238,13 @@
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="114" t="s">
+      <c r="A10" s="118" t="s">
         <v>172</v>
       </c>
-      <c r="B10" s="114"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -9285,14 +9289,14 @@
       <c r="E12" s="78" t="s">
         <v>290</v>
       </c>
-      <c r="F12" s="118" t="s">
+      <c r="F12" s="127" t="s">
         <v>206</v>
       </c>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="118"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9311,16 +9315,16 @@
       <c r="E13" s="78" t="s">
         <v>293</v>
       </c>
-      <c r="F13" s="125" t="s">
+      <c r="F13" s="124" t="s">
         <v>566</v>
       </c>
-      <c r="G13" s="126"/>
-      <c r="H13" s="126"/>
-      <c r="I13" s="117" t="s">
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="126" t="s">
         <v>571</v>
       </c>
-      <c r="J13" s="117"/>
-      <c r="K13" s="117"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
       <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9339,12 +9343,12 @@
       <c r="E14" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="117"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9363,12 +9367,12 @@
       <c r="E15" s="79" t="s">
         <v>299</v>
       </c>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="K15" s="117"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9387,12 +9391,12 @@
       <c r="E16" s="78" t="s">
         <v>211</v>
       </c>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="126"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9411,12 +9415,12 @@
       <c r="E17" s="78" t="s">
         <v>210</v>
       </c>
-      <c r="F17" s="126"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="126"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="K17" s="117"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9435,12 +9439,12 @@
       <c r="E18" s="78" t="s">
         <v>306</v>
       </c>
-      <c r="F18" s="126"/>
-      <c r="G18" s="126"/>
-      <c r="H18" s="126"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="K18" s="117"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" s="73" customFormat="1" ht="33" x14ac:dyDescent="0.2">
@@ -9459,22 +9463,22 @@
       <c r="E19" s="79" t="s">
         <v>560</v>
       </c>
-      <c r="F19" s="126"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="126"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="117"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="122" t="s">
+      <c r="A20" s="121" t="s">
         <v>567</v>
       </c>
-      <c r="B20" s="123"/>
-      <c r="C20" s="123"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="124"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="123"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
@@ -9545,13 +9549,13 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="122" t="s">
+      <c r="A25" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="B25" s="123"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="124"/>
+      <c r="B25" s="122"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="123"/>
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
       <c r="H25" s="41"/>
@@ -9610,13 +9614,13 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="122" t="s">
+      <c r="A30" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="123"/>
-      <c r="C30" s="123"/>
-      <c r="D30" s="123"/>
-      <c r="E30" s="124"/>
+      <c r="B30" s="122"/>
+      <c r="C30" s="122"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="123"/>
     </row>
     <row r="31" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
@@ -9687,16 +9691,16 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="119" t="s">
+      <c r="A37" s="128" t="s">
         <v>218</v>
       </c>
-      <c r="B37" s="120"/>
-      <c r="C37" s="120"/>
-      <c r="D37" s="120"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="121"/>
+      <c r="B37" s="129"/>
+      <c r="C37" s="129"/>
+      <c r="D37" s="129"/>
+      <c r="E37" s="129"/>
+      <c r="F37" s="129"/>
+      <c r="G37" s="129"/>
+      <c r="H37" s="130"/>
     </row>
     <row r="38" spans="1:8" ht="49.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -10064,13 +10068,13 @@
     </row>
     <row r="53" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="111" t="s">
+      <c r="A54" s="117" t="s">
         <v>435</v>
       </c>
-      <c r="B54" s="96"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="96"/>
-      <c r="E54" s="96"/>
+      <c r="B54" s="99"/>
+      <c r="C54" s="99"/>
+      <c r="D54" s="99"/>
+      <c r="E54" s="99"/>
     </row>
     <row r="55" spans="1:8" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A55" s="59" t="s">
@@ -10143,13 +10147,13 @@
     <row r="59" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="61" spans="1:8" s="82" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="111" t="s">
+      <c r="A61" s="117" t="s">
         <v>670</v>
       </c>
-      <c r="B61" s="96"/>
-      <c r="C61" s="96"/>
-      <c r="D61" s="96"/>
-      <c r="E61" s="96"/>
+      <c r="B61" s="99"/>
+      <c r="C61" s="99"/>
+      <c r="D61" s="99"/>
+      <c r="E61" s="99"/>
     </row>
     <row r="62" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="59" t="s">
@@ -10205,13 +10209,13 @@
     <row r="65" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="67" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="111" t="s">
+      <c r="A67" s="117" t="s">
         <v>436</v>
       </c>
-      <c r="B67" s="96"/>
-      <c r="C67" s="96"/>
-      <c r="D67" s="96"/>
-      <c r="E67" s="96"/>
+      <c r="B67" s="99"/>
+      <c r="C67" s="99"/>
+      <c r="D67" s="99"/>
+      <c r="E67" s="99"/>
     </row>
     <row r="68" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A68" s="59" t="s">
@@ -10289,9 +10293,9 @@
       <c r="C74" s="82"/>
       <c r="D74" s="82"/>
       <c r="E74" s="82"/>
-      <c r="F74" s="105"/>
-      <c r="G74" s="96"/>
-      <c r="H74" s="96"/>
+      <c r="F74" s="102"/>
+      <c r="G74" s="99"/>
+      <c r="H74" s="99"/>
     </row>
     <row r="75" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="82"/>
@@ -10421,12 +10425,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F13:H19"/>
     <mergeCell ref="I13:K19"/>
     <mergeCell ref="F12:K12"/>
     <mergeCell ref="F74:H74"/>
@@ -10434,6 +10432,12 @@
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F13:H19"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10453,13 +10457,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="119" t="s">
         <v>696</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -10598,13 +10602,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="127" t="s">
+      <c r="A10" s="131" t="s">
         <v>267</v>
       </c>
-      <c r="B10" s="114"/>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
     </row>
     <row r="11" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
@@ -10675,13 +10679,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="131" t="s">
         <v>269</v>
       </c>
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
     </row>
     <row r="16" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -10744,13 +10748,13 @@
       <c r="E19" s="42"/>
     </row>
     <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="127" t="s">
+      <c r="A20" s="131" t="s">
         <v>268</v>
       </c>
-      <c r="B20" s="114"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="114"/>
-      <c r="E20" s="114"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
     </row>
     <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
@@ -10821,13 +10825,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="127" t="s">
+      <c r="A25" s="131" t="s">
         <v>254</v>
       </c>
-      <c r="B25" s="114"/>
-      <c r="C25" s="114"/>
-      <c r="D25" s="114"/>
-      <c r="E25" s="114"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
     </row>
     <row r="26" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
@@ -10915,13 +10919,13 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="122" t="s">
+      <c r="A31" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="123"/>
-      <c r="C31" s="123"/>
-      <c r="D31" s="123"/>
-      <c r="E31" s="124"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="122"/>
+      <c r="E31" s="123"/>
     </row>
     <row r="32" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
@@ -11023,13 +11027,13 @@
       <c r="E40" s="82"/>
     </row>
     <row r="41" spans="1:5" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="116" t="s">
+      <c r="A41" s="119" t="s">
         <v>697</v>
       </c>
-      <c r="B41" s="115"/>
-      <c r="C41" s="115"/>
-      <c r="D41" s="115"/>
-      <c r="E41" s="115"/>
+      <c r="B41" s="120"/>
+      <c r="C41" s="120"/>
+      <c r="D41" s="120"/>
+      <c r="E41" s="120"/>
     </row>
     <row r="42" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
@@ -11168,13 +11172,13 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="114" t="s">
+      <c r="A50" s="118" t="s">
         <v>683</v>
       </c>
-      <c r="B50" s="114"/>
-      <c r="C50" s="114"/>
-      <c r="D50" s="114"/>
-      <c r="E50" s="114"/>
+      <c r="B50" s="118"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
     </row>
     <row r="51" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -11245,13 +11249,13 @@
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="127" t="s">
+      <c r="A55" s="131" t="s">
         <v>282</v>
       </c>
-      <c r="B55" s="114"/>
-      <c r="C55" s="114"/>
-      <c r="D55" s="114"/>
-      <c r="E55" s="114"/>
+      <c r="B55" s="118"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
     </row>
     <row r="56" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
@@ -11583,13 +11587,13 @@
       <c r="E77" s="82"/>
     </row>
     <row r="78" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A78" s="114" t="s">
+      <c r="A78" s="118" t="s">
         <v>682</v>
       </c>
-      <c r="B78" s="114"/>
-      <c r="C78" s="114"/>
-      <c r="D78" s="114"/>
-      <c r="E78" s="114"/>
+      <c r="B78" s="118"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="118"/>
+      <c r="E78" s="118"/>
     </row>
     <row r="79" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
@@ -11660,13 +11664,13 @@
       </c>
     </row>
     <row r="83" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="127" t="s">
+      <c r="A83" s="131" t="s">
         <v>285</v>
       </c>
-      <c r="B83" s="114"/>
-      <c r="C83" s="114"/>
-      <c r="D83" s="114"/>
-      <c r="E83" s="114"/>
+      <c r="B83" s="118"/>
+      <c r="C83" s="118"/>
+      <c r="D83" s="118"/>
+      <c r="E83" s="118"/>
     </row>
     <row r="84" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
@@ -11870,13 +11874,13 @@
       <c r="E96" s="43"/>
     </row>
     <row r="97" spans="1:5" s="82" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="116" t="s">
+      <c r="A97" s="119" t="s">
         <v>698</v>
       </c>
-      <c r="B97" s="115"/>
-      <c r="C97" s="115"/>
-      <c r="D97" s="115"/>
-      <c r="E97" s="115"/>
+      <c r="B97" s="120"/>
+      <c r="C97" s="120"/>
+      <c r="D97" s="120"/>
+      <c r="E97" s="120"/>
     </row>
     <row r="98" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
@@ -12015,13 +12019,13 @@
       </c>
     </row>
     <row r="106" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A106" s="114" t="s">
+      <c r="A106" s="118" t="s">
         <v>681</v>
       </c>
-      <c r="B106" s="114"/>
-      <c r="C106" s="114"/>
-      <c r="D106" s="114"/>
-      <c r="E106" s="114"/>
+      <c r="B106" s="118"/>
+      <c r="C106" s="118"/>
+      <c r="D106" s="118"/>
+      <c r="E106" s="118"/>
     </row>
     <row r="107" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
@@ -12092,13 +12096,13 @@
       </c>
     </row>
     <row r="111" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A111" s="127" t="s">
+      <c r="A111" s="131" t="s">
         <v>282</v>
       </c>
-      <c r="B111" s="114"/>
-      <c r="C111" s="114"/>
-      <c r="D111" s="114"/>
-      <c r="E111" s="114"/>
+      <c r="B111" s="118"/>
+      <c r="C111" s="118"/>
+      <c r="D111" s="118"/>
+      <c r="E111" s="118"/>
     </row>
     <row r="112" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
@@ -12410,13 +12414,13 @@
       </c>
     </row>
     <row r="134" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A134" s="114" t="s">
+      <c r="A134" s="118" t="s">
         <v>680</v>
       </c>
-      <c r="B134" s="114"/>
-      <c r="C134" s="114"/>
-      <c r="D134" s="114"/>
-      <c r="E134" s="114"/>
+      <c r="B134" s="118"/>
+      <c r="C134" s="118"/>
+      <c r="D134" s="118"/>
+      <c r="E134" s="118"/>
     </row>
     <row r="135" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
@@ -12487,13 +12491,13 @@
       </c>
     </row>
     <row r="139" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A139" s="127" t="s">
+      <c r="A139" s="131" t="s">
         <v>285</v>
       </c>
-      <c r="B139" s="114"/>
-      <c r="C139" s="114"/>
-      <c r="D139" s="114"/>
-      <c r="E139" s="114"/>
+      <c r="B139" s="118"/>
+      <c r="C139" s="118"/>
+      <c r="D139" s="118"/>
+      <c r="E139" s="118"/>
     </row>
     <row r="140" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
@@ -12699,13 +12703,13 @@
     <row r="153" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="154" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="155" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="116" t="s">
+      <c r="A155" s="119" t="s">
         <v>699</v>
       </c>
-      <c r="B155" s="115"/>
-      <c r="C155" s="115"/>
-      <c r="D155" s="115"/>
-      <c r="E155" s="115"/>
+      <c r="B155" s="120"/>
+      <c r="C155" s="120"/>
+      <c r="D155" s="120"/>
+      <c r="E155" s="120"/>
     </row>
     <row r="156" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
@@ -12844,13 +12848,13 @@
       </c>
     </row>
     <row r="164" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A164" s="114" t="s">
+      <c r="A164" s="118" t="s">
         <v>598</v>
       </c>
-      <c r="B164" s="114"/>
-      <c r="C164" s="114"/>
-      <c r="D164" s="114"/>
-      <c r="E164" s="114"/>
+      <c r="B164" s="118"/>
+      <c r="C164" s="118"/>
+      <c r="D164" s="118"/>
+      <c r="E164" s="118"/>
     </row>
     <row r="165" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A165" s="6" t="s">
@@ -12921,13 +12925,13 @@
       </c>
     </row>
     <row r="169" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A169" s="114" t="s">
+      <c r="A169" s="118" t="s">
         <v>597</v>
       </c>
-      <c r="B169" s="114"/>
-      <c r="C169" s="114"/>
-      <c r="D169" s="114"/>
-      <c r="E169" s="114"/>
+      <c r="B169" s="118"/>
+      <c r="C169" s="118"/>
+      <c r="D169" s="118"/>
+      <c r="E169" s="118"/>
     </row>
     <row r="170" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A170" s="6" t="s">
@@ -13016,13 +13020,13 @@
       <c r="D176" s="12"/>
     </row>
     <row r="177" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A177" s="127" t="s">
+      <c r="A177" s="131" t="s">
         <v>354</v>
       </c>
-      <c r="B177" s="114"/>
-      <c r="C177" s="114"/>
-      <c r="D177" s="114"/>
-      <c r="E177" s="114"/>
+      <c r="B177" s="118"/>
+      <c r="C177" s="118"/>
+      <c r="D177" s="118"/>
+      <c r="E177" s="118"/>
     </row>
     <row r="178" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A178" s="6" t="s">
@@ -13093,13 +13097,13 @@
       </c>
     </row>
     <row r="184" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="116" t="s">
+      <c r="A184" s="119" t="s">
         <v>700</v>
       </c>
-      <c r="B184" s="115"/>
-      <c r="C184" s="115"/>
-      <c r="D184" s="115"/>
-      <c r="E184" s="115"/>
+      <c r="B184" s="120"/>
+      <c r="C184" s="120"/>
+      <c r="D184" s="120"/>
+      <c r="E184" s="120"/>
     </row>
     <row r="185" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
@@ -13238,13 +13242,13 @@
       </c>
     </row>
     <row r="193" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A193" s="127" t="s">
+      <c r="A193" s="131" t="s">
         <v>355</v>
       </c>
-      <c r="B193" s="114"/>
-      <c r="C193" s="114"/>
-      <c r="D193" s="114"/>
-      <c r="E193" s="114"/>
+      <c r="B193" s="118"/>
+      <c r="C193" s="118"/>
+      <c r="D193" s="118"/>
+      <c r="E193" s="118"/>
     </row>
     <row r="194" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
@@ -13315,13 +13319,13 @@
       </c>
     </row>
     <row r="198" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A198" s="127" t="s">
+      <c r="A198" s="131" t="s">
         <v>356</v>
       </c>
-      <c r="B198" s="114"/>
-      <c r="C198" s="114"/>
-      <c r="D198" s="114"/>
-      <c r="E198" s="114"/>
+      <c r="B198" s="118"/>
+      <c r="C198" s="118"/>
+      <c r="D198" s="118"/>
+      <c r="E198" s="118"/>
     </row>
     <row r="199" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
@@ -13392,13 +13396,13 @@
       </c>
     </row>
     <row r="203" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A203" s="127" t="s">
+      <c r="A203" s="131" t="s">
         <v>359</v>
       </c>
-      <c r="B203" s="114"/>
-      <c r="C203" s="114"/>
-      <c r="D203" s="114"/>
-      <c r="E203" s="114"/>
+      <c r="B203" s="118"/>
+      <c r="C203" s="118"/>
+      <c r="D203" s="118"/>
+      <c r="E203" s="118"/>
     </row>
     <row r="204" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A204" s="6" t="s">
@@ -13475,13 +13479,13 @@
       <c r="E209" s="82"/>
     </row>
     <row r="210" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="116" t="s">
+      <c r="A210" s="119" t="s">
         <v>702</v>
       </c>
-      <c r="B210" s="115"/>
-      <c r="C210" s="115"/>
-      <c r="D210" s="115"/>
-      <c r="E210" s="115"/>
+      <c r="B210" s="120"/>
+      <c r="C210" s="120"/>
+      <c r="D210" s="120"/>
+      <c r="E210" s="120"/>
     </row>
     <row r="211" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
@@ -13620,13 +13624,13 @@
       </c>
     </row>
     <row r="219" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A219" s="127" t="s">
+      <c r="A219" s="131" t="s">
         <v>394</v>
       </c>
-      <c r="B219" s="114"/>
-      <c r="C219" s="114"/>
-      <c r="D219" s="114"/>
-      <c r="E219" s="114"/>
+      <c r="B219" s="118"/>
+      <c r="C219" s="118"/>
+      <c r="D219" s="118"/>
+      <c r="E219" s="118"/>
     </row>
     <row r="220" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A220" s="6" t="s">
@@ -13697,13 +13701,13 @@
       </c>
     </row>
     <row r="224" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A224" s="127" t="s">
+      <c r="A224" s="131" t="s">
         <v>395</v>
       </c>
-      <c r="B224" s="114"/>
-      <c r="C224" s="114"/>
-      <c r="D224" s="114"/>
-      <c r="E224" s="114"/>
+      <c r="B224" s="118"/>
+      <c r="C224" s="118"/>
+      <c r="D224" s="118"/>
+      <c r="E224" s="118"/>
     </row>
     <row r="225" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A225" s="6" t="s">
@@ -13780,13 +13784,13 @@
       <c r="E230" s="82"/>
     </row>
     <row r="231" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A231" s="127" t="s">
+      <c r="A231" s="131" t="s">
         <v>393</v>
       </c>
-      <c r="B231" s="114"/>
-      <c r="C231" s="114"/>
-      <c r="D231" s="114"/>
-      <c r="E231" s="114"/>
+      <c r="B231" s="118"/>
+      <c r="C231" s="118"/>
+      <c r="D231" s="118"/>
+      <c r="E231" s="118"/>
     </row>
     <row r="232" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A232" s="6" t="s">
@@ -13871,83 +13875,83 @@
       <c r="E237" s="82"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A238" s="131" t="s">
+      <c r="A238" s="134" t="s">
         <v>281</v>
       </c>
-      <c r="B238" s="132"/>
-      <c r="C238" s="132"/>
-      <c r="D238" s="132"/>
-      <c r="E238" s="132"/>
+      <c r="B238" s="135"/>
+      <c r="C238" s="135"/>
+      <c r="D238" s="135"/>
+      <c r="E238" s="135"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A239" s="132"/>
-      <c r="B239" s="132"/>
-      <c r="C239" s="132"/>
-      <c r="D239" s="132"/>
-      <c r="E239" s="132"/>
+      <c r="A239" s="135"/>
+      <c r="B239" s="135"/>
+      <c r="C239" s="135"/>
+      <c r="D239" s="135"/>
+      <c r="E239" s="135"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A240" s="132"/>
-      <c r="B240" s="132"/>
-      <c r="C240" s="132"/>
-      <c r="D240" s="132"/>
-      <c r="E240" s="132"/>
+      <c r="A240" s="135"/>
+      <c r="B240" s="135"/>
+      <c r="C240" s="135"/>
+      <c r="D240" s="135"/>
+      <c r="E240" s="135"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A241" s="132"/>
-      <c r="B241" s="132"/>
-      <c r="C241" s="132"/>
-      <c r="D241" s="132"/>
-      <c r="E241" s="132"/>
+      <c r="A241" s="135"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="135"/>
+      <c r="E241" s="135"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A242" s="132"/>
-      <c r="B242" s="132"/>
-      <c r="C242" s="132"/>
-      <c r="D242" s="132"/>
-      <c r="E242" s="132"/>
+      <c r="A242" s="135"/>
+      <c r="B242" s="135"/>
+      <c r="C242" s="135"/>
+      <c r="D242" s="135"/>
+      <c r="E242" s="135"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A243" s="132"/>
-      <c r="B243" s="132"/>
-      <c r="C243" s="132"/>
-      <c r="D243" s="132"/>
-      <c r="E243" s="132"/>
+      <c r="A243" s="135"/>
+      <c r="B243" s="135"/>
+      <c r="C243" s="135"/>
+      <c r="D243" s="135"/>
+      <c r="E243" s="135"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A244" s="132"/>
-      <c r="B244" s="132"/>
-      <c r="C244" s="132"/>
-      <c r="D244" s="132"/>
-      <c r="E244" s="132"/>
+      <c r="A244" s="135"/>
+      <c r="B244" s="135"/>
+      <c r="C244" s="135"/>
+      <c r="D244" s="135"/>
+      <c r="E244" s="135"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" s="132"/>
-      <c r="B245" s="132"/>
-      <c r="C245" s="132"/>
-      <c r="D245" s="132"/>
-      <c r="E245" s="132"/>
+      <c r="A245" s="135"/>
+      <c r="B245" s="135"/>
+      <c r="C245" s="135"/>
+      <c r="D245" s="135"/>
+      <c r="E245" s="135"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A246" s="132"/>
-      <c r="B246" s="132"/>
-      <c r="C246" s="132"/>
-      <c r="D246" s="132"/>
-      <c r="E246" s="132"/>
+      <c r="A246" s="135"/>
+      <c r="B246" s="135"/>
+      <c r="C246" s="135"/>
+      <c r="D246" s="135"/>
+      <c r="E246" s="135"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247" s="132"/>
-      <c r="B247" s="132"/>
-      <c r="C247" s="132"/>
-      <c r="D247" s="132"/>
-      <c r="E247" s="132"/>
+      <c r="A247" s="135"/>
+      <c r="B247" s="135"/>
+      <c r="C247" s="135"/>
+      <c r="D247" s="135"/>
+      <c r="E247" s="135"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248" s="132"/>
-      <c r="B248" s="132"/>
-      <c r="C248" s="132"/>
-      <c r="D248" s="132"/>
-      <c r="E248" s="132"/>
+      <c r="A248" s="135"/>
+      <c r="B248" s="135"/>
+      <c r="C248" s="135"/>
+      <c r="D248" s="135"/>
+      <c r="E248" s="135"/>
     </row>
     <row r="249" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A249" s="14"/>
@@ -13964,13 +13968,13 @@
       <c r="E250" s="82"/>
     </row>
     <row r="251" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A251" s="122" t="s">
+      <c r="A251" s="121" t="s">
         <v>392</v>
       </c>
-      <c r="B251" s="129"/>
-      <c r="C251" s="129"/>
-      <c r="D251" s="129"/>
-      <c r="E251" s="130"/>
+      <c r="B251" s="132"/>
+      <c r="C251" s="132"/>
+      <c r="D251" s="132"/>
+      <c r="E251" s="133"/>
     </row>
     <row r="252" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A252" s="6" t="s">
@@ -14231,13 +14235,13 @@
       <c r="E276" s="42"/>
     </row>
     <row r="277" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="116" t="s">
+      <c r="A277" s="119" t="s">
         <v>704</v>
       </c>
-      <c r="B277" s="115"/>
-      <c r="C277" s="115"/>
-      <c r="D277" s="115"/>
-      <c r="E277" s="115"/>
+      <c r="B277" s="120"/>
+      <c r="C277" s="120"/>
+      <c r="D277" s="120"/>
+      <c r="E277" s="120"/>
     </row>
     <row r="278" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
@@ -14376,13 +14380,13 @@
       </c>
     </row>
     <row r="286" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A286" s="122" t="s">
+      <c r="A286" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="B286" s="123"/>
-      <c r="C286" s="123"/>
-      <c r="D286" s="123"/>
-      <c r="E286" s="124"/>
+      <c r="B286" s="122"/>
+      <c r="C286" s="122"/>
+      <c r="D286" s="122"/>
+      <c r="E286" s="123"/>
     </row>
     <row r="287" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A287" s="6" t="s">
@@ -14463,13 +14467,13 @@
       <c r="E292" s="53"/>
     </row>
     <row r="293" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A293" s="127" t="s">
+      <c r="A293" s="131" t="s">
         <v>267</v>
       </c>
-      <c r="B293" s="114"/>
-      <c r="C293" s="114"/>
-      <c r="D293" s="114"/>
-      <c r="E293" s="114"/>
+      <c r="B293" s="118"/>
+      <c r="C293" s="118"/>
+      <c r="D293" s="118"/>
+      <c r="E293" s="118"/>
     </row>
     <row r="294" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A294" s="6" t="s">
@@ -14540,13 +14544,13 @@
       </c>
     </row>
     <row r="298" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A298" s="127" t="s">
+      <c r="A298" s="131" t="s">
         <v>269</v>
       </c>
-      <c r="B298" s="114"/>
-      <c r="C298" s="114"/>
-      <c r="D298" s="114"/>
-      <c r="E298" s="114"/>
+      <c r="B298" s="118"/>
+      <c r="C298" s="118"/>
+      <c r="D298" s="118"/>
+      <c r="E298" s="118"/>
     </row>
     <row r="299" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A299" s="6" t="s">
@@ -14623,13 +14627,13 @@
       <c r="E304" s="17"/>
     </row>
     <row r="305" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A305" s="127" t="s">
+      <c r="A305" s="131" t="s">
         <v>268</v>
       </c>
-      <c r="B305" s="114"/>
-      <c r="C305" s="114"/>
-      <c r="D305" s="114"/>
-      <c r="E305" s="114"/>
+      <c r="B305" s="118"/>
+      <c r="C305" s="118"/>
+      <c r="D305" s="118"/>
+      <c r="E305" s="118"/>
     </row>
     <row r="306" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A306" s="6" t="s">
@@ -14700,13 +14704,13 @@
       </c>
     </row>
     <row r="310" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A310" s="127" t="s">
+      <c r="A310" s="131" t="s">
         <v>254</v>
       </c>
-      <c r="B310" s="114"/>
-      <c r="C310" s="114"/>
-      <c r="D310" s="114"/>
-      <c r="E310" s="114"/>
+      <c r="B310" s="118"/>
+      <c r="C310" s="118"/>
+      <c r="D310" s="118"/>
+      <c r="E310" s="118"/>
     </row>
     <row r="311" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A311" s="6" t="s">
@@ -14808,13 +14812,13 @@
       <c r="E317" s="82"/>
     </row>
     <row r="318" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="116" t="s">
+      <c r="A318" s="119" t="s">
         <v>707</v>
       </c>
-      <c r="B318" s="115"/>
-      <c r="C318" s="115"/>
-      <c r="D318" s="115"/>
-      <c r="E318" s="115"/>
+      <c r="B318" s="120"/>
+      <c r="C318" s="120"/>
+      <c r="D318" s="120"/>
+      <c r="E318" s="120"/>
     </row>
     <row r="319" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
@@ -14953,13 +14957,13 @@
       </c>
     </row>
     <row r="327" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A327" s="127" t="s">
+      <c r="A327" s="131" t="s">
         <v>381</v>
       </c>
-      <c r="B327" s="114"/>
-      <c r="C327" s="114"/>
-      <c r="D327" s="114"/>
-      <c r="E327" s="114"/>
+      <c r="B327" s="118"/>
+      <c r="C327" s="118"/>
+      <c r="D327" s="118"/>
+      <c r="E327" s="118"/>
     </row>
     <row r="328" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A328" s="6" t="s">
@@ -15030,13 +15034,13 @@
       </c>
     </row>
     <row r="332" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A332" s="127" t="s">
+      <c r="A332" s="131" t="s">
         <v>382</v>
       </c>
-      <c r="B332" s="114"/>
-      <c r="C332" s="114"/>
-      <c r="D332" s="114"/>
-      <c r="E332" s="114"/>
+      <c r="B332" s="118"/>
+      <c r="C332" s="118"/>
+      <c r="D332" s="118"/>
+      <c r="E332" s="118"/>
     </row>
     <row r="333" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A333" s="6" t="s">
@@ -15083,13 +15087,13 @@
       <c r="E336" s="82"/>
     </row>
     <row r="337" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A337" s="127" t="s">
+      <c r="A337" s="131" t="s">
         <v>264</v>
       </c>
-      <c r="B337" s="114"/>
-      <c r="C337" s="114"/>
-      <c r="D337" s="114"/>
-      <c r="E337" s="114"/>
+      <c r="B337" s="118"/>
+      <c r="C337" s="118"/>
+      <c r="D337" s="118"/>
+      <c r="E337" s="118"/>
     </row>
     <row r="338" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A338" s="6" t="s">
@@ -15160,13 +15164,13 @@
       </c>
     </row>
     <row r="342" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A342" s="127" t="s">
+      <c r="A342" s="131" t="s">
         <v>238</v>
       </c>
-      <c r="B342" s="114"/>
-      <c r="C342" s="114"/>
-      <c r="D342" s="114"/>
-      <c r="E342" s="114"/>
+      <c r="B342" s="118"/>
+      <c r="C342" s="118"/>
+      <c r="D342" s="118"/>
+      <c r="E342" s="118"/>
     </row>
     <row r="343" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A343" s="6" t="s">
@@ -15251,13 +15255,13 @@
       <c r="E348" s="82"/>
     </row>
     <row r="349" spans="1:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A349" s="116" t="s">
+      <c r="A349" s="119" t="s">
         <v>709</v>
       </c>
-      <c r="B349" s="115"/>
-      <c r="C349" s="115"/>
-      <c r="D349" s="115"/>
-      <c r="E349" s="115"/>
+      <c r="B349" s="120"/>
+      <c r="C349" s="120"/>
+      <c r="D349" s="120"/>
+      <c r="E349" s="120"/>
     </row>
     <row r="350" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
@@ -15396,13 +15400,13 @@
       </c>
     </row>
     <row r="358" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A358" s="127" t="s">
+      <c r="A358" s="131" t="s">
         <v>355</v>
       </c>
-      <c r="B358" s="114"/>
-      <c r="C358" s="114"/>
-      <c r="D358" s="114"/>
-      <c r="E358" s="114"/>
+      <c r="B358" s="118"/>
+      <c r="C358" s="118"/>
+      <c r="D358" s="118"/>
+      <c r="E358" s="118"/>
     </row>
     <row r="359" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A359" s="6" t="s">
@@ -15473,13 +15477,13 @@
       </c>
     </row>
     <row r="363" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A363" s="127" t="s">
+      <c r="A363" s="131" t="s">
         <v>356</v>
       </c>
-      <c r="B363" s="114"/>
-      <c r="C363" s="114"/>
-      <c r="D363" s="114"/>
-      <c r="E363" s="114"/>
+      <c r="B363" s="118"/>
+      <c r="C363" s="118"/>
+      <c r="D363" s="118"/>
+      <c r="E363" s="118"/>
     </row>
     <row r="364" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A364" s="6" t="s">
@@ -15550,13 +15554,13 @@
       </c>
     </row>
     <row r="368" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A368" s="127" t="s">
+      <c r="A368" s="131" t="s">
         <v>359</v>
       </c>
-      <c r="B368" s="114"/>
-      <c r="C368" s="114"/>
-      <c r="D368" s="114"/>
-      <c r="E368" s="114"/>
+      <c r="B368" s="118"/>
+      <c r="C368" s="118"/>
+      <c r="D368" s="118"/>
+      <c r="E368" s="118"/>
     </row>
     <row r="369" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A369" s="6" t="s">
@@ -15647,13 +15651,13 @@
       <c r="E376" s="82"/>
     </row>
     <row r="377" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A377" s="116" t="s">
+      <c r="A377" s="119" t="s">
         <v>710</v>
       </c>
-      <c r="B377" s="115"/>
-      <c r="C377" s="115"/>
-      <c r="D377" s="115"/>
-      <c r="E377" s="115"/>
+      <c r="B377" s="120"/>
+      <c r="C377" s="120"/>
+      <c r="D377" s="120"/>
+      <c r="E377" s="120"/>
     </row>
     <row r="378" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A378" s="2" t="s">
@@ -15792,13 +15796,13 @@
       </c>
     </row>
     <row r="386" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A386" s="127" t="s">
+      <c r="A386" s="131" t="s">
         <v>394</v>
       </c>
-      <c r="B386" s="114"/>
-      <c r="C386" s="114"/>
-      <c r="D386" s="114"/>
-      <c r="E386" s="114"/>
+      <c r="B386" s="118"/>
+      <c r="C386" s="118"/>
+      <c r="D386" s="118"/>
+      <c r="E386" s="118"/>
     </row>
     <row r="387" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A387" s="6" t="s">
@@ -15869,13 +15873,13 @@
       </c>
     </row>
     <row r="391" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A391" s="127" t="s">
+      <c r="A391" s="131" t="s">
         <v>395</v>
       </c>
-      <c r="B391" s="114"/>
-      <c r="C391" s="114"/>
-      <c r="D391" s="114"/>
-      <c r="E391" s="114"/>
+      <c r="B391" s="118"/>
+      <c r="C391" s="118"/>
+      <c r="D391" s="118"/>
+      <c r="E391" s="118"/>
     </row>
     <row r="392" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A392" s="6" t="s">
@@ -15952,13 +15956,13 @@
       <c r="E397" s="82"/>
     </row>
     <row r="398" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A398" s="127" t="s">
+      <c r="A398" s="131" t="s">
         <v>393</v>
       </c>
-      <c r="B398" s="114"/>
-      <c r="C398" s="114"/>
-      <c r="D398" s="114"/>
-      <c r="E398" s="114"/>
+      <c r="B398" s="118"/>
+      <c r="C398" s="118"/>
+      <c r="D398" s="118"/>
+      <c r="E398" s="118"/>
     </row>
     <row r="399" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A399" s="6" t="s">
@@ -16043,13 +16047,13 @@
       <c r="E404" s="82"/>
     </row>
     <row r="405" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A405" s="128" t="s">
+      <c r="A405" s="136" t="s">
         <v>406</v>
       </c>
-      <c r="B405" s="129"/>
-      <c r="C405" s="129"/>
-      <c r="D405" s="129"/>
-      <c r="E405" s="130"/>
+      <c r="B405" s="132"/>
+      <c r="C405" s="132"/>
+      <c r="D405" s="132"/>
+      <c r="E405" s="133"/>
     </row>
     <row r="406" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A406" s="6" t="s">
@@ -16221,24 +16225,22 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A134:E134"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A368:E368"/>
-    <mergeCell ref="A377:E377"/>
-    <mergeCell ref="A386:E386"/>
-    <mergeCell ref="A391:E391"/>
-    <mergeCell ref="A184:E184"/>
-    <mergeCell ref="A251:E251"/>
-    <mergeCell ref="A238:E248"/>
-    <mergeCell ref="A224:E224"/>
-    <mergeCell ref="A210:E210"/>
-    <mergeCell ref="A193:E193"/>
-    <mergeCell ref="A198:E198"/>
-    <mergeCell ref="A203:E203"/>
-    <mergeCell ref="A231:E231"/>
-    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="A164:E164"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A97:E97"/>
     <mergeCell ref="A405:E405"/>
     <mergeCell ref="A305:E305"/>
     <mergeCell ref="A310:E310"/>
@@ -16255,22 +16257,24 @@
     <mergeCell ref="A318:E318"/>
     <mergeCell ref="A337:E337"/>
     <mergeCell ref="A342:E342"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A155:E155"/>
-    <mergeCell ref="A164:E164"/>
-    <mergeCell ref="A169:E169"/>
-    <mergeCell ref="A177:E177"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A377:E377"/>
+    <mergeCell ref="A386:E386"/>
+    <mergeCell ref="A391:E391"/>
+    <mergeCell ref="A184:E184"/>
+    <mergeCell ref="A251:E251"/>
+    <mergeCell ref="A238:E248"/>
+    <mergeCell ref="A224:E224"/>
+    <mergeCell ref="A210:E210"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A198:E198"/>
+    <mergeCell ref="A203:E203"/>
+    <mergeCell ref="A231:E231"/>
+    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A368:E368"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16290,13 +16294,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="117" t="s">
         <v>685</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -16384,13 +16388,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="128" t="s">
+      <c r="A7" s="136" t="s">
         <v>223</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -16441,13 +16445,13 @@
       <c r="E11" s="82"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="111" t="s">
+      <c r="A12" s="117" t="s">
         <v>686</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
     </row>
     <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="59" t="s">
@@ -16518,13 +16522,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="111" t="s">
+      <c r="A19" s="117" t="s">
         <v>687</v>
       </c>
-      <c r="B19" s="96"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
     </row>
     <row r="20" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="59" t="s">
@@ -16561,13 +16565,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="111" t="s">
+      <c r="A24" s="117" t="s">
         <v>688</v>
       </c>
-      <c r="B24" s="96"/>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-      <c r="E24" s="96"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
     </row>
     <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="59" t="s">
@@ -16667,22 +16671,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="156" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
     </row>
     <row r="2" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="65" t="s">
@@ -16700,17 +16704,17 @@
       <c r="E2" s="66" t="s">
         <v>423</v>
       </c>
-      <c r="F2" s="136" t="s">
+      <c r="F2" s="157" t="s">
         <v>424</v>
       </c>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="138"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="151"/>
     </row>
     <row r="3" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="65"/>
@@ -16722,17 +16726,17 @@
         <v>184</v>
       </c>
       <c r="E3" s="66"/>
-      <c r="F3" s="136" t="s">
+      <c r="F3" s="157" t="s">
         <v>446</v>
       </c>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="137"/>
-      <c r="M3" s="137"/>
-      <c r="N3" s="138"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="150"/>
+      <c r="N3" s="151"/>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="65"/>
@@ -16744,17 +16748,17 @@
         <v>184</v>
       </c>
       <c r="E4" s="66"/>
-      <c r="F4" s="136" t="s">
+      <c r="F4" s="157" t="s">
         <v>442</v>
       </c>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="138"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="150"/>
+      <c r="N4" s="151"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="65"/>
@@ -16766,17 +16770,17 @@
         <v>184</v>
       </c>
       <c r="E5" s="66"/>
-      <c r="F5" s="136" t="s">
+      <c r="F5" s="157" t="s">
         <v>444</v>
       </c>
-      <c r="G5" s="137"/>
-      <c r="H5" s="137"/>
-      <c r="I5" s="137"/>
-      <c r="J5" s="137"/>
-      <c r="K5" s="137"/>
-      <c r="L5" s="137"/>
-      <c r="M5" s="137"/>
-      <c r="N5" s="138"/>
+      <c r="G5" s="150"/>
+      <c r="H5" s="150"/>
+      <c r="I5" s="150"/>
+      <c r="J5" s="150"/>
+      <c r="K5" s="150"/>
+      <c r="L5" s="150"/>
+      <c r="M5" s="150"/>
+      <c r="N5" s="151"/>
     </row>
     <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="65"/>
@@ -16788,17 +16792,17 @@
         <v>184</v>
       </c>
       <c r="E6" s="66"/>
-      <c r="F6" s="136" t="s">
+      <c r="F6" s="157" t="s">
         <v>445</v>
       </c>
-      <c r="G6" s="137"/>
-      <c r="H6" s="137"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="138"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="150"/>
+      <c r="I6" s="150"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="150"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="151"/>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="65"/>
@@ -16810,17 +16814,17 @@
         <v>184</v>
       </c>
       <c r="E7" s="66"/>
-      <c r="F7" s="136" t="s">
+      <c r="F7" s="157" t="s">
         <v>448</v>
       </c>
-      <c r="G7" s="137"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="137"/>
-      <c r="K7" s="137"/>
-      <c r="L7" s="137"/>
-      <c r="M7" s="137"/>
-      <c r="N7" s="138"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="150"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="150"/>
+      <c r="N7" s="151"/>
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="65"/>
@@ -16832,17 +16836,17 @@
         <v>184</v>
       </c>
       <c r="E8" s="66"/>
-      <c r="F8" s="136" t="s">
+      <c r="F8" s="157" t="s">
         <v>449</v>
       </c>
-      <c r="G8" s="137"/>
-      <c r="H8" s="137"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="137"/>
-      <c r="K8" s="137"/>
-      <c r="L8" s="137"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="138"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="150"/>
+      <c r="I8" s="150"/>
+      <c r="J8" s="150"/>
+      <c r="K8" s="150"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="150"/>
+      <c r="N8" s="151"/>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="65"/>
@@ -16854,17 +16858,17 @@
         <v>184</v>
       </c>
       <c r="E9" s="66"/>
-      <c r="F9" s="136" t="s">
+      <c r="F9" s="157" t="s">
         <v>451</v>
       </c>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="138"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="150"/>
+      <c r="J9" s="150"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="150"/>
+      <c r="N9" s="151"/>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="65"/>
@@ -16876,17 +16880,17 @@
         <v>452</v>
       </c>
       <c r="E10" s="66"/>
-      <c r="F10" s="136" t="s">
+      <c r="F10" s="157" t="s">
         <v>453</v>
       </c>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="138"/>
+      <c r="G10" s="150"/>
+      <c r="H10" s="150"/>
+      <c r="I10" s="150"/>
+      <c r="J10" s="150"/>
+      <c r="K10" s="150"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+      <c r="N10" s="151"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="65"/>
@@ -16898,17 +16902,17 @@
         <v>184</v>
       </c>
       <c r="E11" s="66"/>
-      <c r="F11" s="136" t="s">
+      <c r="F11" s="157" t="s">
         <v>455</v>
       </c>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="138"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="151"/>
     </row>
     <row r="12" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="65"/>
@@ -16920,17 +16924,17 @@
         <v>456</v>
       </c>
       <c r="E12" s="66"/>
-      <c r="F12" s="142" t="s">
+      <c r="F12" s="158" t="s">
         <v>555</v>
       </c>
-      <c r="G12" s="143"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="143"/>
-      <c r="M12" s="143"/>
-      <c r="N12" s="144"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="154"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="65"/>
@@ -16942,17 +16946,17 @@
         <v>490</v>
       </c>
       <c r="E13" s="66"/>
-      <c r="F13" s="136" t="s">
+      <c r="F13" s="157" t="s">
         <v>457</v>
       </c>
-      <c r="G13" s="137"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="137"/>
-      <c r="L13" s="137"/>
-      <c r="M13" s="137"/>
-      <c r="N13" s="138"/>
+      <c r="G13" s="150"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="150"/>
+      <c r="J13" s="150"/>
+      <c r="K13" s="150"/>
+      <c r="L13" s="150"/>
+      <c r="M13" s="150"/>
+      <c r="N13" s="151"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="65"/>
@@ -16964,17 +16968,17 @@
         <v>458</v>
       </c>
       <c r="E14" s="66"/>
-      <c r="F14" s="136" t="s">
+      <c r="F14" s="157" t="s">
         <v>459</v>
       </c>
-      <c r="G14" s="137"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="137"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="138"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="150"/>
+      <c r="M14" s="150"/>
+      <c r="N14" s="151"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="65"/>
@@ -16986,17 +16990,17 @@
         <v>460</v>
       </c>
       <c r="E15" s="66"/>
-      <c r="F15" s="136" t="s">
+      <c r="F15" s="157" t="s">
         <v>461</v>
       </c>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="138"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="150"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="150"/>
+      <c r="M15" s="150"/>
+      <c r="N15" s="151"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="65"/>
@@ -17008,17 +17012,17 @@
         <v>463</v>
       </c>
       <c r="E16" s="66"/>
-      <c r="F16" s="136" t="s">
+      <c r="F16" s="157" t="s">
         <v>465</v>
       </c>
-      <c r="G16" s="137"/>
-      <c r="H16" s="137"/>
-      <c r="I16" s="137"/>
-      <c r="J16" s="137"/>
-      <c r="K16" s="137"/>
-      <c r="L16" s="137"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="138"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="150"/>
+      <c r="N16" s="151"/>
     </row>
     <row r="17" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="65"/>
@@ -17030,17 +17034,17 @@
         <v>462</v>
       </c>
       <c r="E17" s="66"/>
-      <c r="F17" s="136" t="s">
+      <c r="F17" s="157" t="s">
         <v>464</v>
       </c>
-      <c r="G17" s="137"/>
-      <c r="H17" s="137"/>
-      <c r="I17" s="137"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="137"/>
-      <c r="L17" s="137"/>
-      <c r="M17" s="137"/>
-      <c r="N17" s="138"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="150"/>
+      <c r="J17" s="150"/>
+      <c r="K17" s="150"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="150"/>
+      <c r="N17" s="151"/>
     </row>
     <row r="18" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="65"/>
@@ -17052,17 +17056,17 @@
         <v>466</v>
       </c>
       <c r="E18" s="66"/>
-      <c r="F18" s="136" t="s">
+      <c r="F18" s="157" t="s">
         <v>467</v>
       </c>
-      <c r="G18" s="137"/>
-      <c r="H18" s="137"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="137"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="137"/>
-      <c r="N18" s="138"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="150"/>
+      <c r="M18" s="150"/>
+      <c r="N18" s="151"/>
     </row>
     <row r="19" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="65"/>
@@ -17074,17 +17078,17 @@
         <v>468</v>
       </c>
       <c r="E19" s="66"/>
-      <c r="F19" s="136" t="s">
+      <c r="F19" s="157" t="s">
         <v>469</v>
       </c>
-      <c r="G19" s="137"/>
-      <c r="H19" s="137"/>
-      <c r="I19" s="137"/>
-      <c r="J19" s="137"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="138"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="150"/>
+      <c r="J19" s="150"/>
+      <c r="K19" s="150"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="150"/>
+      <c r="N19" s="151"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="65"/>
@@ -17092,17 +17096,17 @@
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
       <c r="E20" s="66"/>
-      <c r="F20" s="136">
+      <c r="F20" s="157">
         <v>1</v>
       </c>
-      <c r="G20" s="137"/>
-      <c r="H20" s="137"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="137"/>
-      <c r="K20" s="137"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="138"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="150"/>
+      <c r="J20" s="150"/>
+      <c r="K20" s="150"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="150"/>
+      <c r="N20" s="151"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="57"/>
@@ -17110,51 +17114,51 @@
       <c r="C21" s="57"/>
       <c r="D21" s="57"/>
       <c r="E21" s="58"/>
-      <c r="F21" s="139"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="140"/>
-      <c r="I21" s="140"/>
-      <c r="J21" s="140"/>
-      <c r="K21" s="140"/>
-      <c r="L21" s="140"/>
-      <c r="M21" s="140"/>
-      <c r="N21" s="141"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="163"/>
+      <c r="I21" s="163"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="163"/>
+      <c r="L21" s="163"/>
+      <c r="M21" s="163"/>
+      <c r="N21" s="164"/>
     </row>
     <row r="22" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="133" t="s">
+      <c r="A22" s="159" t="s">
         <v>488</v>
       </c>
-      <c r="B22" s="134"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="134"/>
-      <c r="N22" s="135"/>
+      <c r="B22" s="160"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="160"/>
+      <c r="I22" s="160"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="160"/>
+      <c r="L22" s="160"/>
+      <c r="M22" s="160"/>
+      <c r="N22" s="161"/>
     </row>
     <row r="23" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="146" t="s">
+      <c r="A23" s="155" t="s">
         <v>472</v>
       </c>
-      <c r="B23" s="145"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145"/>
-      <c r="H23" s="145"/>
-      <c r="I23" s="145"/>
-      <c r="J23" s="145"/>
-      <c r="K23" s="145"/>
-      <c r="L23" s="145"/>
-      <c r="M23" s="145"/>
-      <c r="N23" s="145"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="156"/>
+      <c r="H23" s="156"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="156"/>
+      <c r="K23" s="156"/>
+      <c r="L23" s="156"/>
+      <c r="M23" s="156"/>
+      <c r="N23" s="156"/>
     </row>
     <row r="24" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="65" t="s">
@@ -17172,17 +17176,17 @@
       <c r="E24" s="66" t="s">
         <v>423</v>
       </c>
-      <c r="F24" s="147" t="s">
+      <c r="F24" s="149" t="s">
         <v>473</v>
       </c>
-      <c r="G24" s="137"/>
-      <c r="H24" s="137"/>
-      <c r="I24" s="137"/>
-      <c r="J24" s="137"/>
-      <c r="K24" s="137"/>
-      <c r="L24" s="137"/>
-      <c r="M24" s="137"/>
-      <c r="N24" s="138"/>
+      <c r="G24" s="150"/>
+      <c r="H24" s="150"/>
+      <c r="I24" s="150"/>
+      <c r="J24" s="150"/>
+      <c r="K24" s="150"/>
+      <c r="L24" s="150"/>
+      <c r="M24" s="150"/>
+      <c r="N24" s="151"/>
     </row>
     <row r="25" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="65"/>
@@ -17194,17 +17198,17 @@
         <v>474</v>
       </c>
       <c r="E25" s="66"/>
-      <c r="F25" s="147" t="s">
+      <c r="F25" s="149" t="s">
         <v>475</v>
       </c>
-      <c r="G25" s="137"/>
-      <c r="H25" s="137"/>
-      <c r="I25" s="137"/>
-      <c r="J25" s="137"/>
-      <c r="K25" s="137"/>
-      <c r="L25" s="137"/>
-      <c r="M25" s="137"/>
-      <c r="N25" s="138"/>
+      <c r="G25" s="150"/>
+      <c r="H25" s="150"/>
+      <c r="I25" s="150"/>
+      <c r="J25" s="150"/>
+      <c r="K25" s="150"/>
+      <c r="L25" s="150"/>
+      <c r="M25" s="150"/>
+      <c r="N25" s="151"/>
     </row>
     <row r="26" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="65"/>
@@ -17216,17 +17220,17 @@
         <v>476</v>
       </c>
       <c r="E26" s="66"/>
-      <c r="F26" s="147" t="s">
+      <c r="F26" s="149" t="s">
         <v>477</v>
       </c>
-      <c r="G26" s="137"/>
-      <c r="H26" s="137"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="137"/>
-      <c r="K26" s="137"/>
-      <c r="L26" s="137"/>
-      <c r="M26" s="137"/>
-      <c r="N26" s="138"/>
+      <c r="G26" s="150"/>
+      <c r="H26" s="150"/>
+      <c r="I26" s="150"/>
+      <c r="J26" s="150"/>
+      <c r="K26" s="150"/>
+      <c r="L26" s="150"/>
+      <c r="M26" s="150"/>
+      <c r="N26" s="151"/>
     </row>
     <row r="27" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="65"/>
@@ -17238,17 +17242,17 @@
         <v>184</v>
       </c>
       <c r="E27" s="66"/>
-      <c r="F27" s="147" t="s">
+      <c r="F27" s="149" t="s">
         <v>479</v>
       </c>
-      <c r="G27" s="137"/>
-      <c r="H27" s="137"/>
-      <c r="I27" s="137"/>
-      <c r="J27" s="137"/>
-      <c r="K27" s="137"/>
-      <c r="L27" s="137"/>
-      <c r="M27" s="137"/>
-      <c r="N27" s="138"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="150"/>
+      <c r="I27" s="150"/>
+      <c r="J27" s="150"/>
+      <c r="K27" s="150"/>
+      <c r="L27" s="150"/>
+      <c r="M27" s="150"/>
+      <c r="N27" s="151"/>
     </row>
     <row r="28" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="65"/>
@@ -17260,17 +17264,17 @@
         <v>474</v>
       </c>
       <c r="E28" s="66"/>
-      <c r="F28" s="147" t="s">
+      <c r="F28" s="149" t="s">
         <v>478</v>
       </c>
-      <c r="G28" s="137"/>
-      <c r="H28" s="137"/>
-      <c r="I28" s="137"/>
-      <c r="J28" s="137"/>
-      <c r="K28" s="137"/>
-      <c r="L28" s="137"/>
-      <c r="M28" s="137"/>
-      <c r="N28" s="138"/>
+      <c r="G28" s="150"/>
+      <c r="H28" s="150"/>
+      <c r="I28" s="150"/>
+      <c r="J28" s="150"/>
+      <c r="K28" s="150"/>
+      <c r="L28" s="150"/>
+      <c r="M28" s="150"/>
+      <c r="N28" s="151"/>
     </row>
     <row r="29" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="65"/>
@@ -17282,17 +17286,17 @@
         <v>474</v>
       </c>
       <c r="E29" s="66"/>
-      <c r="F29" s="147" t="s">
+      <c r="F29" s="149" t="s">
         <v>480</v>
       </c>
-      <c r="G29" s="137"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="137"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="138"/>
+      <c r="G29" s="150"/>
+      <c r="H29" s="150"/>
+      <c r="I29" s="150"/>
+      <c r="J29" s="150"/>
+      <c r="K29" s="150"/>
+      <c r="L29" s="150"/>
+      <c r="M29" s="150"/>
+      <c r="N29" s="151"/>
     </row>
     <row r="30" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="65"/>
@@ -17304,17 +17308,17 @@
         <v>184</v>
       </c>
       <c r="E30" s="66"/>
-      <c r="F30" s="147" t="s">
+      <c r="F30" s="149" t="s">
         <v>482</v>
       </c>
-      <c r="G30" s="137"/>
-      <c r="H30" s="137"/>
-      <c r="I30" s="137"/>
-      <c r="J30" s="137"/>
-      <c r="K30" s="137"/>
-      <c r="L30" s="137"/>
-      <c r="M30" s="137"/>
-      <c r="N30" s="138"/>
+      <c r="G30" s="150"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="150"/>
+      <c r="K30" s="150"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="150"/>
+      <c r="N30" s="151"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="65"/>
@@ -17326,17 +17330,17 @@
         <v>184</v>
       </c>
       <c r="E31" s="66"/>
-      <c r="F31" s="147" t="s">
+      <c r="F31" s="149" t="s">
         <v>484</v>
       </c>
-      <c r="G31" s="137"/>
-      <c r="H31" s="137"/>
-      <c r="I31" s="137"/>
-      <c r="J31" s="137"/>
-      <c r="K31" s="137"/>
-      <c r="L31" s="137"/>
-      <c r="M31" s="137"/>
-      <c r="N31" s="138"/>
+      <c r="G31" s="150"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="150"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="150"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="151"/>
     </row>
     <row r="32" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="65"/>
@@ -17348,17 +17352,17 @@
         <v>184</v>
       </c>
       <c r="E32" s="66"/>
-      <c r="F32" s="147" t="s">
+      <c r="F32" s="149" t="s">
         <v>485</v>
       </c>
-      <c r="G32" s="137"/>
-      <c r="H32" s="137"/>
-      <c r="I32" s="137"/>
-      <c r="J32" s="137"/>
-      <c r="K32" s="137"/>
-      <c r="L32" s="137"/>
-      <c r="M32" s="137"/>
-      <c r="N32" s="138"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="150"/>
+      <c r="K32" s="150"/>
+      <c r="L32" s="150"/>
+      <c r="M32" s="150"/>
+      <c r="N32" s="151"/>
     </row>
     <row r="33" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="65"/>
@@ -17370,17 +17374,17 @@
         <v>184</v>
       </c>
       <c r="E33" s="66"/>
-      <c r="F33" s="147" t="s">
+      <c r="F33" s="149" t="s">
         <v>486</v>
       </c>
-      <c r="G33" s="137"/>
-      <c r="H33" s="137"/>
-      <c r="I33" s="137"/>
-      <c r="J33" s="137"/>
-      <c r="K33" s="137"/>
-      <c r="L33" s="137"/>
-      <c r="M33" s="137"/>
-      <c r="N33" s="138"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="150"/>
+      <c r="K33" s="150"/>
+      <c r="L33" s="150"/>
+      <c r="M33" s="150"/>
+      <c r="N33" s="151"/>
     </row>
     <row r="34" spans="1:14" s="53" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="65"/>
@@ -17404,358 +17408,344 @@
       <c r="C35" s="65"/>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
-      <c r="F35" s="160"/>
-      <c r="G35" s="143"/>
-      <c r="H35" s="143"/>
-      <c r="I35" s="143"/>
-      <c r="J35" s="143"/>
-      <c r="K35" s="143"/>
-      <c r="L35" s="143"/>
-      <c r="M35" s="143"/>
-      <c r="N35" s="144"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="153"/>
+      <c r="H35" s="153"/>
+      <c r="I35" s="153"/>
+      <c r="J35" s="153"/>
+      <c r="K35" s="153"/>
+      <c r="L35" s="153"/>
+      <c r="M35" s="153"/>
+      <c r="N35" s="154"/>
     </row>
     <row r="36" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="148" t="s">
+      <c r="A36" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B36" s="149"/>
-      <c r="C36" s="149"/>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="149"/>
-      <c r="G36" s="149"/>
-      <c r="H36" s="149"/>
-      <c r="I36" s="149"/>
-      <c r="J36" s="149"/>
-      <c r="K36" s="149"/>
-      <c r="L36" s="149"/>
-      <c r="M36" s="149"/>
-      <c r="N36" s="150"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="138"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="138"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
+      <c r="M36" s="138"/>
+      <c r="N36" s="139"/>
     </row>
     <row r="116" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="117" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D117" s="151" t="s">
+      <c r="D117" s="140" t="s">
         <v>489</v>
       </c>
-      <c r="E117" s="152"/>
-      <c r="F117" s="152"/>
-      <c r="G117" s="152"/>
-      <c r="H117" s="152"/>
-      <c r="I117" s="152"/>
-      <c r="J117" s="152"/>
-      <c r="K117" s="152"/>
-      <c r="L117" s="152"/>
-      <c r="M117" s="152"/>
-      <c r="N117" s="152"/>
-      <c r="O117" s="152"/>
-      <c r="P117" s="153"/>
+      <c r="E117" s="141"/>
+      <c r="F117" s="141"/>
+      <c r="G117" s="141"/>
+      <c r="H117" s="141"/>
+      <c r="I117" s="141"/>
+      <c r="J117" s="141"/>
+      <c r="K117" s="141"/>
+      <c r="L117" s="141"/>
+      <c r="M117" s="141"/>
+      <c r="N117" s="141"/>
+      <c r="O117" s="141"/>
+      <c r="P117" s="142"/>
     </row>
     <row r="118" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D118" s="154"/>
-      <c r="E118" s="155"/>
-      <c r="F118" s="155"/>
-      <c r="G118" s="155"/>
-      <c r="H118" s="155"/>
-      <c r="I118" s="155"/>
-      <c r="J118" s="155"/>
-      <c r="K118" s="155"/>
-      <c r="L118" s="155"/>
-      <c r="M118" s="155"/>
-      <c r="N118" s="155"/>
-      <c r="O118" s="155"/>
-      <c r="P118" s="156"/>
+      <c r="D118" s="143"/>
+      <c r="E118" s="144"/>
+      <c r="F118" s="144"/>
+      <c r="G118" s="144"/>
+      <c r="H118" s="144"/>
+      <c r="I118" s="144"/>
+      <c r="J118" s="144"/>
+      <c r="K118" s="144"/>
+      <c r="L118" s="144"/>
+      <c r="M118" s="144"/>
+      <c r="N118" s="144"/>
+      <c r="O118" s="144"/>
+      <c r="P118" s="145"/>
     </row>
     <row r="119" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D119" s="154"/>
-      <c r="E119" s="155"/>
-      <c r="F119" s="155"/>
-      <c r="G119" s="155"/>
-      <c r="H119" s="155"/>
-      <c r="I119" s="155"/>
-      <c r="J119" s="155"/>
-      <c r="K119" s="155"/>
-      <c r="L119" s="155"/>
-      <c r="M119" s="155"/>
-      <c r="N119" s="155"/>
-      <c r="O119" s="155"/>
-      <c r="P119" s="156"/>
+      <c r="D119" s="143"/>
+      <c r="E119" s="144"/>
+      <c r="F119" s="144"/>
+      <c r="G119" s="144"/>
+      <c r="H119" s="144"/>
+      <c r="I119" s="144"/>
+      <c r="J119" s="144"/>
+      <c r="K119" s="144"/>
+      <c r="L119" s="144"/>
+      <c r="M119" s="144"/>
+      <c r="N119" s="144"/>
+      <c r="O119" s="144"/>
+      <c r="P119" s="145"/>
     </row>
     <row r="120" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D120" s="154"/>
-      <c r="E120" s="155"/>
-      <c r="F120" s="155"/>
-      <c r="G120" s="155"/>
-      <c r="H120" s="155"/>
-      <c r="I120" s="155"/>
-      <c r="J120" s="155"/>
-      <c r="K120" s="155"/>
-      <c r="L120" s="155"/>
-      <c r="M120" s="155"/>
-      <c r="N120" s="155"/>
-      <c r="O120" s="155"/>
-      <c r="P120" s="156"/>
+      <c r="D120" s="143"/>
+      <c r="E120" s="144"/>
+      <c r="F120" s="144"/>
+      <c r="G120" s="144"/>
+      <c r="H120" s="144"/>
+      <c r="I120" s="144"/>
+      <c r="J120" s="144"/>
+      <c r="K120" s="144"/>
+      <c r="L120" s="144"/>
+      <c r="M120" s="144"/>
+      <c r="N120" s="144"/>
+      <c r="O120" s="144"/>
+      <c r="P120" s="145"/>
     </row>
     <row r="121" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D121" s="154"/>
-      <c r="E121" s="155"/>
-      <c r="F121" s="155"/>
-      <c r="G121" s="155"/>
-      <c r="H121" s="155"/>
-      <c r="I121" s="155"/>
-      <c r="J121" s="155"/>
-      <c r="K121" s="155"/>
-      <c r="L121" s="155"/>
-      <c r="M121" s="155"/>
-      <c r="N121" s="155"/>
-      <c r="O121" s="155"/>
-      <c r="P121" s="156"/>
+      <c r="D121" s="143"/>
+      <c r="E121" s="144"/>
+      <c r="F121" s="144"/>
+      <c r="G121" s="144"/>
+      <c r="H121" s="144"/>
+      <c r="I121" s="144"/>
+      <c r="J121" s="144"/>
+      <c r="K121" s="144"/>
+      <c r="L121" s="144"/>
+      <c r="M121" s="144"/>
+      <c r="N121" s="144"/>
+      <c r="O121" s="144"/>
+      <c r="P121" s="145"/>
     </row>
     <row r="122" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D122" s="154"/>
-      <c r="E122" s="155"/>
-      <c r="F122" s="155"/>
-      <c r="G122" s="155"/>
-      <c r="H122" s="155"/>
-      <c r="I122" s="155"/>
-      <c r="J122" s="155"/>
-      <c r="K122" s="155"/>
-      <c r="L122" s="155"/>
-      <c r="M122" s="155"/>
-      <c r="N122" s="155"/>
-      <c r="O122" s="155"/>
-      <c r="P122" s="156"/>
+      <c r="D122" s="143"/>
+      <c r="E122" s="144"/>
+      <c r="F122" s="144"/>
+      <c r="G122" s="144"/>
+      <c r="H122" s="144"/>
+      <c r="I122" s="144"/>
+      <c r="J122" s="144"/>
+      <c r="K122" s="144"/>
+      <c r="L122" s="144"/>
+      <c r="M122" s="144"/>
+      <c r="N122" s="144"/>
+      <c r="O122" s="144"/>
+      <c r="P122" s="145"/>
     </row>
     <row r="123" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D123" s="154"/>
-      <c r="E123" s="155"/>
-      <c r="F123" s="155"/>
-      <c r="G123" s="155"/>
-      <c r="H123" s="155"/>
-      <c r="I123" s="155"/>
-      <c r="J123" s="155"/>
-      <c r="K123" s="155"/>
-      <c r="L123" s="155"/>
-      <c r="M123" s="155"/>
-      <c r="N123" s="155"/>
-      <c r="O123" s="155"/>
-      <c r="P123" s="156"/>
+      <c r="D123" s="143"/>
+      <c r="E123" s="144"/>
+      <c r="F123" s="144"/>
+      <c r="G123" s="144"/>
+      <c r="H123" s="144"/>
+      <c r="I123" s="144"/>
+      <c r="J123" s="144"/>
+      <c r="K123" s="144"/>
+      <c r="L123" s="144"/>
+      <c r="M123" s="144"/>
+      <c r="N123" s="144"/>
+      <c r="O123" s="144"/>
+      <c r="P123" s="145"/>
     </row>
     <row r="124" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D124" s="154"/>
-      <c r="E124" s="155"/>
-      <c r="F124" s="155"/>
-      <c r="G124" s="155"/>
-      <c r="H124" s="155"/>
-      <c r="I124" s="155"/>
-      <c r="J124" s="155"/>
-      <c r="K124" s="155"/>
-      <c r="L124" s="155"/>
-      <c r="M124" s="155"/>
-      <c r="N124" s="155"/>
-      <c r="O124" s="155"/>
-      <c r="P124" s="156"/>
+      <c r="D124" s="143"/>
+      <c r="E124" s="144"/>
+      <c r="F124" s="144"/>
+      <c r="G124" s="144"/>
+      <c r="H124" s="144"/>
+      <c r="I124" s="144"/>
+      <c r="J124" s="144"/>
+      <c r="K124" s="144"/>
+      <c r="L124" s="144"/>
+      <c r="M124" s="144"/>
+      <c r="N124" s="144"/>
+      <c r="O124" s="144"/>
+      <c r="P124" s="145"/>
     </row>
     <row r="125" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D125" s="154"/>
-      <c r="E125" s="155"/>
-      <c r="F125" s="155"/>
-      <c r="G125" s="155"/>
-      <c r="H125" s="155"/>
-      <c r="I125" s="155"/>
-      <c r="J125" s="155"/>
-      <c r="K125" s="155"/>
-      <c r="L125" s="155"/>
-      <c r="M125" s="155"/>
-      <c r="N125" s="155"/>
-      <c r="O125" s="155"/>
-      <c r="P125" s="156"/>
+      <c r="D125" s="143"/>
+      <c r="E125" s="144"/>
+      <c r="F125" s="144"/>
+      <c r="G125" s="144"/>
+      <c r="H125" s="144"/>
+      <c r="I125" s="144"/>
+      <c r="J125" s="144"/>
+      <c r="K125" s="144"/>
+      <c r="L125" s="144"/>
+      <c r="M125" s="144"/>
+      <c r="N125" s="144"/>
+      <c r="O125" s="144"/>
+      <c r="P125" s="145"/>
     </row>
     <row r="126" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D126" s="154"/>
-      <c r="E126" s="155"/>
-      <c r="F126" s="155"/>
-      <c r="G126" s="155"/>
-      <c r="H126" s="155"/>
-      <c r="I126" s="155"/>
-      <c r="J126" s="155"/>
-      <c r="K126" s="155"/>
-      <c r="L126" s="155"/>
-      <c r="M126" s="155"/>
-      <c r="N126" s="155"/>
-      <c r="O126" s="155"/>
-      <c r="P126" s="156"/>
+      <c r="D126" s="143"/>
+      <c r="E126" s="144"/>
+      <c r="F126" s="144"/>
+      <c r="G126" s="144"/>
+      <c r="H126" s="144"/>
+      <c r="I126" s="144"/>
+      <c r="J126" s="144"/>
+      <c r="K126" s="144"/>
+      <c r="L126" s="144"/>
+      <c r="M126" s="144"/>
+      <c r="N126" s="144"/>
+      <c r="O126" s="144"/>
+      <c r="P126" s="145"/>
     </row>
     <row r="127" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D127" s="154"/>
-      <c r="E127" s="155"/>
-      <c r="F127" s="155"/>
-      <c r="G127" s="155"/>
-      <c r="H127" s="155"/>
-      <c r="I127" s="155"/>
-      <c r="J127" s="155"/>
-      <c r="K127" s="155"/>
-      <c r="L127" s="155"/>
-      <c r="M127" s="155"/>
-      <c r="N127" s="155"/>
-      <c r="O127" s="155"/>
-      <c r="P127" s="156"/>
+      <c r="D127" s="143"/>
+      <c r="E127" s="144"/>
+      <c r="F127" s="144"/>
+      <c r="G127" s="144"/>
+      <c r="H127" s="144"/>
+      <c r="I127" s="144"/>
+      <c r="J127" s="144"/>
+      <c r="K127" s="144"/>
+      <c r="L127" s="144"/>
+      <c r="M127" s="144"/>
+      <c r="N127" s="144"/>
+      <c r="O127" s="144"/>
+      <c r="P127" s="145"/>
     </row>
     <row r="128" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D128" s="154"/>
-      <c r="E128" s="155"/>
-      <c r="F128" s="155"/>
-      <c r="G128" s="155"/>
-      <c r="H128" s="155"/>
-      <c r="I128" s="155"/>
-      <c r="J128" s="155"/>
-      <c r="K128" s="155"/>
-      <c r="L128" s="155"/>
-      <c r="M128" s="155"/>
-      <c r="N128" s="155"/>
-      <c r="O128" s="155"/>
-      <c r="P128" s="156"/>
+      <c r="D128" s="143"/>
+      <c r="E128" s="144"/>
+      <c r="F128" s="144"/>
+      <c r="G128" s="144"/>
+      <c r="H128" s="144"/>
+      <c r="I128" s="144"/>
+      <c r="J128" s="144"/>
+      <c r="K128" s="144"/>
+      <c r="L128" s="144"/>
+      <c r="M128" s="144"/>
+      <c r="N128" s="144"/>
+      <c r="O128" s="144"/>
+      <c r="P128" s="145"/>
     </row>
     <row r="129" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D129" s="154"/>
-      <c r="E129" s="155"/>
-      <c r="F129" s="155"/>
-      <c r="G129" s="155"/>
-      <c r="H129" s="155"/>
-      <c r="I129" s="155"/>
-      <c r="J129" s="155"/>
-      <c r="K129" s="155"/>
-      <c r="L129" s="155"/>
-      <c r="M129" s="155"/>
-      <c r="N129" s="155"/>
-      <c r="O129" s="155"/>
-      <c r="P129" s="156"/>
+      <c r="D129" s="143"/>
+      <c r="E129" s="144"/>
+      <c r="F129" s="144"/>
+      <c r="G129" s="144"/>
+      <c r="H129" s="144"/>
+      <c r="I129" s="144"/>
+      <c r="J129" s="144"/>
+      <c r="K129" s="144"/>
+      <c r="L129" s="144"/>
+      <c r="M129" s="144"/>
+      <c r="N129" s="144"/>
+      <c r="O129" s="144"/>
+      <c r="P129" s="145"/>
     </row>
     <row r="130" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D130" s="154"/>
-      <c r="E130" s="155"/>
-      <c r="F130" s="155"/>
-      <c r="G130" s="155"/>
-      <c r="H130" s="155"/>
-      <c r="I130" s="155"/>
-      <c r="J130" s="155"/>
-      <c r="K130" s="155"/>
-      <c r="L130" s="155"/>
-      <c r="M130" s="155"/>
-      <c r="N130" s="155"/>
-      <c r="O130" s="155"/>
-      <c r="P130" s="156"/>
+      <c r="D130" s="143"/>
+      <c r="E130" s="144"/>
+      <c r="F130" s="144"/>
+      <c r="G130" s="144"/>
+      <c r="H130" s="144"/>
+      <c r="I130" s="144"/>
+      <c r="J130" s="144"/>
+      <c r="K130" s="144"/>
+      <c r="L130" s="144"/>
+      <c r="M130" s="144"/>
+      <c r="N130" s="144"/>
+      <c r="O130" s="144"/>
+      <c r="P130" s="145"/>
     </row>
     <row r="131" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D131" s="154"/>
-      <c r="E131" s="155"/>
-      <c r="F131" s="155"/>
-      <c r="G131" s="155"/>
-      <c r="H131" s="155"/>
-      <c r="I131" s="155"/>
-      <c r="J131" s="155"/>
-      <c r="K131" s="155"/>
-      <c r="L131" s="155"/>
-      <c r="M131" s="155"/>
-      <c r="N131" s="155"/>
-      <c r="O131" s="155"/>
-      <c r="P131" s="156"/>
+      <c r="D131" s="143"/>
+      <c r="E131" s="144"/>
+      <c r="F131" s="144"/>
+      <c r="G131" s="144"/>
+      <c r="H131" s="144"/>
+      <c r="I131" s="144"/>
+      <c r="J131" s="144"/>
+      <c r="K131" s="144"/>
+      <c r="L131" s="144"/>
+      <c r="M131" s="144"/>
+      <c r="N131" s="144"/>
+      <c r="O131" s="144"/>
+      <c r="P131" s="145"/>
     </row>
     <row r="132" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D132" s="154"/>
-      <c r="E132" s="155"/>
-      <c r="F132" s="155"/>
-      <c r="G132" s="155"/>
-      <c r="H132" s="155"/>
-      <c r="I132" s="155"/>
-      <c r="J132" s="155"/>
-      <c r="K132" s="155"/>
-      <c r="L132" s="155"/>
-      <c r="M132" s="155"/>
-      <c r="N132" s="155"/>
-      <c r="O132" s="155"/>
-      <c r="P132" s="156"/>
+      <c r="D132" s="143"/>
+      <c r="E132" s="144"/>
+      <c r="F132" s="144"/>
+      <c r="G132" s="144"/>
+      <c r="H132" s="144"/>
+      <c r="I132" s="144"/>
+      <c r="J132" s="144"/>
+      <c r="K132" s="144"/>
+      <c r="L132" s="144"/>
+      <c r="M132" s="144"/>
+      <c r="N132" s="144"/>
+      <c r="O132" s="144"/>
+      <c r="P132" s="145"/>
     </row>
     <row r="133" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D133" s="154"/>
-      <c r="E133" s="155"/>
-      <c r="F133" s="155"/>
-      <c r="G133" s="155"/>
-      <c r="H133" s="155"/>
-      <c r="I133" s="155"/>
-      <c r="J133" s="155"/>
-      <c r="K133" s="155"/>
-      <c r="L133" s="155"/>
-      <c r="M133" s="155"/>
-      <c r="N133" s="155"/>
-      <c r="O133" s="155"/>
-      <c r="P133" s="156"/>
+      <c r="D133" s="143"/>
+      <c r="E133" s="144"/>
+      <c r="F133" s="144"/>
+      <c r="G133" s="144"/>
+      <c r="H133" s="144"/>
+      <c r="I133" s="144"/>
+      <c r="J133" s="144"/>
+      <c r="K133" s="144"/>
+      <c r="L133" s="144"/>
+      <c r="M133" s="144"/>
+      <c r="N133" s="144"/>
+      <c r="O133" s="144"/>
+      <c r="P133" s="145"/>
     </row>
     <row r="134" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D134" s="154"/>
-      <c r="E134" s="155"/>
-      <c r="F134" s="155"/>
-      <c r="G134" s="155"/>
-      <c r="H134" s="155"/>
-      <c r="I134" s="155"/>
-      <c r="J134" s="155"/>
-      <c r="K134" s="155"/>
-      <c r="L134" s="155"/>
-      <c r="M134" s="155"/>
-      <c r="N134" s="155"/>
-      <c r="O134" s="155"/>
-      <c r="P134" s="156"/>
+      <c r="D134" s="143"/>
+      <c r="E134" s="144"/>
+      <c r="F134" s="144"/>
+      <c r="G134" s="144"/>
+      <c r="H134" s="144"/>
+      <c r="I134" s="144"/>
+      <c r="J134" s="144"/>
+      <c r="K134" s="144"/>
+      <c r="L134" s="144"/>
+      <c r="M134" s="144"/>
+      <c r="N134" s="144"/>
+      <c r="O134" s="144"/>
+      <c r="P134" s="145"/>
     </row>
     <row r="135" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D135" s="154"/>
-      <c r="E135" s="155"/>
-      <c r="F135" s="155"/>
-      <c r="G135" s="155"/>
-      <c r="H135" s="155"/>
-      <c r="I135" s="155"/>
-      <c r="J135" s="155"/>
-      <c r="K135" s="155"/>
-      <c r="L135" s="155"/>
-      <c r="M135" s="155"/>
-      <c r="N135" s="155"/>
-      <c r="O135" s="155"/>
-      <c r="P135" s="156"/>
+      <c r="D135" s="143"/>
+      <c r="E135" s="144"/>
+      <c r="F135" s="144"/>
+      <c r="G135" s="144"/>
+      <c r="H135" s="144"/>
+      <c r="I135" s="144"/>
+      <c r="J135" s="144"/>
+      <c r="K135" s="144"/>
+      <c r="L135" s="144"/>
+      <c r="M135" s="144"/>
+      <c r="N135" s="144"/>
+      <c r="O135" s="144"/>
+      <c r="P135" s="145"/>
     </row>
     <row r="136" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D136" s="157"/>
-      <c r="E136" s="158"/>
-      <c r="F136" s="158"/>
-      <c r="G136" s="158"/>
-      <c r="H136" s="158"/>
-      <c r="I136" s="158"/>
-      <c r="J136" s="158"/>
-      <c r="K136" s="158"/>
-      <c r="L136" s="158"/>
-      <c r="M136" s="158"/>
-      <c r="N136" s="158"/>
-      <c r="O136" s="158"/>
-      <c r="P136" s="159"/>
+      <c r="D136" s="146"/>
+      <c r="E136" s="147"/>
+      <c r="F136" s="147"/>
+      <c r="G136" s="147"/>
+      <c r="H136" s="147"/>
+      <c r="I136" s="147"/>
+      <c r="J136" s="147"/>
+      <c r="K136" s="147"/>
+      <c r="L136" s="147"/>
+      <c r="M136" s="147"/>
+      <c r="N136" s="147"/>
+      <c r="O136" s="147"/>
+      <c r="P136" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="D117:P136"/>
-    <mergeCell ref="F33:N33"/>
-    <mergeCell ref="F35:N35"/>
-    <mergeCell ref="F28:N28"/>
-    <mergeCell ref="F29:N29"/>
-    <mergeCell ref="F30:N30"/>
-    <mergeCell ref="F31:N31"/>
-    <mergeCell ref="F32:N32"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="F24:N24"/>
-    <mergeCell ref="F25:N25"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="F3:N3"/>
-    <mergeCell ref="F4:N4"/>
-    <mergeCell ref="F5:N5"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="F18:N18"/>
+    <mergeCell ref="F19:N19"/>
+    <mergeCell ref="F20:N20"/>
+    <mergeCell ref="F21:N21"/>
     <mergeCell ref="F17:N17"/>
     <mergeCell ref="F6:N6"/>
     <mergeCell ref="F7:N7"/>
@@ -17768,11 +17758,25 @@
     <mergeCell ref="F14:N14"/>
     <mergeCell ref="F15:N15"/>
     <mergeCell ref="F16:N16"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="F18:N18"/>
-    <mergeCell ref="F19:N19"/>
-    <mergeCell ref="F20:N20"/>
-    <mergeCell ref="F21:N21"/>
+    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F3:N3"/>
+    <mergeCell ref="F4:N4"/>
+    <mergeCell ref="F5:N5"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="F24:N24"/>
+    <mergeCell ref="F25:N25"/>
+    <mergeCell ref="F26:N26"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="D117:P136"/>
+    <mergeCell ref="F33:N33"/>
+    <mergeCell ref="F35:N35"/>
+    <mergeCell ref="F28:N28"/>
+    <mergeCell ref="F29:N29"/>
+    <mergeCell ref="F30:N30"/>
+    <mergeCell ref="F31:N31"/>
+    <mergeCell ref="F32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
+++ b/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LinWenTao\Desktop\Outbound_station\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9297DE00-C584-43EE-BB95-56F319724729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2832D7-E0D7-4907-8911-75B0BE4F3863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="版本" sheetId="3" r:id="rId1"/>
@@ -1613,10 +1613,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>响应类型编号：12001，JSON数据：见下表，名称：</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>任务下发的时间戳</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2606,11 +2602,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>下发解除库位传送带运行超时警告指令
-请求类型编号：2001，JSON数据：见下表，名称：</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>解除库位传送带运行超时异常</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2955,6 +2946,15 @@
   </si>
   <si>
     <t>station_status</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>下发解除库位传送带运行超时警告指令
+请求类型编号：2001，JSON数据：见下表，名称：clear_storage_conveyor_timeout_alarm_req</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应类型编号：12001，JSON数据：见下表，名称：clear_storage_conveyor_timeout_alarm_res</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -4143,13 +4143,13 @@
     </row>
     <row r="4" spans="1:8" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
+        <v>490</v>
+      </c>
+      <c r="B4" s="71" t="s">
+        <v>573</v>
+      </c>
+      <c r="C4" s="39" t="s">
         <v>491</v>
-      </c>
-      <c r="B4" s="71" t="s">
-        <v>574</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>492</v>
       </c>
       <c r="D4" s="40">
         <v>46155</v>
@@ -4157,13 +4157,13 @@
     </row>
     <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="92" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D5" s="40">
         <v>46160</v>
@@ -4304,7 +4304,7 @@
       <c r="E4" s="99"/>
       <c r="F4" s="99"/>
       <c r="G4" s="21" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H4" s="21" t="s">
         <v>11</v>
@@ -4320,15 +4320,15 @@
       <c r="E5" s="99"/>
       <c r="F5" s="99"/>
       <c r="G5" s="21" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H5" s="87" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="49" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="108" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B6" s="99"/>
       <c r="C6" s="99"/>
@@ -4781,7 +4781,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="114" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B1" s="115"/>
       <c r="C1" s="115"/>
@@ -4848,7 +4848,7 @@
         <v>11003</v>
       </c>
       <c r="C6" s="110" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D6" s="112"/>
       <c r="E6" s="112"/>
@@ -4900,7 +4900,7 @@
         <v>11007</v>
       </c>
       <c r="C10" s="110" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D10" s="112"/>
       <c r="E10" s="112"/>
@@ -4930,7 +4930,7 @@
         <v>11100</v>
       </c>
       <c r="C15" s="117" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D15" s="99"/>
       <c r="E15" s="99"/>
@@ -4944,14 +4944,14 @@
         <v>11101</v>
       </c>
       <c r="C16" s="117" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D16" s="99"/>
       <c r="E16" s="99"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="114" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B19" s="115"/>
       <c r="C19" s="115"/>
@@ -4992,7 +4992,7 @@
         <v>12001</v>
       </c>
       <c r="C22" s="113" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D22" s="113"/>
       <c r="E22" s="113"/>
@@ -5020,7 +5020,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="114" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B26" s="115"/>
       <c r="C26" s="115"/>
@@ -5035,7 +5035,7 @@
         <v>13000</v>
       </c>
       <c r="C27" s="110" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D27" s="111"/>
       <c r="E27" s="111"/>
@@ -5048,7 +5048,7 @@
         <v>13001</v>
       </c>
       <c r="C28" s="110" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D28" s="111"/>
       <c r="E28" s="111"/>
@@ -5061,7 +5061,7 @@
         <v>13002</v>
       </c>
       <c r="C29" s="110" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D29" s="111"/>
       <c r="E29" s="111"/>
@@ -5074,7 +5074,7 @@
         <v>13003</v>
       </c>
       <c r="C30" s="110" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D30" s="110"/>
       <c r="E30" s="110"/>
@@ -5087,7 +5087,7 @@
         <v>13004</v>
       </c>
       <c r="C31" s="110" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D31" s="110"/>
       <c r="E31" s="110"/>
@@ -5100,7 +5100,7 @@
         <v>13005</v>
       </c>
       <c r="C32" s="110" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D32" s="110"/>
       <c r="E32" s="110"/>
@@ -5113,7 +5113,7 @@
         <v>13006</v>
       </c>
       <c r="C33" s="110" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D33" s="110"/>
       <c r="E33" s="110"/>
@@ -5126,7 +5126,7 @@
         <v>13007</v>
       </c>
       <c r="C34" s="110" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D34" s="110"/>
       <c r="E34" s="110"/>
@@ -5139,7 +5139,7 @@
         <v>13008</v>
       </c>
       <c r="C35" s="110" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D35" s="110"/>
       <c r="E35" s="110"/>
@@ -5152,7 +5152,7 @@
         <v>13009</v>
       </c>
       <c r="C36" s="110" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D36" s="110"/>
       <c r="E36" s="110"/>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="114" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
@@ -5250,7 +5250,7 @@
         <v>14001</v>
       </c>
       <c r="C46" s="110" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D46" s="111"/>
       <c r="E46" s="111"/>
@@ -5467,10 +5467,10 @@
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>57</v>
@@ -5479,7 +5479,7 @@
         <v>243</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
@@ -5496,7 +5496,7 @@
         <v>65</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="21" spans="1:8" ht="66" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>72</v>
@@ -5671,7 +5671,7 @@
         <v>65</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -5906,7 +5906,7 @@
     </row>
     <row r="48" spans="1:8" s="82" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="117" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B48" s="99"/>
       <c r="C48" s="99"/>
@@ -5986,27 +5986,27 @@
     </row>
     <row r="53" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A53" s="61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B53" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="C53" s="62" t="s">
         <v>611</v>
-      </c>
-      <c r="C53" s="62" t="s">
-        <v>612</v>
       </c>
       <c r="D53" s="74" t="s">
         <v>221</v>
       </c>
       <c r="E53" s="64" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="54" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A54" s="85" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B54" s="61" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C54" s="62" t="s">
         <v>235</v>
@@ -6015,12 +6015,12 @@
         <v>221</v>
       </c>
       <c r="E54" s="64" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="55" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A55" s="118" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B55" s="118"/>
       <c r="C55" s="118"/>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="57" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A57" s="85" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B57" s="61" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C57" s="62" t="s">
         <v>228</v>
@@ -6058,185 +6058,185 @@
         <v>221</v>
       </c>
       <c r="E57" s="64" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="58" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A58" s="61" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B58" s="61" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C58" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D58" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E58" s="64" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="59" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A59" s="61" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B59" s="61" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C59" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D59" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E59" s="64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="60" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A60" s="61" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B60" s="61" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C60" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D60" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E60" s="64" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="61" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A61" s="61" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B61" s="61" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C61" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D61" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E61" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="62" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="61" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B62" s="61" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C62" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D62" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E62" s="64" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="63" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A63" s="61" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B63" s="61" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C63" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D63" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E63" s="64" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="64" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A64" s="61" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B64" s="61" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C64" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D64" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E64" s="64" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A65" s="61" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B65" s="61" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C65" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D65" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E65" s="64" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="66" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A66" s="61" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C66" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D66" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E66" s="64" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A67" s="61" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B67" s="61" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C67" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D67" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E67" s="64" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="68" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A68" s="61" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B68" s="61" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C68" s="62" t="s">
         <v>242</v>
@@ -6245,15 +6245,15 @@
         <v>221</v>
       </c>
       <c r="E68" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A69" s="61" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B69" s="61" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C69" s="62" t="s">
         <v>242</v>
@@ -6262,15 +6262,15 @@
         <v>221</v>
       </c>
       <c r="E69" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="70" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A70" s="61" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C70" s="62" t="s">
         <v>242</v>
@@ -6279,15 +6279,15 @@
         <v>221</v>
       </c>
       <c r="E70" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="71" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A71" s="61" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C71" s="62" t="s">
         <v>242</v>
@@ -6296,14 +6296,14 @@
         <v>221</v>
       </c>
       <c r="E71" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="72" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="117" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B74" s="99"/>
       <c r="C74" s="99"/>
@@ -6463,13 +6463,13 @@
         <v>65</v>
       </c>
       <c r="E83" s="43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="84" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="86" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="117" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B86" s="99"/>
       <c r="C86" s="99"/>
@@ -6592,7 +6592,7 @@
     </row>
     <row r="94" spans="1:8" ht="66" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>72</v>
@@ -6638,12 +6638,12 @@
         <v>65</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="119" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B99" s="120"/>
       <c r="C99" s="120"/>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="120" spans="1:8" s="82" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="117" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B120" s="99"/>
       <c r="C120" s="99"/>
@@ -6951,27 +6951,27 @@
     </row>
     <row r="125" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A125" s="61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B125" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="C125" s="62" t="s">
         <v>611</v>
-      </c>
-      <c r="C125" s="62" t="s">
-        <v>612</v>
       </c>
       <c r="D125" s="74" t="s">
         <v>221</v>
       </c>
       <c r="E125" s="64" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="126" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A126" s="61" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B126" s="61" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C126" s="62" t="s">
         <v>235</v>
@@ -6980,12 +6980,12 @@
         <v>221</v>
       </c>
       <c r="E126" s="64" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="127" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A127" s="118" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B127" s="118"/>
       <c r="C127" s="118"/>
@@ -7011,10 +7011,10 @@
     </row>
     <row r="129" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A129" s="61" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B129" s="61" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C129" s="62" t="s">
         <v>228</v>
@@ -7023,185 +7023,185 @@
         <v>221</v>
       </c>
       <c r="E129" s="64" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="130" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A130" s="61" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B130" s="61" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C130" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D130" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E130" s="64" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="131" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A131" s="61" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B131" s="61" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C131" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D131" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E131" s="64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="132" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A132" s="61" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B132" s="61" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C132" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D132" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E132" s="64" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="133" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A133" s="61" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B133" s="61" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C133" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D133" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E133" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="134" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A134" s="61" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B134" s="61" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C134" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D134" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E134" s="64" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="135" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A135" s="61" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B135" s="61" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C135" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D135" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E135" s="64" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="136" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A136" s="61" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B136" s="61" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C136" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D136" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E136" s="64" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="137" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A137" s="61" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B137" s="61" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C137" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D137" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E137" s="64" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="138" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A138" s="61" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B138" s="61" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C138" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D138" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E138" s="64" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="139" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A139" s="61" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B139" s="61" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C139" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D139" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E139" s="64" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="140" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A140" s="61" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B140" s="61" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C140" s="62" t="s">
         <v>242</v>
@@ -7210,15 +7210,15 @@
         <v>221</v>
       </c>
       <c r="E140" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="141" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A141" s="61" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B141" s="61" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C141" s="62" t="s">
         <v>242</v>
@@ -7227,15 +7227,15 @@
         <v>221</v>
       </c>
       <c r="E141" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="142" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A142" s="61" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B142" s="61" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C142" s="62" t="s">
         <v>242</v>
@@ -7244,15 +7244,15 @@
         <v>221</v>
       </c>
       <c r="E142" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="143" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A143" s="61" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B143" s="61" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C143" s="62" t="s">
         <v>242</v>
@@ -7261,14 +7261,14 @@
         <v>221</v>
       </c>
       <c r="E143" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="144" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="145" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="146" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="117" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B146" s="99"/>
       <c r="C146" s="99"/>
@@ -7445,7 +7445,7 @@
         <v>65</v>
       </c>
       <c r="E156" s="43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
@@ -7535,27 +7535,27 @@
     </row>
     <row r="162" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A162" s="61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B162" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="C162" s="62" t="s">
         <v>611</v>
-      </c>
-      <c r="C162" s="62" t="s">
-        <v>612</v>
       </c>
       <c r="D162" s="74" t="s">
         <v>221</v>
       </c>
       <c r="E162" s="64" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="163" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A163" s="61" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B163" s="61" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C163" s="62" t="s">
         <v>235</v>
@@ -7564,7 +7564,7 @@
         <v>221</v>
       </c>
       <c r="E163" s="64" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -7658,7 +7658,7 @@
         <v>65</v>
       </c>
       <c r="E169" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -7740,10 +7740,10 @@
     </row>
     <row r="175" spans="1:5" s="80" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A175" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>242</v>
@@ -7752,7 +7752,7 @@
         <v>243</v>
       </c>
       <c r="E175" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -7783,7 +7783,7 @@
     </row>
     <row r="178" spans="1:8" ht="66" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>72</v>
@@ -7832,12 +7832,12 @@
         <v>65</v>
       </c>
       <c r="E180" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A181" s="118" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B181" s="118"/>
       <c r="C181" s="118"/>
@@ -7863,10 +7863,10 @@
     </row>
     <row r="183" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A183" s="61" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B183" s="61" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C183" s="62" t="s">
         <v>228</v>
@@ -7875,185 +7875,185 @@
         <v>221</v>
       </c>
       <c r="E183" s="64" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="184" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A184" s="61" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B184" s="61" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C184" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D184" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E184" s="64" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="185" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A185" s="61" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B185" s="61" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C185" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D185" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E185" s="64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="186" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A186" s="61" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B186" s="61" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C186" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D186" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E186" s="64" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="187" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A187" s="61" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B187" s="61" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C187" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D187" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E187" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="188" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A188" s="61" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B188" s="61" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C188" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D188" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E188" s="64" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="189" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A189" s="61" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B189" s="61" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C189" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D189" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E189" s="64" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="190" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A190" s="61" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B190" s="61" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C190" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D190" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E190" s="64" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="191" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A191" s="61" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B191" s="61" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C191" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D191" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E191" s="64" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="192" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A192" s="61" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B192" s="61" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C192" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D192" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E192" s="64" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="193" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A193" s="61" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B193" s="61" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C193" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D193" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E193" s="64" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="194" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A194" s="61" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B194" s="61" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C194" s="62" t="s">
         <v>242</v>
@@ -8062,15 +8062,15 @@
         <v>221</v>
       </c>
       <c r="E194" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="195" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A195" s="61" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B195" s="61" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C195" s="62" t="s">
         <v>242</v>
@@ -8079,15 +8079,15 @@
         <v>221</v>
       </c>
       <c r="E195" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="196" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A196" s="61" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B196" s="61" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C196" s="62" t="s">
         <v>242</v>
@@ -8096,15 +8096,15 @@
         <v>221</v>
       </c>
       <c r="E196" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="197" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A197" s="61" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B197" s="61" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C197" s="62" t="s">
         <v>242</v>
@@ -8113,32 +8113,32 @@
         <v>221</v>
       </c>
       <c r="E197" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="198" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A198" s="61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B198" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="C198" s="62" t="s">
         <v>611</v>
-      </c>
-      <c r="C198" s="62" t="s">
-        <v>612</v>
       </c>
       <c r="D198" s="74" t="s">
         <v>221</v>
       </c>
       <c r="E198" s="64" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="199" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A199" s="61" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B199" s="61" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C199" s="62" t="s">
         <v>235</v>
@@ -8147,7 +8147,7 @@
         <v>221</v>
       </c>
       <c r="E199" s="64" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="200" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -8166,7 +8166,7 @@
     </row>
     <row r="202" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="119" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B202" s="119"/>
       <c r="C202" s="119"/>
@@ -8323,7 +8323,7 @@
         <v>65</v>
       </c>
       <c r="E211" s="43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -8516,7 +8516,7 @@
         <v>65</v>
       </c>
       <c r="E224" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -8598,10 +8598,10 @@
     </row>
     <row r="230" spans="1:5" s="80" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A230" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B230" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B230" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C230" s="11" t="s">
         <v>242</v>
@@ -8610,7 +8610,7 @@
         <v>243</v>
       </c>
       <c r="E230" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -8641,7 +8641,7 @@
     </row>
     <row r="233" spans="1:5" ht="66" x14ac:dyDescent="0.2">
       <c r="A233" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>72</v>
@@ -8687,12 +8687,12 @@
         <v>65</v>
       </c>
       <c r="E235" s="13" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A236" s="118" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B236" s="118"/>
       <c r="C236" s="118"/>
@@ -8718,10 +8718,10 @@
     </row>
     <row r="238" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A238" s="61" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B238" s="61" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C238" s="62" t="s">
         <v>228</v>
@@ -8730,185 +8730,185 @@
         <v>221</v>
       </c>
       <c r="E238" s="64" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A239" s="61" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B239" s="61" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C239" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D239" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E239" s="64" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A240" s="61" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B240" s="61" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C240" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D240" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E240" s="64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="241" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A241" s="61" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B241" s="61" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C241" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D241" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E241" s="64" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="242" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A242" s="61" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B242" s="61" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C242" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D242" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E242" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="243" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A243" s="61" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B243" s="61" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C243" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D243" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E243" s="64" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="244" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A244" s="61" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B244" s="61" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C244" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D244" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E244" s="64" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="245" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A245" s="61" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B245" s="61" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C245" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D245" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E245" s="64" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="246" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A246" s="61" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B246" s="61" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C246" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D246" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E246" s="64" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A247" s="61" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B247" s="61" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C247" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D247" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E247" s="64" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="248" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A248" s="61" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B248" s="61" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C248" s="62" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D248" s="63" t="s">
         <v>221</v>
       </c>
       <c r="E248" s="64" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="249" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A249" s="61" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B249" s="61" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C249" s="62" t="s">
         <v>242</v>
@@ -8917,15 +8917,15 @@
         <v>221</v>
       </c>
       <c r="E249" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A250" s="61" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B250" s="61" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C250" s="62" t="s">
         <v>242</v>
@@ -8934,15 +8934,15 @@
         <v>221</v>
       </c>
       <c r="E250" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="251" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A251" s="61" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B251" s="61" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C251" s="62" t="s">
         <v>242</v>
@@ -8951,15 +8951,15 @@
         <v>221</v>
       </c>
       <c r="E251" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="252" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A252" s="61" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B252" s="61" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C252" s="62" t="s">
         <v>242</v>
@@ -8968,32 +8968,32 @@
         <v>221</v>
       </c>
       <c r="E252" s="64" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="253" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A253" s="61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B253" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="C253" s="62" t="s">
         <v>611</v>
-      </c>
-      <c r="C253" s="62" t="s">
-        <v>612</v>
       </c>
       <c r="D253" s="74" t="s">
         <v>221</v>
       </c>
       <c r="E253" s="64" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="254" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A254" s="61" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B254" s="61" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C254" s="62" t="s">
         <v>235</v>
@@ -9002,7 +9002,7 @@
         <v>221</v>
       </c>
       <c r="E254" s="64" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -9151,10 +9151,10 @@
     </row>
     <row r="6" spans="1:12" s="93" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="94" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C6" s="95" t="s">
         <v>228</v>
@@ -9163,7 +9163,7 @@
         <v>243</v>
       </c>
       <c r="E6" s="97" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="7" spans="1:12" s="76" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>242</v>
@@ -9185,7 +9185,7 @@
         <v>243</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -9207,7 +9207,7 @@
         <v>243</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -9217,10 +9217,10 @@
     </row>
     <row r="9" spans="1:12" ht="33" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>235</v>
@@ -9229,7 +9229,7 @@
         <v>243</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -9316,12 +9316,12 @@
         <v>293</v>
       </c>
       <c r="F13" s="124" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G13" s="125"/>
       <c r="H13" s="125"/>
       <c r="I13" s="126" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J13" s="126"/>
       <c r="K13" s="126"/>
@@ -9461,7 +9461,7 @@
         <v>221</v>
       </c>
       <c r="E19" s="79" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="F19" s="125"/>
       <c r="G19" s="125"/>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B20" s="122"/>
       <c r="C20" s="122"/>
@@ -9502,7 +9502,7 @@
         <v>317</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>228</v>
@@ -9511,15 +9511,15 @@
         <v>221</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="75" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>561</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>562</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>242</v>
@@ -9528,7 +9528,7 @@
         <v>221</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9545,7 +9545,7 @@
         <v>221</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9938,7 +9938,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B47" s="9">
         <v>9</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B48" s="9">
         <v>10</v>
@@ -10095,10 +10095,10 @@
     </row>
     <row r="56" spans="1:8" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A56" s="61" t="s">
+        <v>469</v>
+      </c>
+      <c r="B56" s="61" t="s">
         <v>470</v>
-      </c>
-      <c r="B56" s="61" t="s">
-        <v>471</v>
       </c>
       <c r="C56" s="62" t="s">
         <v>57</v>
@@ -10148,7 +10148,7 @@
     <row r="60" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="61" spans="1:8" s="82" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="117" t="s">
-        <v>670</v>
+        <v>748</v>
       </c>
       <c r="B61" s="99"/>
       <c r="C61" s="99"/>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="63" spans="1:8" s="82" customFormat="1" ht="49.5" x14ac:dyDescent="0.2">
       <c r="A63" s="85" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B63" s="85" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C63" s="83" t="s">
         <v>242</v>
@@ -10186,7 +10186,7 @@
         <v>221</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="64" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -10210,7 +10210,7 @@
     <row r="66" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="67" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="117" t="s">
-        <v>436</v>
+        <v>749</v>
       </c>
       <c r="B67" s="99"/>
       <c r="C67" s="99"/>
@@ -10458,7 +10458,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="119" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B1" s="120"/>
       <c r="C1" s="120"/>
@@ -10535,10 +10535,10 @@
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B6" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B6" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C6" s="83" t="s">
         <v>228</v>
@@ -10547,7 +10547,7 @@
         <v>221</v>
       </c>
       <c r="E6" s="86" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -10564,7 +10564,7 @@
         <v>47</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -10581,7 +10581,7 @@
         <v>65</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -10589,7 +10589,7 @@
         <v>118</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>68</v>
@@ -10598,7 +10598,7 @@
         <v>65</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -10675,7 +10675,7 @@
         <v>65</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -10778,7 +10778,7 @@
         <v>135</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C22" s="47" t="s">
         <v>242</v>
@@ -10787,7 +10787,7 @@
         <v>65</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -10809,10 +10809,10 @@
     </row>
     <row r="24" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>242</v>
@@ -10821,7 +10821,7 @@
         <v>243</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -10881,7 +10881,7 @@
         <v>65</v>
       </c>
       <c r="E28" s="72" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -11028,7 +11028,7 @@
     </row>
     <row r="41" spans="1:5" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="119" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B41" s="120"/>
       <c r="C41" s="120"/>
@@ -11105,10 +11105,10 @@
     </row>
     <row r="46" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A46" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B46" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B46" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C46" s="83" t="s">
         <v>228</v>
@@ -11117,7 +11117,7 @@
         <v>221</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -11134,7 +11134,7 @@
         <v>47</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -11151,7 +11151,7 @@
         <v>65</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -11159,7 +11159,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>68</v>
@@ -11168,12 +11168,12 @@
         <v>65</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A50" s="118" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B50" s="118"/>
       <c r="C50" s="118"/>
@@ -11245,7 +11245,7 @@
         <v>65</v>
       </c>
       <c r="E54" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -11274,73 +11274,73 @@
     </row>
     <row r="57" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>500</v>
-      </c>
       <c r="C57" s="11" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E57" s="82"/>
     </row>
     <row r="58" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B58" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>501</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>502</v>
       </c>
       <c r="E58" s="82"/>
     </row>
     <row r="59" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>505</v>
-      </c>
       <c r="D59" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E59" s="82"/>
     </row>
     <row r="60" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>508</v>
-      </c>
       <c r="D60" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E60" s="82"/>
     </row>
     <row r="61" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="C61" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>511</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>278</v>
@@ -11349,13 +11349,13 @@
     </row>
     <row r="62" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B62" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C62" s="11" t="s">
         <v>512</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>513</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>277</v>
@@ -11364,13 +11364,13 @@
     </row>
     <row r="63" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="C63" s="11" t="s">
         <v>515</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>516</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>278</v>
@@ -11379,13 +11379,13 @@
     </row>
     <row r="64" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="C64" s="11" t="s">
         <v>518</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>519</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>277</v>
@@ -11394,13 +11394,13 @@
     </row>
     <row r="65" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>522</v>
       </c>
       <c r="D65" s="12" t="s">
         <v>277</v>
@@ -11409,13 +11409,13 @@
     </row>
     <row r="66" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C66" s="11" t="s">
         <v>523</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>524</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>277</v>
@@ -11424,13 +11424,13 @@
     </row>
     <row r="67" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="11" t="s">
         <v>526</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>527</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>277</v>
@@ -11439,13 +11439,13 @@
     </row>
     <row r="68" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C68" s="11" t="s">
         <v>529</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>530</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>278</v>
@@ -11454,13 +11454,13 @@
     </row>
     <row r="69" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="11" t="s">
         <v>532</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>533</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>278</v>
@@ -11469,13 +11469,13 @@
     </row>
     <row r="70" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="C70" s="11" t="s">
         <v>534</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>535</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>277</v>
@@ -11484,13 +11484,13 @@
     </row>
     <row r="71" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="11" t="s">
         <v>537</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>538</v>
       </c>
       <c r="D71" s="12" t="s">
         <v>277</v>
@@ -11499,58 +11499,58 @@
     </row>
     <row r="72" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="C72" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="C72" s="11" t="s">
-        <v>541</v>
-      </c>
       <c r="D72" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E72" s="82"/>
     </row>
     <row r="73" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="C73" s="11" t="s">
-        <v>544</v>
-      </c>
       <c r="D73" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E73" s="82"/>
     </row>
     <row r="74" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B74" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="C74" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>546</v>
-      </c>
       <c r="D74" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E74" s="82"/>
     </row>
     <row r="75" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C75" s="11" t="s">
         <v>715</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>717</v>
       </c>
       <c r="D75" s="12" t="s">
         <v>278</v>
@@ -11558,28 +11558,28 @@
     </row>
     <row r="76" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="C76" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="C76" s="11" t="s">
-        <v>549</v>
-      </c>
       <c r="D76" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E76" s="82"/>
     </row>
     <row r="77" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="C77" s="11" t="s">
         <v>551</v>
-      </c>
-      <c r="C77" s="11" t="s">
-        <v>552</v>
       </c>
       <c r="D77" s="12" t="s">
         <v>278</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="78" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A78" s="118" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B78" s="118"/>
       <c r="C78" s="118"/>
@@ -11617,7 +11617,7 @@
         <v>135</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C80" s="47" t="s">
         <v>242</v>
@@ -11648,10 +11648,10 @@
     </row>
     <row r="82" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>242</v>
@@ -11660,7 +11660,7 @@
         <v>243</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11691,10 +11691,10 @@
     </row>
     <row r="85" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>242</v>
@@ -11703,32 +11703,32 @@
         <v>221</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>221</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C87" s="11" t="s">
         <v>228</v>
@@ -11737,15 +11737,15 @@
         <v>221</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>228</v>
@@ -11754,7 +11754,7 @@
         <v>221</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -11762,7 +11762,7 @@
         <v>291</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>228</v>
@@ -11771,15 +11771,15 @@
         <v>221</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>287</v>
@@ -11788,7 +11788,7 @@
         <v>221</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="91" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -11805,15 +11805,15 @@
         <v>221</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C92" s="11" t="s">
         <v>242</v>
@@ -11822,32 +11822,32 @@
         <v>221</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C93" s="11" t="s">
         <v>242</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="94" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C94" s="11" t="s">
         <v>242</v>
@@ -11856,7 +11856,7 @@
         <v>221</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="95" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -11875,7 +11875,7 @@
     </row>
     <row r="97" spans="1:5" s="82" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="119" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B97" s="120"/>
       <c r="C97" s="120"/>
@@ -11952,10 +11952,10 @@
     </row>
     <row r="102" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A102" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B102" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B102" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C102" s="83" t="s">
         <v>228</v>
@@ -11964,7 +11964,7 @@
         <v>221</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="103" spans="1:5" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
@@ -11981,7 +11981,7 @@
         <v>47</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="104" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -11998,7 +11998,7 @@
         <v>65</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="105" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -12006,7 +12006,7 @@
         <v>118</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C105" s="11" t="s">
         <v>68</v>
@@ -12015,12 +12015,12 @@
         <v>65</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="106" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A106" s="118" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B106" s="118"/>
       <c r="C106" s="118"/>
@@ -12092,7 +12092,7 @@
         <v>65</v>
       </c>
       <c r="E110" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="111" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -12121,69 +12121,69 @@
     </row>
     <row r="113" spans="1:4" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="B113" s="5" t="s">
-        <v>500</v>
-      </c>
       <c r="C113" s="11" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="114" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B114" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="D114" s="12" t="s">
         <v>501</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>554</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="115" spans="1:4" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="B115" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="C115" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="C115" s="11" t="s">
-        <v>505</v>
-      </c>
       <c r="D115" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="116" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="C116" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>508</v>
-      </c>
       <c r="D116" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="117" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="B117" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="C117" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>511</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>278</v>
@@ -12191,13 +12191,13 @@
     </row>
     <row r="118" spans="1:4" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B118" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="C118" s="11" t="s">
         <v>512</v>
-      </c>
-      <c r="C118" s="11" t="s">
-        <v>513</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>277</v>
@@ -12205,13 +12205,13 @@
     </row>
     <row r="119" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="B119" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="C119" s="11" t="s">
         <v>515</v>
-      </c>
-      <c r="C119" s="11" t="s">
-        <v>516</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>278</v>
@@ -12219,13 +12219,13 @@
     </row>
     <row r="120" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B120" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="C120" s="11" t="s">
         <v>518</v>
-      </c>
-      <c r="C120" s="11" t="s">
-        <v>519</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>277</v>
@@ -12233,13 +12233,13 @@
     </row>
     <row r="121" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B121" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="C121" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="C121" s="11" t="s">
-        <v>522</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>277</v>
@@ -12247,13 +12247,13 @@
     </row>
     <row r="122" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B122" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C122" s="11" t="s">
         <v>523</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>524</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>277</v>
@@ -12261,13 +12261,13 @@
     </row>
     <row r="123" spans="1:4" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="C123" s="11" t="s">
         <v>526</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>527</v>
       </c>
       <c r="D123" s="12" t="s">
         <v>277</v>
@@ -12275,13 +12275,13 @@
     </row>
     <row r="124" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="B124" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="C124" s="11" t="s">
         <v>529</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>530</v>
       </c>
       <c r="D124" s="12" t="s">
         <v>278</v>
@@ -12289,13 +12289,13 @@
     </row>
     <row r="125" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="B125" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="C125" s="11" t="s">
         <v>532</v>
-      </c>
-      <c r="C125" s="11" t="s">
-        <v>533</v>
       </c>
       <c r="D125" s="12" t="s">
         <v>278</v>
@@ -12303,13 +12303,13 @@
     </row>
     <row r="126" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B126" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="C126" s="11" t="s">
         <v>534</v>
-      </c>
-      <c r="C126" s="11" t="s">
-        <v>535</v>
       </c>
       <c r="D126" s="12" t="s">
         <v>277</v>
@@ -12317,13 +12317,13 @@
     </row>
     <row r="127" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="B127" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="C127" s="11" t="s">
         <v>537</v>
-      </c>
-      <c r="C127" s="11" t="s">
-        <v>538</v>
       </c>
       <c r="D127" s="12" t="s">
         <v>277</v>
@@ -12331,55 +12331,55 @@
     </row>
     <row r="128" spans="1:4" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B128" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="C128" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="C128" s="11" t="s">
-        <v>541</v>
-      </c>
       <c r="D128" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="129" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="B129" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="C129" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="C129" s="11" t="s">
-        <v>544</v>
-      </c>
       <c r="D129" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="130" spans="1:5" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="C130" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="C130" s="11" t="s">
-        <v>546</v>
-      </c>
       <c r="D130" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="131" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C131" s="11" t="s">
         <v>715</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>717</v>
       </c>
       <c r="D131" s="12" t="s">
         <v>278</v>
@@ -12387,27 +12387,27 @@
     </row>
     <row r="132" spans="1:5" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B132" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="C132" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="C132" s="11" t="s">
-        <v>549</v>
-      </c>
       <c r="D132" s="12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="133" spans="1:5" s="82" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="B133" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="C133" s="11" t="s">
         <v>551</v>
-      </c>
-      <c r="C133" s="11" t="s">
-        <v>552</v>
       </c>
       <c r="D133" s="12" t="s">
         <v>278</v>
@@ -12415,7 +12415,7 @@
     </row>
     <row r="134" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A134" s="118" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B134" s="118"/>
       <c r="C134" s="118"/>
@@ -12444,7 +12444,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C136" s="47" t="s">
         <v>242</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="138" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C138" s="11" t="s">
         <v>242</v>
@@ -12487,7 +12487,7 @@
         <v>243</v>
       </c>
       <c r="E138" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="139" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -12518,10 +12518,10 @@
     </row>
     <row r="141" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>242</v>
@@ -12530,32 +12530,32 @@
         <v>221</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="142" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D142" s="12" t="s">
         <v>221</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="143" spans="1:5" s="84" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C143" s="11" t="s">
         <v>228</v>
@@ -12564,15 +12564,15 @@
         <v>221</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="144" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>228</v>
@@ -12581,7 +12581,7 @@
         <v>221</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="145" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -12589,7 +12589,7 @@
         <v>291</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>228</v>
@@ -12598,15 +12598,15 @@
         <v>221</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="146" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C146" s="11" t="s">
         <v>287</v>
@@ -12615,7 +12615,7 @@
         <v>221</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="147" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -12632,15 +12632,15 @@
         <v>221</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="148" spans="1:5" s="84" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C148" s="11" t="s">
         <v>242</v>
@@ -12649,32 +12649,32 @@
         <v>221</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="149" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C149" s="11" t="s">
         <v>242</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="150" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>242</v>
@@ -12683,7 +12683,7 @@
         <v>221</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="151" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
@@ -12704,7 +12704,7 @@
     <row r="154" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="155" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="119" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B155" s="120"/>
       <c r="C155" s="120"/>
@@ -12781,10 +12781,10 @@
     </row>
     <row r="160" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A160" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B160" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B160" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C160" s="83" t="s">
         <v>228</v>
@@ -12793,7 +12793,7 @@
         <v>221</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -12810,7 +12810,7 @@
         <v>47</v>
       </c>
       <c r="E161" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -12827,7 +12827,7 @@
         <v>65</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -12835,7 +12835,7 @@
         <v>118</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>68</v>
@@ -12844,12 +12844,12 @@
         <v>65</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A164" s="118" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B164" s="118"/>
       <c r="C164" s="118"/>
@@ -12921,12 +12921,12 @@
         <v>65</v>
       </c>
       <c r="E168" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A169" s="118" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B169" s="118"/>
       <c r="C169" s="118"/>
@@ -13081,10 +13081,10 @@
     </row>
     <row r="181" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>242</v>
@@ -13093,12 +13093,12 @@
         <v>243</v>
       </c>
       <c r="E181" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="119" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B184" s="120"/>
       <c r="C184" s="120"/>
@@ -13175,10 +13175,10 @@
     </row>
     <row r="189" spans="1:5" ht="33" x14ac:dyDescent="0.2">
       <c r="A189" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B189" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B189" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C189" s="83" t="s">
         <v>228</v>
@@ -13187,7 +13187,7 @@
         <v>221</v>
       </c>
       <c r="E189" s="13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -13204,7 +13204,7 @@
         <v>47</v>
       </c>
       <c r="E190" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13221,7 +13221,7 @@
         <v>65</v>
       </c>
       <c r="E191" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13229,7 +13229,7 @@
         <v>118</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C192" s="11" t="s">
         <v>68</v>
@@ -13238,7 +13238,7 @@
         <v>65</v>
       </c>
       <c r="E192" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13303,10 +13303,10 @@
     </row>
     <row r="197" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A197" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B197" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C197" s="11" t="s">
         <v>242</v>
@@ -13315,7 +13315,7 @@
         <v>243</v>
       </c>
       <c r="E197" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13392,7 +13392,7 @@
         <v>65</v>
       </c>
       <c r="E202" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13480,7 +13480,7 @@
     </row>
     <row r="210" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="119" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B210" s="120"/>
       <c r="C210" s="120"/>
@@ -13557,10 +13557,10 @@
     </row>
     <row r="215" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A215" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B215" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B215" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C215" s="83" t="s">
         <v>228</v>
@@ -13569,7 +13569,7 @@
         <v>221</v>
       </c>
       <c r="E215" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -13586,7 +13586,7 @@
         <v>47</v>
       </c>
       <c r="E216" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13603,7 +13603,7 @@
         <v>65</v>
       </c>
       <c r="E217" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13611,7 +13611,7 @@
         <v>118</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C218" s="11" t="s">
         <v>68</v>
@@ -13620,7 +13620,7 @@
         <v>65</v>
       </c>
       <c r="E218" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13643,7 +13643,7 @@
         <v>41</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>43</v>
@@ -13697,7 +13697,7 @@
         <v>65</v>
       </c>
       <c r="E223" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -13845,10 +13845,10 @@
     </row>
     <row r="235" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A235" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B235" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B235" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C235" s="11" t="s">
         <v>242</v>
@@ -13857,7 +13857,7 @@
         <v>243</v>
       </c>
       <c r="E235" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14236,7 +14236,7 @@
     </row>
     <row r="277" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="119" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B277" s="120"/>
       <c r="C277" s="120"/>
@@ -14313,10 +14313,10 @@
     </row>
     <row r="282" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A282" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B282" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B282" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C282" s="83" t="s">
         <v>228</v>
@@ -14325,7 +14325,7 @@
         <v>221</v>
       </c>
       <c r="E282" s="86" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="283" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -14342,7 +14342,7 @@
         <v>47</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="284" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14359,7 +14359,7 @@
         <v>65</v>
       </c>
       <c r="E284" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="285" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14367,7 +14367,7 @@
         <v>118</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C285" s="11" t="s">
         <v>68</v>
@@ -14376,7 +14376,7 @@
         <v>65</v>
       </c>
       <c r="E285" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="286" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14540,7 +14540,7 @@
         <v>65</v>
       </c>
       <c r="E297" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="298" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14688,10 +14688,10 @@
     </row>
     <row r="309" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A309" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B309" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B309" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C309" s="11" t="s">
         <v>242</v>
@@ -14700,7 +14700,7 @@
         <v>243</v>
       </c>
       <c r="E309" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="310" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14760,7 +14760,7 @@
         <v>65</v>
       </c>
       <c r="E313" s="72" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="314" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14813,7 +14813,7 @@
     </row>
     <row r="318" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="119" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B318" s="120"/>
       <c r="C318" s="120"/>
@@ -14890,10 +14890,10 @@
     </row>
     <row r="323" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A323" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B323" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B323" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C323" s="83" t="s">
         <v>228</v>
@@ -14902,7 +14902,7 @@
         <v>221</v>
       </c>
       <c r="E323" s="86" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="324" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -14919,7 +14919,7 @@
         <v>47</v>
       </c>
       <c r="E324" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="325" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14936,7 +14936,7 @@
         <v>65</v>
       </c>
       <c r="E325" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="326" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -14944,7 +14944,7 @@
         <v>118</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C326" s="11" t="s">
         <v>68</v>
@@ -14953,7 +14953,7 @@
         <v>65</v>
       </c>
       <c r="E326" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="327" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15030,7 +15030,7 @@
         <v>65</v>
       </c>
       <c r="E331" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="332" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15148,10 +15148,10 @@
     </row>
     <row r="341" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A341" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B341" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C341" s="11" t="s">
         <v>242</v>
@@ -15160,7 +15160,7 @@
         <v>243</v>
       </c>
       <c r="E341" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="342" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15256,7 +15256,7 @@
     </row>
     <row r="349" spans="1:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="119" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B349" s="120"/>
       <c r="C349" s="120"/>
@@ -15333,10 +15333,10 @@
     </row>
     <row r="354" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A354" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B354" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B354" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C354" s="83" t="s">
         <v>228</v>
@@ -15345,7 +15345,7 @@
         <v>221</v>
       </c>
       <c r="E354" s="13" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="355" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -15362,7 +15362,7 @@
         <v>47</v>
       </c>
       <c r="E355" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="356" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15379,7 +15379,7 @@
         <v>65</v>
       </c>
       <c r="E356" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="357" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15387,7 +15387,7 @@
         <v>118</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C357" s="11" t="s">
         <v>68</v>
@@ -15396,7 +15396,7 @@
         <v>65</v>
       </c>
       <c r="E357" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="358" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15461,10 +15461,10 @@
     </row>
     <row r="362" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A362" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B362" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B362" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C362" s="11" t="s">
         <v>242</v>
@@ -15473,7 +15473,7 @@
         <v>243</v>
       </c>
       <c r="E362" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="363" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15550,7 +15550,7 @@
         <v>65</v>
       </c>
       <c r="E367" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="368" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15652,7 +15652,7 @@
     </row>
     <row r="377" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="119" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B377" s="120"/>
       <c r="C377" s="120"/>
@@ -15729,10 +15729,10 @@
     </row>
     <row r="382" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A382" s="85" t="s">
+        <v>588</v>
+      </c>
+      <c r="B382" s="85" t="s">
         <v>589</v>
-      </c>
-      <c r="B382" s="85" t="s">
-        <v>590</v>
       </c>
       <c r="C382" s="83" t="s">
         <v>228</v>
@@ -15741,7 +15741,7 @@
         <v>221</v>
       </c>
       <c r="E382" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="383" spans="1:5" ht="33" x14ac:dyDescent="0.2">
@@ -15758,7 +15758,7 @@
         <v>47</v>
       </c>
       <c r="E383" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="384" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15775,7 +15775,7 @@
         <v>65</v>
       </c>
       <c r="E384" s="13" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="385" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15783,7 +15783,7 @@
         <v>118</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C385" s="11" t="s">
         <v>68</v>
@@ -15792,7 +15792,7 @@
         <v>65</v>
       </c>
       <c r="E385" s="13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="386" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -15869,7 +15869,7 @@
         <v>65</v>
       </c>
       <c r="E390" s="43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="391" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -16017,10 +16017,10 @@
     </row>
     <row r="402" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A402" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="B402" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="B402" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="C402" s="11" t="s">
         <v>242</v>
@@ -16029,7 +16029,7 @@
         <v>243</v>
       </c>
       <c r="E402" s="43" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="403" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
@@ -16295,7 +16295,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="117" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B1" s="99"/>
       <c r="C1" s="99"/>
@@ -16350,7 +16350,7 @@
         <v>221</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -16367,7 +16367,7 @@
         <v>221</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
@@ -16446,7 +16446,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="117" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B12" s="99"/>
       <c r="C12" s="99"/>
@@ -16523,7 +16523,7 @@
     </row>
     <row r="19" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="117" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B19" s="99"/>
       <c r="C19" s="99"/>
@@ -16566,7 +16566,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="117" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B24" s="99"/>
       <c r="C24" s="99"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="E3" s="66"/>
       <c r="F3" s="157" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G3" s="150"/>
       <c r="H3" s="150"/>
@@ -16741,7 +16741,7 @@
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="65"/>
       <c r="B4" s="65" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C4" s="65"/>
       <c r="D4" s="65" t="s">
@@ -16749,7 +16749,7 @@
       </c>
       <c r="E4" s="66"/>
       <c r="F4" s="157" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G4" s="150"/>
       <c r="H4" s="150"/>
@@ -16763,7 +16763,7 @@
     <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="65"/>
       <c r="B5" s="65" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C5" s="65"/>
       <c r="D5" s="65" t="s">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="E5" s="66"/>
       <c r="F5" s="157" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G5" s="150"/>
       <c r="H5" s="150"/>
@@ -16785,7 +16785,7 @@
     <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="65"/>
       <c r="B6" s="65" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C6" s="65"/>
       <c r="D6" s="65" t="s">
@@ -16793,7 +16793,7 @@
       </c>
       <c r="E6" s="66"/>
       <c r="F6" s="157" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G6" s="150"/>
       <c r="H6" s="150"/>
@@ -16807,7 +16807,7 @@
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="65"/>
       <c r="B7" s="65" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C7" s="65"/>
       <c r="D7" s="65" t="s">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="E7" s="66"/>
       <c r="F7" s="157" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G7" s="150"/>
       <c r="H7" s="150"/>
@@ -16829,7 +16829,7 @@
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="65"/>
       <c r="B8" s="65" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C8" s="65"/>
       <c r="D8" s="65" t="s">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="E8" s="66"/>
       <c r="F8" s="157" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G8" s="150"/>
       <c r="H8" s="150"/>
@@ -16851,7 +16851,7 @@
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="65"/>
       <c r="B9" s="65" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C9" s="65"/>
       <c r="D9" s="65" t="s">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="E9" s="66"/>
       <c r="F9" s="157" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G9" s="150"/>
       <c r="H9" s="150"/>
@@ -16873,15 +16873,15 @@
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="65"/>
       <c r="B10" s="65" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C10" s="65"/>
       <c r="D10" s="65" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E10" s="66"/>
       <c r="F10" s="157" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G10" s="150"/>
       <c r="H10" s="150"/>
@@ -16895,7 +16895,7 @@
     <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="65"/>
       <c r="B11" s="65" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="65" t="s">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="E11" s="66"/>
       <c r="F11" s="157" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G11" s="150"/>
       <c r="H11" s="150"/>
@@ -16921,11 +16921,11 @@
       </c>
       <c r="C12" s="65"/>
       <c r="D12" s="65" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E12" s="66"/>
       <c r="F12" s="158" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G12" s="153"/>
       <c r="H12" s="153"/>
@@ -16943,11 +16943,11 @@
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="69" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E13" s="66"/>
       <c r="F13" s="157" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G13" s="150"/>
       <c r="H13" s="150"/>
@@ -16965,11 +16965,11 @@
       </c>
       <c r="C14" s="65"/>
       <c r="D14" s="65" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E14" s="66"/>
       <c r="F14" s="157" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G14" s="150"/>
       <c r="H14" s="150"/>
@@ -16987,11 +16987,11 @@
       </c>
       <c r="C15" s="65"/>
       <c r="D15" s="65" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E15" s="66"/>
       <c r="F15" s="157" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G15" s="150"/>
       <c r="H15" s="150"/>
@@ -17009,11 +17009,11 @@
       </c>
       <c r="C16" s="65"/>
       <c r="D16" s="65" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E16" s="66"/>
       <c r="F16" s="157" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G16" s="150"/>
       <c r="H16" s="150"/>
@@ -17031,11 +17031,11 @@
       </c>
       <c r="C17" s="65"/>
       <c r="D17" s="65" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E17" s="66"/>
       <c r="F17" s="157" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G17" s="150"/>
       <c r="H17" s="150"/>
@@ -17053,11 +17053,11 @@
       </c>
       <c r="C18" s="65"/>
       <c r="D18" s="65" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E18" s="66"/>
       <c r="F18" s="157" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G18" s="150"/>
       <c r="H18" s="150"/>
@@ -17075,11 +17075,11 @@
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="65" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E19" s="66"/>
       <c r="F19" s="157" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G19" s="150"/>
       <c r="H19" s="150"/>
@@ -17126,7 +17126,7 @@
     </row>
     <row r="22" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="159" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B22" s="160"/>
       <c r="C22" s="160"/>
@@ -17144,7 +17144,7 @@
     </row>
     <row r="23" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="155" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B23" s="156"/>
       <c r="C23" s="156"/>
@@ -17177,7 +17177,7 @@
         <v>423</v>
       </c>
       <c r="F24" s="149" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G24" s="150"/>
       <c r="H24" s="150"/>
@@ -17195,11 +17195,11 @@
       </c>
       <c r="C25" s="65"/>
       <c r="D25" s="69" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E25" s="66"/>
       <c r="F25" s="149" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G25" s="150"/>
       <c r="H25" s="150"/>
@@ -17217,11 +17217,11 @@
       </c>
       <c r="C26" s="65"/>
       <c r="D26" s="69" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E26" s="66"/>
       <c r="F26" s="149" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G26" s="150"/>
       <c r="H26" s="150"/>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="E27" s="66"/>
       <c r="F27" s="149" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G27" s="150"/>
       <c r="H27" s="150"/>
@@ -17261,11 +17261,11 @@
       </c>
       <c r="C28" s="65"/>
       <c r="D28" s="69" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E28" s="66"/>
       <c r="F28" s="149" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G28" s="150"/>
       <c r="H28" s="150"/>
@@ -17279,15 +17279,15 @@
     <row r="29" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="65"/>
       <c r="B29" s="69" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C29" s="65"/>
       <c r="D29" s="69" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E29" s="66"/>
       <c r="F29" s="149" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G29" s="150"/>
       <c r="H29" s="150"/>
@@ -17301,7 +17301,7 @@
     <row r="30" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="65"/>
       <c r="B30" s="69" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C30" s="65"/>
       <c r="D30" s="69" t="s">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="E30" s="66"/>
       <c r="F30" s="149" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G30" s="150"/>
       <c r="H30" s="150"/>
@@ -17323,7 +17323,7 @@
     <row r="31" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="65"/>
       <c r="B31" s="69" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C31" s="65"/>
       <c r="D31" s="69" t="s">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="E31" s="66"/>
       <c r="F31" s="149" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G31" s="150"/>
       <c r="H31" s="150"/>
@@ -17345,7 +17345,7 @@
     <row r="32" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="65"/>
       <c r="B32" s="69" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C32" s="65"/>
       <c r="D32" s="69" t="s">
@@ -17353,7 +17353,7 @@
       </c>
       <c r="E32" s="66"/>
       <c r="F32" s="149" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G32" s="150"/>
       <c r="H32" s="150"/>
@@ -17367,7 +17367,7 @@
     <row r="33" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="65"/>
       <c r="B33" s="69" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C33" s="65"/>
       <c r="D33" s="69" t="s">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="E33" s="66"/>
       <c r="F33" s="149" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G33" s="150"/>
       <c r="H33" s="150"/>
@@ -17420,7 +17420,7 @@
     </row>
     <row r="36" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="137" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B36" s="138"/>
       <c r="C36" s="138"/>
@@ -17439,7 +17439,7 @@
     <row r="116" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="117" spans="4:16" x14ac:dyDescent="0.2">
       <c r="D117" s="140" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E117" s="141"/>
       <c r="F117" s="141"/>

--- a/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
+++ b/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LinWenTao\Desktop\Outbound_station\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2832D7-E0D7-4907-8911-75B0BE4F3863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464383F3-D059-4B33-9899-964BB28414AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3533,20 +3533,17 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3560,25 +3557,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3588,10 +3588,25 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3609,22 +3624,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3639,9 +3642,37 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3678,40 +3709,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4259,50 +4259,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
     </row>
     <row r="2" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
     </row>
     <row r="4" spans="1:8" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="108" t="s">
+      <c r="A4" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
       <c r="G4" s="21" t="s">
         <v>711</v>
       </c>
@@ -4311,14 +4311,14 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
+      <c r="A5" s="99" t="s">
         <v>409</v>
       </c>
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
       <c r="G5" s="21" t="s">
         <v>710</v>
       </c>
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="49" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="99" t="s">
         <v>712</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
@@ -4349,26 +4349,26 @@
       <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="20"/>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="105"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="104"/>
       <c r="G9" s="22"/>
       <c r="H9" s="20"/>
     </row>
@@ -4383,10 +4383,10 @@
       <c r="D10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="104" t="s">
+      <c r="E10" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="105"/>
+      <c r="F10" s="104"/>
       <c r="G10" s="22"/>
       <c r="H10" s="20"/>
     </row>
@@ -4401,10 +4401,10 @@
       <c r="D11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="106" t="s">
+      <c r="E11" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="101"/>
+      <c r="F11" s="106"/>
       <c r="G11" s="22"/>
       <c r="H11" s="20"/>
     </row>
@@ -4419,10 +4419,10 @@
       <c r="D12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="106" t="s">
+      <c r="E12" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="101"/>
+      <c r="F12" s="106"/>
       <c r="G12" s="22"/>
       <c r="H12" s="20"/>
     </row>
@@ -4435,10 +4435,10 @@
       <c r="D13" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="106" t="s">
+      <c r="E13" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="101"/>
+      <c r="F13" s="106"/>
       <c r="G13" s="22"/>
       <c r="H13" s="20"/>
     </row>
@@ -4451,10 +4451,10 @@
       <c r="D14" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="100" t="s">
+      <c r="E14" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="101"/>
+      <c r="F14" s="106"/>
       <c r="G14" s="22"/>
       <c r="H14" s="20"/>
     </row>
@@ -4467,10 +4467,10 @@
       <c r="D15" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="100" t="s">
+      <c r="E15" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="101"/>
+      <c r="F15" s="106"/>
       <c r="G15" s="22"/>
       <c r="H15" s="20"/>
     </row>
@@ -4483,10 +4483,10 @@
       <c r="D16" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="100" t="s">
+      <c r="E16" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="101"/>
+      <c r="F16" s="106"/>
       <c r="G16" s="22"/>
       <c r="H16" s="20"/>
     </row>
@@ -4501,15 +4501,15 @@
       <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="102" t="s">
+      <c r="A18" s="109" t="s">
         <v>418</v>
       </c>
-      <c r="B18" s="102"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="102"/>
+      <c r="B18" s="109"/>
+      <c r="C18" s="109"/>
+      <c r="D18" s="109"/>
+      <c r="E18" s="109"/>
+      <c r="F18" s="109"/>
+      <c r="G18" s="109"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -4533,11 +4533,11 @@
       <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="98"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
+      <c r="A21" s="107"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="29"/>
@@ -4613,11 +4613,11 @@
       <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="98"/>
-      <c r="B29" s="98"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="98"/>
-      <c r="E29" s="98"/>
+      <c r="A29" s="107"/>
+      <c r="B29" s="107"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="107"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
@@ -4733,17 +4733,29 @@
       <c r="H40" s="20"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="99"/>
-      <c r="B41" s="99"/>
-      <c r="C41" s="99"/>
-      <c r="D41" s="99"/>
-      <c r="E41" s="99"/>
-      <c r="F41" s="99"/>
-      <c r="G41" s="99"/>
-      <c r="H41" s="99"/>
+      <c r="A41" s="100"/>
+      <c r="B41" s="100"/>
+      <c r="C41" s="100"/>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:H3"/>
@@ -4751,18 +4763,6 @@
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4780,13 +4780,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="110" t="s">
         <v>672</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -4795,11 +4795,11 @@
       <c r="B2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
@@ -4808,11 +4808,11 @@
       <c r="B3" s="19">
         <v>11000</v>
       </c>
-      <c r="C3" s="113" t="s">
+      <c r="C3" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="113"/>
-      <c r="E3" s="113"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
@@ -4821,11 +4821,11 @@
       <c r="B4" s="19">
         <v>11001</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
@@ -4834,11 +4834,11 @@
       <c r="B5" s="19">
         <v>11002</v>
       </c>
-      <c r="C5" s="113" t="s">
+      <c r="C5" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
     </row>
     <row r="6" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
@@ -4847,11 +4847,11 @@
       <c r="B6" s="19">
         <v>11003</v>
       </c>
-      <c r="C6" s="110" t="s">
+      <c r="C6" s="113" t="s">
         <v>665</v>
       </c>
-      <c r="D6" s="112"/>
-      <c r="E6" s="112"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
@@ -4860,11 +4860,11 @@
       <c r="B7" s="19">
         <v>11004</v>
       </c>
-      <c r="C7" s="113" t="s">
+      <c r="C7" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="113"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
@@ -4873,11 +4873,11 @@
       <c r="B8" s="19">
         <v>11005</v>
       </c>
-      <c r="C8" s="113" t="s">
+      <c r="C8" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="113"/>
-      <c r="E8" s="113"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
@@ -4886,11 +4886,11 @@
       <c r="B9" s="19">
         <v>11006</v>
       </c>
-      <c r="C9" s="113" t="s">
+      <c r="C9" s="112" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="113"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
@@ -4899,18 +4899,18 @@
       <c r="B10" s="19">
         <v>11007</v>
       </c>
-      <c r="C10" s="110" t="s">
+      <c r="C10" s="113" t="s">
         <v>666</v>
       </c>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="19"/>
       <c r="B11" s="19"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="111"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="116" t="s">
@@ -4932,8 +4932,8 @@
       <c r="C15" s="117" t="s">
         <v>667</v>
       </c>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
     </row>
     <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -4946,17 +4946,17 @@
       <c r="C16" s="117" t="s">
         <v>668</v>
       </c>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="114" t="s">
+      <c r="A19" s="110" t="s">
         <v>673</v>
       </c>
-      <c r="B19" s="115"/>
-      <c r="C19" s="115"/>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
@@ -4965,11 +4965,11 @@
       <c r="B20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="99" t="s">
+      <c r="C20" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
@@ -4978,11 +4978,11 @@
       <c r="B21" s="19">
         <v>12000</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C21" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
+      <c r="D21" s="112"/>
+      <c r="E21" s="112"/>
     </row>
     <row r="22" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
@@ -4991,41 +4991,41 @@
       <c r="B22" s="19">
         <v>12001</v>
       </c>
-      <c r="C22" s="113" t="s">
+      <c r="C22" s="112" t="s">
         <v>671</v>
       </c>
-      <c r="D22" s="113"/>
-      <c r="E22" s="113"/>
+      <c r="D22" s="112"/>
+      <c r="E22" s="112"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
       <c r="B23" s="19"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
       <c r="B24" s="19"/>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
+      <c r="C24" s="115"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="115"/>
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
       <c r="B25" s="19"/>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
+      <c r="C25" s="115"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="115"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="114" t="s">
+      <c r="A26" s="110" t="s">
         <v>687</v>
       </c>
-      <c r="B26" s="115"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="115"/>
-      <c r="E26" s="115"/>
+      <c r="B26" s="111"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
@@ -5034,11 +5034,11 @@
       <c r="B27" s="19">
         <v>13000</v>
       </c>
-      <c r="C27" s="110" t="s">
+      <c r="C27" s="113" t="s">
         <v>690</v>
       </c>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="19">
@@ -5047,11 +5047,11 @@
       <c r="B28" s="19">
         <v>13001</v>
       </c>
-      <c r="C28" s="110" t="s">
+      <c r="C28" s="113" t="s">
         <v>691</v>
       </c>
-      <c r="D28" s="111"/>
-      <c r="E28" s="111"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19">
@@ -5060,11 +5060,11 @@
       <c r="B29" s="19">
         <v>13002</v>
       </c>
-      <c r="C29" s="110" t="s">
+      <c r="C29" s="113" t="s">
         <v>692</v>
       </c>
-      <c r="D29" s="111"/>
-      <c r="E29" s="111"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="19">
@@ -5073,11 +5073,11 @@
       <c r="B30" s="19">
         <v>13003</v>
       </c>
-      <c r="C30" s="110" t="s">
+      <c r="C30" s="113" t="s">
         <v>693</v>
       </c>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
+      <c r="D30" s="113"/>
+      <c r="E30" s="113"/>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19">
@@ -5086,11 +5086,11 @@
       <c r="B31" s="19">
         <v>13004</v>
       </c>
-      <c r="C31" s="110" t="s">
+      <c r="C31" s="113" t="s">
         <v>699</v>
       </c>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="113"/>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
@@ -5099,11 +5099,11 @@
       <c r="B32" s="19">
         <v>13005</v>
       </c>
-      <c r="C32" s="110" t="s">
+      <c r="C32" s="113" t="s">
         <v>701</v>
       </c>
-      <c r="D32" s="110"/>
-      <c r="E32" s="110"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19">
@@ -5112,11 +5112,11 @@
       <c r="B33" s="19">
         <v>13006</v>
       </c>
-      <c r="C33" s="110" t="s">
+      <c r="C33" s="113" t="s">
         <v>703</v>
       </c>
-      <c r="D33" s="110"/>
-      <c r="E33" s="110"/>
+      <c r="D33" s="113"/>
+      <c r="E33" s="113"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="19">
@@ -5125,11 +5125,11 @@
       <c r="B34" s="19">
         <v>13007</v>
       </c>
-      <c r="C34" s="110" t="s">
+      <c r="C34" s="113" t="s">
         <v>704</v>
       </c>
-      <c r="D34" s="110"/>
-      <c r="E34" s="110"/>
+      <c r="D34" s="113"/>
+      <c r="E34" s="113"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
@@ -5138,11 +5138,11 @@
       <c r="B35" s="19">
         <v>13008</v>
       </c>
-      <c r="C35" s="110" t="s">
+      <c r="C35" s="113" t="s">
         <v>706</v>
       </c>
-      <c r="D35" s="110"/>
-      <c r="E35" s="110"/>
+      <c r="D35" s="113"/>
+      <c r="E35" s="113"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
@@ -5151,11 +5151,11 @@
       <c r="B36" s="19">
         <v>13009</v>
       </c>
-      <c r="C36" s="110" t="s">
+      <c r="C36" s="113" t="s">
         <v>709</v>
       </c>
-      <c r="D36" s="110"/>
-      <c r="E36" s="110"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
@@ -5164,9 +5164,9 @@
       <c r="B37" s="19">
         <v>13010</v>
       </c>
-      <c r="C37" s="111"/>
-      <c r="D37" s="111"/>
-      <c r="E37" s="111"/>
+      <c r="C37" s="115"/>
+      <c r="D37" s="115"/>
+      <c r="E37" s="115"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
@@ -5175,9 +5175,9 @@
       <c r="B38" s="19">
         <v>13011</v>
       </c>
-      <c r="C38" s="111"/>
-      <c r="D38" s="111"/>
-      <c r="E38" s="111"/>
+      <c r="C38" s="115"/>
+      <c r="D38" s="115"/>
+      <c r="E38" s="115"/>
     </row>
     <row r="39" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
@@ -5208,13 +5208,13 @@
       <c r="E42" s="81"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="114" t="s">
+      <c r="A43" s="110" t="s">
         <v>688</v>
       </c>
-      <c r="B43" s="115"/>
-      <c r="C43" s="115"/>
-      <c r="D43" s="115"/>
-      <c r="E43" s="115"/>
+      <c r="B43" s="111"/>
+      <c r="C43" s="111"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="111"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="18" t="s">
@@ -5223,11 +5223,11 @@
       <c r="B44" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="99" t="s">
+      <c r="C44" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="99"/>
-      <c r="E44" s="99"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="100"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="19">
@@ -5236,11 +5236,11 @@
       <c r="B45" s="19">
         <v>14000</v>
       </c>
-      <c r="C45" s="111" t="s">
+      <c r="C45" s="115" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="111"/>
-      <c r="E45" s="111"/>
+      <c r="D45" s="115"/>
+      <c r="E45" s="115"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="19">
@@ -5249,11 +5249,11 @@
       <c r="B46" s="19">
         <v>14001</v>
       </c>
-      <c r="C46" s="110" t="s">
+      <c r="C46" s="113" t="s">
         <v>689</v>
       </c>
-      <c r="D46" s="111"/>
-      <c r="E46" s="111"/>
+      <c r="D46" s="115"/>
+      <c r="E46" s="115"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="19"/>
@@ -5277,6 +5277,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="A43:E43"/>
@@ -5293,28 +5315,6 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C45:E45"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5335,16 +5335,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -5501,16 +5501,16 @@
     </row>
     <row r="11" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="102" t="s">
+      <c r="A13" s="109" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="99"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
-      <c r="H13" s="99"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -5675,13 +5675,13 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="120"/>
-      <c r="C26" s="120"/>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -5829,16 +5829,16 @@
       <c r="E36" s="17"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="99" t="s">
+      <c r="A37" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="99"/>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
+      <c r="B37" s="100"/>
+      <c r="C37" s="100"/>
+      <c r="D37" s="100"/>
+      <c r="E37" s="100"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="100"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -5908,13 +5908,13 @@
       <c r="A48" s="117" t="s">
         <v>659</v>
       </c>
-      <c r="B48" s="99"/>
-      <c r="C48" s="99"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="99"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
+      <c r="B48" s="100"/>
+      <c r="C48" s="100"/>
+      <c r="D48" s="100"/>
+      <c r="E48" s="100"/>
+      <c r="F48" s="100"/>
+      <c r="G48" s="100"/>
+      <c r="H48" s="100"/>
     </row>
     <row r="49" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
@@ -6305,13 +6305,13 @@
       <c r="A74" s="117" t="s">
         <v>660</v>
       </c>
-      <c r="B74" s="99"/>
-      <c r="C74" s="99"/>
-      <c r="D74" s="99"/>
-      <c r="E74" s="99"/>
-      <c r="F74" s="99"/>
-      <c r="G74" s="99"/>
-      <c r="H74" s="99"/>
+      <c r="B74" s="100"/>
+      <c r="C74" s="100"/>
+      <c r="D74" s="100"/>
+      <c r="E74" s="100"/>
+      <c r="F74" s="100"/>
+      <c r="G74" s="100"/>
+      <c r="H74" s="100"/>
     </row>
     <row r="75" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
@@ -6471,13 +6471,13 @@
       <c r="A86" s="117" t="s">
         <v>661</v>
       </c>
-      <c r="B86" s="99"/>
-      <c r="C86" s="99"/>
-      <c r="D86" s="99"/>
-      <c r="E86" s="99"/>
-      <c r="F86" s="99"/>
-      <c r="G86" s="99"/>
-      <c r="H86" s="99"/>
+      <c r="B86" s="100"/>
+      <c r="C86" s="100"/>
+      <c r="D86" s="100"/>
+      <c r="E86" s="100"/>
+      <c r="F86" s="100"/>
+      <c r="G86" s="100"/>
+      <c r="H86" s="100"/>
     </row>
     <row r="87" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
@@ -6642,13 +6642,13 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="119" t="s">
+      <c r="A99" s="120" t="s">
         <v>662</v>
       </c>
-      <c r="B99" s="120"/>
-      <c r="C99" s="120"/>
-      <c r="D99" s="120"/>
-      <c r="E99" s="120"/>
+      <c r="B99" s="119"/>
+      <c r="C99" s="119"/>
+      <c r="D99" s="119"/>
+      <c r="E99" s="119"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -6873,13 +6873,13 @@
       <c r="A120" s="117" t="s">
         <v>663</v>
       </c>
-      <c r="B120" s="99"/>
-      <c r="C120" s="99"/>
-      <c r="D120" s="99"/>
-      <c r="E120" s="99"/>
-      <c r="F120" s="99"/>
-      <c r="G120" s="99"/>
-      <c r="H120" s="99"/>
+      <c r="B120" s="100"/>
+      <c r="C120" s="100"/>
+      <c r="D120" s="100"/>
+      <c r="E120" s="100"/>
+      <c r="F120" s="100"/>
+      <c r="G120" s="100"/>
+      <c r="H120" s="100"/>
     </row>
     <row r="121" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
@@ -7270,13 +7270,13 @@
       <c r="A146" s="117" t="s">
         <v>583</v>
       </c>
-      <c r="B146" s="99"/>
-      <c r="C146" s="99"/>
-      <c r="D146" s="99"/>
-      <c r="E146" s="99"/>
-      <c r="F146" s="99"/>
-      <c r="G146" s="99"/>
-      <c r="H146" s="99"/>
+      <c r="B146" s="100"/>
+      <c r="C146" s="100"/>
+      <c r="D146" s="100"/>
+      <c r="E146" s="100"/>
+      <c r="F146" s="100"/>
+      <c r="G146" s="100"/>
+      <c r="H146" s="100"/>
     </row>
     <row r="147" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
@@ -8165,13 +8165,13 @@
       <c r="E201" s="91"/>
     </row>
     <row r="202" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="119" t="s">
+      <c r="A202" s="120" t="s">
         <v>584</v>
       </c>
-      <c r="B202" s="119"/>
-      <c r="C202" s="119"/>
-      <c r="D202" s="119"/>
-      <c r="E202" s="119"/>
+      <c r="B202" s="120"/>
+      <c r="C202" s="120"/>
+      <c r="D202" s="120"/>
+      <c r="E202" s="120"/>
     </row>
     <row r="203" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
@@ -9007,18 +9007,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A236:E236"/>
-    <mergeCell ref="A231:E231"/>
-    <mergeCell ref="A170:E170"/>
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="A202:E202"/>
-    <mergeCell ref="A219:E219"/>
-    <mergeCell ref="A225:E225"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A120:H120"/>
@@ -9030,6 +9018,18 @@
     <mergeCell ref="A86:H86"/>
     <mergeCell ref="A92:E92"/>
     <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A236:E236"/>
+    <mergeCell ref="A231:E231"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A225:E225"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9050,16 +9050,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -9118,7 +9118,7 @@
       <c r="D4" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="13" t="s">
         <v>313</v>
       </c>
       <c r="H4" s="4"/>
@@ -9289,14 +9289,14 @@
       <c r="E12" s="78" t="s">
         <v>290</v>
       </c>
-      <c r="F12" s="127" t="s">
+      <c r="F12" s="122" t="s">
         <v>206</v>
       </c>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="127"/>
-      <c r="K12" s="127"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9315,16 +9315,16 @@
       <c r="E13" s="78" t="s">
         <v>293</v>
       </c>
-      <c r="F13" s="124" t="s">
+      <c r="F13" s="129" t="s">
         <v>565</v>
       </c>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="126" t="s">
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="121" t="s">
         <v>570</v>
       </c>
-      <c r="J13" s="126"/>
-      <c r="K13" s="126"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="121"/>
       <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9343,12 +9343,12 @@
       <c r="E14" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14" s="126"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9367,12 +9367,12 @@
       <c r="E15" s="79" t="s">
         <v>299</v>
       </c>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="126"/>
-      <c r="J15" s="126"/>
-      <c r="K15" s="126"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="121"/>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9391,12 +9391,12 @@
       <c r="E16" s="78" t="s">
         <v>211</v>
       </c>
-      <c r="F16" s="125"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="125"/>
-      <c r="I16" s="126"/>
-      <c r="J16" s="126"/>
-      <c r="K16" s="126"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="121"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="121"/>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9415,12 +9415,12 @@
       <c r="E17" s="78" t="s">
         <v>210</v>
       </c>
-      <c r="F17" s="125"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="126"/>
-      <c r="K17" s="126"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9439,12 +9439,12 @@
       <c r="E18" s="78" t="s">
         <v>306</v>
       </c>
-      <c r="F18" s="125"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="126"/>
-      <c r="J18" s="126"/>
-      <c r="K18" s="126"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="121"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" s="73" customFormat="1" ht="33" x14ac:dyDescent="0.2">
@@ -9463,22 +9463,22 @@
       <c r="E19" s="79" t="s">
         <v>559</v>
       </c>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="126"/>
-      <c r="J19" s="126"/>
-      <c r="K19" s="126"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="121"/>
+      <c r="J19" s="121"/>
+      <c r="K19" s="121"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="121" t="s">
+      <c r="A20" s="126" t="s">
         <v>566</v>
       </c>
-      <c r="B20" s="122"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="123"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="127"/>
+      <c r="E20" s="128"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
@@ -9549,13 +9549,13 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="121" t="s">
+      <c r="A25" s="126" t="s">
         <v>181</v>
       </c>
-      <c r="B25" s="122"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="123"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="128"/>
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
       <c r="H25" s="41"/>
@@ -9614,13 +9614,13 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="121" t="s">
+      <c r="A30" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="122"/>
-      <c r="C30" s="122"/>
-      <c r="D30" s="122"/>
-      <c r="E30" s="123"/>
+      <c r="B30" s="127"/>
+      <c r="C30" s="127"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="128"/>
     </row>
     <row r="31" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
@@ -9691,16 +9691,16 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="128" t="s">
+      <c r="A37" s="123" t="s">
         <v>218</v>
       </c>
-      <c r="B37" s="129"/>
-      <c r="C37" s="129"/>
-      <c r="D37" s="129"/>
-      <c r="E37" s="129"/>
-      <c r="F37" s="129"/>
-      <c r="G37" s="129"/>
-      <c r="H37" s="130"/>
+      <c r="B37" s="124"/>
+      <c r="C37" s="124"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="124"/>
+      <c r="G37" s="124"/>
+      <c r="H37" s="125"/>
     </row>
     <row r="38" spans="1:8" ht="49.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -10071,10 +10071,10 @@
       <c r="A54" s="117" t="s">
         <v>435</v>
       </c>
-      <c r="B54" s="99"/>
-      <c r="C54" s="99"/>
-      <c r="D54" s="99"/>
-      <c r="E54" s="99"/>
+      <c r="B54" s="100"/>
+      <c r="C54" s="100"/>
+      <c r="D54" s="100"/>
+      <c r="E54" s="100"/>
     </row>
     <row r="55" spans="1:8" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A55" s="59" t="s">
@@ -10150,10 +10150,10 @@
       <c r="A61" s="117" t="s">
         <v>748</v>
       </c>
-      <c r="B61" s="99"/>
-      <c r="C61" s="99"/>
-      <c r="D61" s="99"/>
-      <c r="E61" s="99"/>
+      <c r="B61" s="100"/>
+      <c r="C61" s="100"/>
+      <c r="D61" s="100"/>
+      <c r="E61" s="100"/>
     </row>
     <row r="62" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="59" t="s">
@@ -10212,10 +10212,10 @@
       <c r="A67" s="117" t="s">
         <v>749</v>
       </c>
-      <c r="B67" s="99"/>
-      <c r="C67" s="99"/>
-      <c r="D67" s="99"/>
-      <c r="E67" s="99"/>
+      <c r="B67" s="100"/>
+      <c r="C67" s="100"/>
+      <c r="D67" s="100"/>
+      <c r="E67" s="100"/>
     </row>
     <row r="68" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A68" s="59" t="s">
@@ -10293,9 +10293,9 @@
       <c r="C74" s="82"/>
       <c r="D74" s="82"/>
       <c r="E74" s="82"/>
-      <c r="F74" s="102"/>
-      <c r="G74" s="99"/>
-      <c r="H74" s="99"/>
+      <c r="F74" s="109"/>
+      <c r="G74" s="100"/>
+      <c r="H74" s="100"/>
     </row>
     <row r="75" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="82"/>
@@ -10425,6 +10425,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F13:H19"/>
     <mergeCell ref="I13:K19"/>
     <mergeCell ref="F12:K12"/>
     <mergeCell ref="F74:H74"/>
@@ -10432,12 +10438,6 @@
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F13:H19"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10457,13 +10457,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>694</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -10919,13 +10919,13 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="121" t="s">
+      <c r="A31" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="122"/>
-      <c r="C31" s="122"/>
-      <c r="D31" s="122"/>
-      <c r="E31" s="123"/>
+      <c r="B31" s="127"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="128"/>
     </row>
     <row r="32" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
@@ -11027,13 +11027,13 @@
       <c r="E40" s="82"/>
     </row>
     <row r="41" spans="1:5" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="119" t="s">
+      <c r="A41" s="120" t="s">
         <v>695</v>
       </c>
-      <c r="B41" s="120"/>
-      <c r="C41" s="120"/>
-      <c r="D41" s="120"/>
-      <c r="E41" s="120"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="119"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="119"/>
     </row>
     <row r="42" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
@@ -11874,13 +11874,13 @@
       <c r="E96" s="43"/>
     </row>
     <row r="97" spans="1:5" s="82" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="119" t="s">
+      <c r="A97" s="120" t="s">
         <v>696</v>
       </c>
-      <c r="B97" s="120"/>
-      <c r="C97" s="120"/>
-      <c r="D97" s="120"/>
-      <c r="E97" s="120"/>
+      <c r="B97" s="119"/>
+      <c r="C97" s="119"/>
+      <c r="D97" s="119"/>
+      <c r="E97" s="119"/>
     </row>
     <row r="98" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
@@ -12703,13 +12703,13 @@
     <row r="153" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="154" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="155" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="119" t="s">
+      <c r="A155" s="120" t="s">
         <v>697</v>
       </c>
-      <c r="B155" s="120"/>
-      <c r="C155" s="120"/>
-      <c r="D155" s="120"/>
-      <c r="E155" s="120"/>
+      <c r="B155" s="119"/>
+      <c r="C155" s="119"/>
+      <c r="D155" s="119"/>
+      <c r="E155" s="119"/>
     </row>
     <row r="156" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
@@ -13097,13 +13097,13 @@
       </c>
     </row>
     <row r="184" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="119" t="s">
+      <c r="A184" s="120" t="s">
         <v>698</v>
       </c>
-      <c r="B184" s="120"/>
-      <c r="C184" s="120"/>
-      <c r="D184" s="120"/>
-      <c r="E184" s="120"/>
+      <c r="B184" s="119"/>
+      <c r="C184" s="119"/>
+      <c r="D184" s="119"/>
+      <c r="E184" s="119"/>
     </row>
     <row r="185" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
@@ -13479,13 +13479,13 @@
       <c r="E209" s="82"/>
     </row>
     <row r="210" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="119" t="s">
+      <c r="A210" s="120" t="s">
         <v>700</v>
       </c>
-      <c r="B210" s="120"/>
-      <c r="C210" s="120"/>
-      <c r="D210" s="120"/>
-      <c r="E210" s="120"/>
+      <c r="B210" s="119"/>
+      <c r="C210" s="119"/>
+      <c r="D210" s="119"/>
+      <c r="E210" s="119"/>
     </row>
     <row r="211" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
@@ -13875,83 +13875,83 @@
       <c r="E237" s="82"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A238" s="134" t="s">
+      <c r="A238" s="135" t="s">
         <v>281</v>
       </c>
-      <c r="B238" s="135"/>
-      <c r="C238" s="135"/>
-      <c r="D238" s="135"/>
-      <c r="E238" s="135"/>
+      <c r="B238" s="136"/>
+      <c r="C238" s="136"/>
+      <c r="D238" s="136"/>
+      <c r="E238" s="136"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A239" s="135"/>
-      <c r="B239" s="135"/>
-      <c r="C239" s="135"/>
-      <c r="D239" s="135"/>
-      <c r="E239" s="135"/>
+      <c r="A239" s="136"/>
+      <c r="B239" s="136"/>
+      <c r="C239" s="136"/>
+      <c r="D239" s="136"/>
+      <c r="E239" s="136"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A240" s="135"/>
-      <c r="B240" s="135"/>
-      <c r="C240" s="135"/>
-      <c r="D240" s="135"/>
-      <c r="E240" s="135"/>
+      <c r="A240" s="136"/>
+      <c r="B240" s="136"/>
+      <c r="C240" s="136"/>
+      <c r="D240" s="136"/>
+      <c r="E240" s="136"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A241" s="135"/>
-      <c r="B241" s="135"/>
-      <c r="C241" s="135"/>
-      <c r="D241" s="135"/>
-      <c r="E241" s="135"/>
+      <c r="A241" s="136"/>
+      <c r="B241" s="136"/>
+      <c r="C241" s="136"/>
+      <c r="D241" s="136"/>
+      <c r="E241" s="136"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A242" s="135"/>
-      <c r="B242" s="135"/>
-      <c r="C242" s="135"/>
-      <c r="D242" s="135"/>
-      <c r="E242" s="135"/>
+      <c r="A242" s="136"/>
+      <c r="B242" s="136"/>
+      <c r="C242" s="136"/>
+      <c r="D242" s="136"/>
+      <c r="E242" s="136"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A243" s="135"/>
-      <c r="B243" s="135"/>
-      <c r="C243" s="135"/>
-      <c r="D243" s="135"/>
-      <c r="E243" s="135"/>
+      <c r="A243" s="136"/>
+      <c r="B243" s="136"/>
+      <c r="C243" s="136"/>
+      <c r="D243" s="136"/>
+      <c r="E243" s="136"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A244" s="135"/>
-      <c r="B244" s="135"/>
-      <c r="C244" s="135"/>
-      <c r="D244" s="135"/>
-      <c r="E244" s="135"/>
+      <c r="A244" s="136"/>
+      <c r="B244" s="136"/>
+      <c r="C244" s="136"/>
+      <c r="D244" s="136"/>
+      <c r="E244" s="136"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" s="135"/>
-      <c r="B245" s="135"/>
-      <c r="C245" s="135"/>
-      <c r="D245" s="135"/>
-      <c r="E245" s="135"/>
+      <c r="A245" s="136"/>
+      <c r="B245" s="136"/>
+      <c r="C245" s="136"/>
+      <c r="D245" s="136"/>
+      <c r="E245" s="136"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A246" s="135"/>
-      <c r="B246" s="135"/>
-      <c r="C246" s="135"/>
-      <c r="D246" s="135"/>
-      <c r="E246" s="135"/>
+      <c r="A246" s="136"/>
+      <c r="B246" s="136"/>
+      <c r="C246" s="136"/>
+      <c r="D246" s="136"/>
+      <c r="E246" s="136"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247" s="135"/>
-      <c r="B247" s="135"/>
-      <c r="C247" s="135"/>
-      <c r="D247" s="135"/>
-      <c r="E247" s="135"/>
+      <c r="A247" s="136"/>
+      <c r="B247" s="136"/>
+      <c r="C247" s="136"/>
+      <c r="D247" s="136"/>
+      <c r="E247" s="136"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248" s="135"/>
-      <c r="B248" s="135"/>
-      <c r="C248" s="135"/>
-      <c r="D248" s="135"/>
-      <c r="E248" s="135"/>
+      <c r="A248" s="136"/>
+      <c r="B248" s="136"/>
+      <c r="C248" s="136"/>
+      <c r="D248" s="136"/>
+      <c r="E248" s="136"/>
     </row>
     <row r="249" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A249" s="14"/>
@@ -13968,13 +13968,13 @@
       <c r="E250" s="82"/>
     </row>
     <row r="251" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A251" s="121" t="s">
+      <c r="A251" s="126" t="s">
         <v>392</v>
       </c>
-      <c r="B251" s="132"/>
-      <c r="C251" s="132"/>
-      <c r="D251" s="132"/>
-      <c r="E251" s="133"/>
+      <c r="B251" s="133"/>
+      <c r="C251" s="133"/>
+      <c r="D251" s="133"/>
+      <c r="E251" s="134"/>
     </row>
     <row r="252" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A252" s="6" t="s">
@@ -14235,13 +14235,13 @@
       <c r="E276" s="42"/>
     </row>
     <row r="277" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="119" t="s">
+      <c r="A277" s="120" t="s">
         <v>702</v>
       </c>
-      <c r="B277" s="120"/>
-      <c r="C277" s="120"/>
-      <c r="D277" s="120"/>
-      <c r="E277" s="120"/>
+      <c r="B277" s="119"/>
+      <c r="C277" s="119"/>
+      <c r="D277" s="119"/>
+      <c r="E277" s="119"/>
     </row>
     <row r="278" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
@@ -14380,13 +14380,13 @@
       </c>
     </row>
     <row r="286" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A286" s="121" t="s">
+      <c r="A286" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="B286" s="122"/>
-      <c r="C286" s="122"/>
-      <c r="D286" s="122"/>
-      <c r="E286" s="123"/>
+      <c r="B286" s="127"/>
+      <c r="C286" s="127"/>
+      <c r="D286" s="127"/>
+      <c r="E286" s="128"/>
     </row>
     <row r="287" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A287" s="6" t="s">
@@ -14812,13 +14812,13 @@
       <c r="E317" s="82"/>
     </row>
     <row r="318" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="119" t="s">
+      <c r="A318" s="120" t="s">
         <v>705</v>
       </c>
-      <c r="B318" s="120"/>
-      <c r="C318" s="120"/>
-      <c r="D318" s="120"/>
-      <c r="E318" s="120"/>
+      <c r="B318" s="119"/>
+      <c r="C318" s="119"/>
+      <c r="D318" s="119"/>
+      <c r="E318" s="119"/>
     </row>
     <row r="319" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
@@ -15255,13 +15255,13 @@
       <c r="E348" s="82"/>
     </row>
     <row r="349" spans="1:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A349" s="119" t="s">
+      <c r="A349" s="120" t="s">
         <v>707</v>
       </c>
-      <c r="B349" s="120"/>
-      <c r="C349" s="120"/>
-      <c r="D349" s="120"/>
-      <c r="E349" s="120"/>
+      <c r="B349" s="119"/>
+      <c r="C349" s="119"/>
+      <c r="D349" s="119"/>
+      <c r="E349" s="119"/>
     </row>
     <row r="350" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
@@ -15651,13 +15651,13 @@
       <c r="E376" s="82"/>
     </row>
     <row r="377" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A377" s="119" t="s">
+      <c r="A377" s="120" t="s">
         <v>708</v>
       </c>
-      <c r="B377" s="120"/>
-      <c r="C377" s="120"/>
-      <c r="D377" s="120"/>
-      <c r="E377" s="120"/>
+      <c r="B377" s="119"/>
+      <c r="C377" s="119"/>
+      <c r="D377" s="119"/>
+      <c r="E377" s="119"/>
     </row>
     <row r="378" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A378" s="2" t="s">
@@ -16047,13 +16047,13 @@
       <c r="E404" s="82"/>
     </row>
     <row r="405" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A405" s="136" t="s">
+      <c r="A405" s="132" t="s">
         <v>406</v>
       </c>
-      <c r="B405" s="132"/>
-      <c r="C405" s="132"/>
-      <c r="D405" s="132"/>
-      <c r="E405" s="133"/>
+      <c r="B405" s="133"/>
+      <c r="C405" s="133"/>
+      <c r="D405" s="133"/>
+      <c r="E405" s="134"/>
     </row>
     <row r="406" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A406" s="6" t="s">
@@ -16225,6 +16225,40 @@
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A368:E368"/>
+    <mergeCell ref="A377:E377"/>
+    <mergeCell ref="A386:E386"/>
+    <mergeCell ref="A391:E391"/>
+    <mergeCell ref="A184:E184"/>
+    <mergeCell ref="A251:E251"/>
+    <mergeCell ref="A238:E248"/>
+    <mergeCell ref="A224:E224"/>
+    <mergeCell ref="A210:E210"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A198:E198"/>
+    <mergeCell ref="A203:E203"/>
+    <mergeCell ref="A231:E231"/>
+    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A405:E405"/>
+    <mergeCell ref="A305:E305"/>
+    <mergeCell ref="A310:E310"/>
+    <mergeCell ref="A398:E398"/>
+    <mergeCell ref="A277:E277"/>
+    <mergeCell ref="A327:E327"/>
+    <mergeCell ref="A332:E332"/>
+    <mergeCell ref="A349:E349"/>
+    <mergeCell ref="A358:E358"/>
+    <mergeCell ref="A363:E363"/>
+    <mergeCell ref="A286:E286"/>
+    <mergeCell ref="A293:E293"/>
+    <mergeCell ref="A298:E298"/>
+    <mergeCell ref="A318:E318"/>
+    <mergeCell ref="A337:E337"/>
+    <mergeCell ref="A342:E342"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A155:E155"/>
     <mergeCell ref="A164:E164"/>
@@ -16241,40 +16275,6 @@
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A97:E97"/>
-    <mergeCell ref="A405:E405"/>
-    <mergeCell ref="A305:E305"/>
-    <mergeCell ref="A310:E310"/>
-    <mergeCell ref="A398:E398"/>
-    <mergeCell ref="A277:E277"/>
-    <mergeCell ref="A327:E327"/>
-    <mergeCell ref="A332:E332"/>
-    <mergeCell ref="A349:E349"/>
-    <mergeCell ref="A358:E358"/>
-    <mergeCell ref="A363:E363"/>
-    <mergeCell ref="A286:E286"/>
-    <mergeCell ref="A293:E293"/>
-    <mergeCell ref="A298:E298"/>
-    <mergeCell ref="A318:E318"/>
-    <mergeCell ref="A337:E337"/>
-    <mergeCell ref="A342:E342"/>
-    <mergeCell ref="A377:E377"/>
-    <mergeCell ref="A386:E386"/>
-    <mergeCell ref="A391:E391"/>
-    <mergeCell ref="A184:E184"/>
-    <mergeCell ref="A251:E251"/>
-    <mergeCell ref="A238:E248"/>
-    <mergeCell ref="A224:E224"/>
-    <mergeCell ref="A210:E210"/>
-    <mergeCell ref="A193:E193"/>
-    <mergeCell ref="A198:E198"/>
-    <mergeCell ref="A203:E203"/>
-    <mergeCell ref="A231:E231"/>
-    <mergeCell ref="A219:E219"/>
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A134:E134"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A368:E368"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16297,10 +16297,10 @@
       <c r="A1" s="117" t="s">
         <v>683</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -16388,13 +16388,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="132" t="s">
         <v>223</v>
       </c>
-      <c r="B7" s="122"/>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="128"/>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -16448,10 +16448,10 @@
       <c r="A12" s="117" t="s">
         <v>684</v>
       </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
     </row>
     <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="59" t="s">
@@ -16525,10 +16525,10 @@
       <c r="A19" s="117" t="s">
         <v>685</v>
       </c>
-      <c r="B19" s="99"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
     </row>
     <row r="20" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="59" t="s">
@@ -16568,10 +16568,10 @@
       <c r="A24" s="117" t="s">
         <v>686</v>
       </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
     </row>
     <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="59" t="s">
@@ -16671,22 +16671,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="149" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
     </row>
     <row r="2" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="65" t="s">
@@ -16704,17 +16704,17 @@
       <c r="E2" s="66" t="s">
         <v>423</v>
       </c>
-      <c r="F2" s="157" t="s">
+      <c r="F2" s="140" t="s">
         <v>424</v>
       </c>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="150"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="150"/>
-      <c r="M2" s="150"/>
-      <c r="N2" s="151"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="142"/>
     </row>
     <row r="3" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="65"/>
@@ -16726,17 +16726,17 @@
         <v>184</v>
       </c>
       <c r="E3" s="66"/>
-      <c r="F3" s="157" t="s">
+      <c r="F3" s="140" t="s">
         <v>445</v>
       </c>
-      <c r="G3" s="150"/>
-      <c r="H3" s="150"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
-      <c r="L3" s="150"/>
-      <c r="M3" s="150"/>
-      <c r="N3" s="151"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="141"/>
+      <c r="K3" s="141"/>
+      <c r="L3" s="141"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="142"/>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="65"/>
@@ -16748,17 +16748,17 @@
         <v>184</v>
       </c>
       <c r="E4" s="66"/>
-      <c r="F4" s="157" t="s">
+      <c r="F4" s="140" t="s">
         <v>441</v>
       </c>
-      <c r="G4" s="150"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="150"/>
-      <c r="K4" s="150"/>
-      <c r="L4" s="150"/>
-      <c r="M4" s="150"/>
-      <c r="N4" s="151"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="141"/>
+      <c r="K4" s="141"/>
+      <c r="L4" s="141"/>
+      <c r="M4" s="141"/>
+      <c r="N4" s="142"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="65"/>
@@ -16770,17 +16770,17 @@
         <v>184</v>
       </c>
       <c r="E5" s="66"/>
-      <c r="F5" s="157" t="s">
+      <c r="F5" s="140" t="s">
         <v>443</v>
       </c>
-      <c r="G5" s="150"/>
-      <c r="H5" s="150"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="150"/>
-      <c r="K5" s="150"/>
-      <c r="L5" s="150"/>
-      <c r="M5" s="150"/>
-      <c r="N5" s="151"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="142"/>
     </row>
     <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="65"/>
@@ -16792,17 +16792,17 @@
         <v>184</v>
       </c>
       <c r="E6" s="66"/>
-      <c r="F6" s="157" t="s">
+      <c r="F6" s="140" t="s">
         <v>444</v>
       </c>
-      <c r="G6" s="150"/>
-      <c r="H6" s="150"/>
-      <c r="I6" s="150"/>
-      <c r="J6" s="150"/>
-      <c r="K6" s="150"/>
-      <c r="L6" s="150"/>
-      <c r="M6" s="150"/>
-      <c r="N6" s="151"/>
+      <c r="G6" s="141"/>
+      <c r="H6" s="141"/>
+      <c r="I6" s="141"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="141"/>
+      <c r="M6" s="141"/>
+      <c r="N6" s="142"/>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="65"/>
@@ -16814,17 +16814,17 @@
         <v>184</v>
       </c>
       <c r="E7" s="66"/>
-      <c r="F7" s="157" t="s">
+      <c r="F7" s="140" t="s">
         <v>447</v>
       </c>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="150"/>
-      <c r="K7" s="150"/>
-      <c r="L7" s="150"/>
-      <c r="M7" s="150"/>
-      <c r="N7" s="151"/>
+      <c r="G7" s="141"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
+      <c r="N7" s="142"/>
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="65"/>
@@ -16836,17 +16836,17 @@
         <v>184</v>
       </c>
       <c r="E8" s="66"/>
-      <c r="F8" s="157" t="s">
+      <c r="F8" s="140" t="s">
         <v>448</v>
       </c>
-      <c r="G8" s="150"/>
-      <c r="H8" s="150"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="150"/>
-      <c r="K8" s="150"/>
-      <c r="L8" s="150"/>
-      <c r="M8" s="150"/>
-      <c r="N8" s="151"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="141"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="141"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="142"/>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="65"/>
@@ -16858,17 +16858,17 @@
         <v>184</v>
       </c>
       <c r="E9" s="66"/>
-      <c r="F9" s="157" t="s">
+      <c r="F9" s="140" t="s">
         <v>450</v>
       </c>
-      <c r="G9" s="150"/>
-      <c r="H9" s="150"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="150"/>
-      <c r="K9" s="150"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="150"/>
-      <c r="N9" s="151"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="141"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="141"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
+      <c r="N9" s="142"/>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="65"/>
@@ -16880,17 +16880,17 @@
         <v>451</v>
       </c>
       <c r="E10" s="66"/>
-      <c r="F10" s="157" t="s">
+      <c r="F10" s="140" t="s">
         <v>452</v>
       </c>
-      <c r="G10" s="150"/>
-      <c r="H10" s="150"/>
-      <c r="I10" s="150"/>
-      <c r="J10" s="150"/>
-      <c r="K10" s="150"/>
-      <c r="L10" s="150"/>
-      <c r="M10" s="150"/>
-      <c r="N10" s="151"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="141"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="141"/>
+      <c r="M10" s="141"/>
+      <c r="N10" s="142"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="65"/>
@@ -16902,17 +16902,17 @@
         <v>184</v>
       </c>
       <c r="E11" s="66"/>
-      <c r="F11" s="157" t="s">
+      <c r="F11" s="140" t="s">
         <v>454</v>
       </c>
-      <c r="G11" s="150"/>
-      <c r="H11" s="150"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="150"/>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="150"/>
-      <c r="N11" s="151"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="141"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="142"/>
     </row>
     <row r="12" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="65"/>
@@ -16924,17 +16924,17 @@
         <v>455</v>
       </c>
       <c r="E12" s="66"/>
-      <c r="F12" s="158" t="s">
+      <c r="F12" s="146" t="s">
         <v>554</v>
       </c>
-      <c r="G12" s="153"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="153"/>
-      <c r="L12" s="153"/>
-      <c r="M12" s="153"/>
-      <c r="N12" s="154"/>
+      <c r="G12" s="147"/>
+      <c r="H12" s="147"/>
+      <c r="I12" s="147"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="148"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="65"/>
@@ -16946,17 +16946,17 @@
         <v>489</v>
       </c>
       <c r="E13" s="66"/>
-      <c r="F13" s="157" t="s">
+      <c r="F13" s="140" t="s">
         <v>456</v>
       </c>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="150"/>
-      <c r="K13" s="150"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="150"/>
-      <c r="N13" s="151"/>
+      <c r="G13" s="141"/>
+      <c r="H13" s="141"/>
+      <c r="I13" s="141"/>
+      <c r="J13" s="141"/>
+      <c r="K13" s="141"/>
+      <c r="L13" s="141"/>
+      <c r="M13" s="141"/>
+      <c r="N13" s="142"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="65"/>
@@ -16968,17 +16968,17 @@
         <v>457</v>
       </c>
       <c r="E14" s="66"/>
-      <c r="F14" s="157" t="s">
+      <c r="F14" s="140" t="s">
         <v>458</v>
       </c>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="150"/>
-      <c r="N14" s="151"/>
+      <c r="G14" s="141"/>
+      <c r="H14" s="141"/>
+      <c r="I14" s="141"/>
+      <c r="J14" s="141"/>
+      <c r="K14" s="141"/>
+      <c r="L14" s="141"/>
+      <c r="M14" s="141"/>
+      <c r="N14" s="142"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="65"/>
@@ -16990,17 +16990,17 @@
         <v>459</v>
       </c>
       <c r="E15" s="66"/>
-      <c r="F15" s="157" t="s">
+      <c r="F15" s="140" t="s">
         <v>460</v>
       </c>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="150"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="150"/>
-      <c r="M15" s="150"/>
-      <c r="N15" s="151"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="141"/>
+      <c r="J15" s="141"/>
+      <c r="K15" s="141"/>
+      <c r="L15" s="141"/>
+      <c r="M15" s="141"/>
+      <c r="N15" s="142"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="65"/>
@@ -17012,17 +17012,17 @@
         <v>462</v>
       </c>
       <c r="E16" s="66"/>
-      <c r="F16" s="157" t="s">
+      <c r="F16" s="140" t="s">
         <v>464</v>
       </c>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="150"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="150"/>
-      <c r="M16" s="150"/>
-      <c r="N16" s="151"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="141"/>
+      <c r="I16" s="141"/>
+      <c r="J16" s="141"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="141"/>
+      <c r="M16" s="141"/>
+      <c r="N16" s="142"/>
     </row>
     <row r="17" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="65"/>
@@ -17034,17 +17034,17 @@
         <v>461</v>
       </c>
       <c r="E17" s="66"/>
-      <c r="F17" s="157" t="s">
+      <c r="F17" s="140" t="s">
         <v>463</v>
       </c>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="150"/>
-      <c r="K17" s="150"/>
-      <c r="L17" s="150"/>
-      <c r="M17" s="150"/>
-      <c r="N17" s="151"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="141"/>
+      <c r="I17" s="141"/>
+      <c r="J17" s="141"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="141"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="142"/>
     </row>
     <row r="18" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="65"/>
@@ -17056,17 +17056,17 @@
         <v>465</v>
       </c>
       <c r="E18" s="66"/>
-      <c r="F18" s="157" t="s">
+      <c r="F18" s="140" t="s">
         <v>466</v>
       </c>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="150"/>
-      <c r="K18" s="150"/>
-      <c r="L18" s="150"/>
-      <c r="M18" s="150"/>
-      <c r="N18" s="151"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="141"/>
+      <c r="I18" s="141"/>
+      <c r="J18" s="141"/>
+      <c r="K18" s="141"/>
+      <c r="L18" s="141"/>
+      <c r="M18" s="141"/>
+      <c r="N18" s="142"/>
     </row>
     <row r="19" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="65"/>
@@ -17078,17 +17078,17 @@
         <v>467</v>
       </c>
       <c r="E19" s="66"/>
-      <c r="F19" s="157" t="s">
+      <c r="F19" s="140" t="s">
         <v>468</v>
       </c>
-      <c r="G19" s="150"/>
-      <c r="H19" s="150"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="150"/>
-      <c r="K19" s="150"/>
-      <c r="L19" s="150"/>
-      <c r="M19" s="150"/>
-      <c r="N19" s="151"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="141"/>
+      <c r="I19" s="141"/>
+      <c r="J19" s="141"/>
+      <c r="K19" s="141"/>
+      <c r="L19" s="141"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="142"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="65"/>
@@ -17096,17 +17096,17 @@
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
       <c r="E20" s="66"/>
-      <c r="F20" s="157">
+      <c r="F20" s="140">
         <v>1</v>
       </c>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="150"/>
-      <c r="K20" s="150"/>
-      <c r="L20" s="150"/>
-      <c r="M20" s="150"/>
-      <c r="N20" s="151"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="141"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="142"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="57"/>
@@ -17114,51 +17114,51 @@
       <c r="C21" s="57"/>
       <c r="D21" s="57"/>
       <c r="E21" s="58"/>
-      <c r="F21" s="162"/>
-      <c r="G21" s="163"/>
-      <c r="H21" s="163"/>
-      <c r="I21" s="163"/>
-      <c r="J21" s="163"/>
-      <c r="K21" s="163"/>
-      <c r="L21" s="163"/>
-      <c r="M21" s="163"/>
-      <c r="N21" s="164"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="144"/>
+      <c r="I21" s="144"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="145"/>
     </row>
     <row r="22" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="159" t="s">
+      <c r="A22" s="137" t="s">
         <v>487</v>
       </c>
-      <c r="B22" s="160"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="160"/>
-      <c r="E22" s="160"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="160"/>
-      <c r="H22" s="160"/>
-      <c r="I22" s="160"/>
-      <c r="J22" s="160"/>
-      <c r="K22" s="160"/>
-      <c r="L22" s="160"/>
-      <c r="M22" s="160"/>
-      <c r="N22" s="161"/>
+      <c r="B22" s="138"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="138"/>
+      <c r="N22" s="139"/>
     </row>
     <row r="23" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="155" t="s">
+      <c r="A23" s="150" t="s">
         <v>471</v>
       </c>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="156"/>
-      <c r="H23" s="156"/>
-      <c r="I23" s="156"/>
-      <c r="J23" s="156"/>
-      <c r="K23" s="156"/>
-      <c r="L23" s="156"/>
-      <c r="M23" s="156"/>
-      <c r="N23" s="156"/>
+      <c r="B23" s="149"/>
+      <c r="C23" s="149"/>
+      <c r="D23" s="149"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="149"/>
+      <c r="G23" s="149"/>
+      <c r="H23" s="149"/>
+      <c r="I23" s="149"/>
+      <c r="J23" s="149"/>
+      <c r="K23" s="149"/>
+      <c r="L23" s="149"/>
+      <c r="M23" s="149"/>
+      <c r="N23" s="149"/>
     </row>
     <row r="24" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="65" t="s">
@@ -17176,17 +17176,17 @@
       <c r="E24" s="66" t="s">
         <v>423</v>
       </c>
-      <c r="F24" s="149" t="s">
+      <c r="F24" s="151" t="s">
         <v>472</v>
       </c>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
-      <c r="I24" s="150"/>
-      <c r="J24" s="150"/>
-      <c r="K24" s="150"/>
-      <c r="L24" s="150"/>
-      <c r="M24" s="150"/>
-      <c r="N24" s="151"/>
+      <c r="G24" s="141"/>
+      <c r="H24" s="141"/>
+      <c r="I24" s="141"/>
+      <c r="J24" s="141"/>
+      <c r="K24" s="141"/>
+      <c r="L24" s="141"/>
+      <c r="M24" s="141"/>
+      <c r="N24" s="142"/>
     </row>
     <row r="25" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="65"/>
@@ -17198,17 +17198,17 @@
         <v>473</v>
       </c>
       <c r="E25" s="66"/>
-      <c r="F25" s="149" t="s">
+      <c r="F25" s="151" t="s">
         <v>474</v>
       </c>
-      <c r="G25" s="150"/>
-      <c r="H25" s="150"/>
-      <c r="I25" s="150"/>
-      <c r="J25" s="150"/>
-      <c r="K25" s="150"/>
-      <c r="L25" s="150"/>
-      <c r="M25" s="150"/>
-      <c r="N25" s="151"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="141"/>
+      <c r="L25" s="141"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="142"/>
     </row>
     <row r="26" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="65"/>
@@ -17220,17 +17220,17 @@
         <v>475</v>
       </c>
       <c r="E26" s="66"/>
-      <c r="F26" s="149" t="s">
+      <c r="F26" s="151" t="s">
         <v>476</v>
       </c>
-      <c r="G26" s="150"/>
-      <c r="H26" s="150"/>
-      <c r="I26" s="150"/>
-      <c r="J26" s="150"/>
-      <c r="K26" s="150"/>
-      <c r="L26" s="150"/>
-      <c r="M26" s="150"/>
-      <c r="N26" s="151"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="141"/>
+      <c r="I26" s="141"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="141"/>
+      <c r="L26" s="141"/>
+      <c r="M26" s="141"/>
+      <c r="N26" s="142"/>
     </row>
     <row r="27" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="65"/>
@@ -17242,17 +17242,17 @@
         <v>184</v>
       </c>
       <c r="E27" s="66"/>
-      <c r="F27" s="149" t="s">
+      <c r="F27" s="151" t="s">
         <v>478</v>
       </c>
-      <c r="G27" s="150"/>
-      <c r="H27" s="150"/>
-      <c r="I27" s="150"/>
-      <c r="J27" s="150"/>
-      <c r="K27" s="150"/>
-      <c r="L27" s="150"/>
-      <c r="M27" s="150"/>
-      <c r="N27" s="151"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="141"/>
+      <c r="I27" s="141"/>
+      <c r="J27" s="141"/>
+      <c r="K27" s="141"/>
+      <c r="L27" s="141"/>
+      <c r="M27" s="141"/>
+      <c r="N27" s="142"/>
     </row>
     <row r="28" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="65"/>
@@ -17264,17 +17264,17 @@
         <v>473</v>
       </c>
       <c r="E28" s="66"/>
-      <c r="F28" s="149" t="s">
+      <c r="F28" s="151" t="s">
         <v>477</v>
       </c>
-      <c r="G28" s="150"/>
-      <c r="H28" s="150"/>
-      <c r="I28" s="150"/>
-      <c r="J28" s="150"/>
-      <c r="K28" s="150"/>
-      <c r="L28" s="150"/>
-      <c r="M28" s="150"/>
-      <c r="N28" s="151"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="142"/>
     </row>
     <row r="29" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="65"/>
@@ -17286,17 +17286,17 @@
         <v>473</v>
       </c>
       <c r="E29" s="66"/>
-      <c r="F29" s="149" t="s">
+      <c r="F29" s="151" t="s">
         <v>479</v>
       </c>
-      <c r="G29" s="150"/>
-      <c r="H29" s="150"/>
-      <c r="I29" s="150"/>
-      <c r="J29" s="150"/>
-      <c r="K29" s="150"/>
-      <c r="L29" s="150"/>
-      <c r="M29" s="150"/>
-      <c r="N29" s="151"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="141"/>
+      <c r="L29" s="141"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="142"/>
     </row>
     <row r="30" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="65"/>
@@ -17308,17 +17308,17 @@
         <v>184</v>
       </c>
       <c r="E30" s="66"/>
-      <c r="F30" s="149" t="s">
+      <c r="F30" s="151" t="s">
         <v>481</v>
       </c>
-      <c r="G30" s="150"/>
-      <c r="H30" s="150"/>
-      <c r="I30" s="150"/>
-      <c r="J30" s="150"/>
-      <c r="K30" s="150"/>
-      <c r="L30" s="150"/>
-      <c r="M30" s="150"/>
-      <c r="N30" s="151"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="141"/>
+      <c r="I30" s="141"/>
+      <c r="J30" s="141"/>
+      <c r="K30" s="141"/>
+      <c r="L30" s="141"/>
+      <c r="M30" s="141"/>
+      <c r="N30" s="142"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="65"/>
@@ -17330,17 +17330,17 @@
         <v>184</v>
       </c>
       <c r="E31" s="66"/>
-      <c r="F31" s="149" t="s">
+      <c r="F31" s="151" t="s">
         <v>483</v>
       </c>
-      <c r="G31" s="150"/>
-      <c r="H31" s="150"/>
-      <c r="I31" s="150"/>
-      <c r="J31" s="150"/>
-      <c r="K31" s="150"/>
-      <c r="L31" s="150"/>
-      <c r="M31" s="150"/>
-      <c r="N31" s="151"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="141"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="141"/>
+      <c r="L31" s="141"/>
+      <c r="M31" s="141"/>
+      <c r="N31" s="142"/>
     </row>
     <row r="32" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="65"/>
@@ -17352,17 +17352,17 @@
         <v>184</v>
       </c>
       <c r="E32" s="66"/>
-      <c r="F32" s="149" t="s">
+      <c r="F32" s="151" t="s">
         <v>484</v>
       </c>
-      <c r="G32" s="150"/>
-      <c r="H32" s="150"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="150"/>
-      <c r="K32" s="150"/>
-      <c r="L32" s="150"/>
-      <c r="M32" s="150"/>
-      <c r="N32" s="151"/>
+      <c r="G32" s="141"/>
+      <c r="H32" s="141"/>
+      <c r="I32" s="141"/>
+      <c r="J32" s="141"/>
+      <c r="K32" s="141"/>
+      <c r="L32" s="141"/>
+      <c r="M32" s="141"/>
+      <c r="N32" s="142"/>
     </row>
     <row r="33" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="65"/>
@@ -17374,17 +17374,17 @@
         <v>184</v>
       </c>
       <c r="E33" s="66"/>
-      <c r="F33" s="149" t="s">
+      <c r="F33" s="151" t="s">
         <v>485</v>
       </c>
-      <c r="G33" s="150"/>
-      <c r="H33" s="150"/>
-      <c r="I33" s="150"/>
-      <c r="J33" s="150"/>
-      <c r="K33" s="150"/>
-      <c r="L33" s="150"/>
-      <c r="M33" s="150"/>
-      <c r="N33" s="151"/>
+      <c r="G33" s="141"/>
+      <c r="H33" s="141"/>
+      <c r="I33" s="141"/>
+      <c r="J33" s="141"/>
+      <c r="K33" s="141"/>
+      <c r="L33" s="141"/>
+      <c r="M33" s="141"/>
+      <c r="N33" s="142"/>
     </row>
     <row r="34" spans="1:14" s="53" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="65"/>
@@ -17408,344 +17408,358 @@
       <c r="C35" s="65"/>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
-      <c r="F35" s="152"/>
-      <c r="G35" s="153"/>
-      <c r="H35" s="153"/>
-      <c r="I35" s="153"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="153"/>
-      <c r="L35" s="153"/>
-      <c r="M35" s="153"/>
-      <c r="N35" s="154"/>
+      <c r="F35" s="164"/>
+      <c r="G35" s="147"/>
+      <c r="H35" s="147"/>
+      <c r="I35" s="147"/>
+      <c r="J35" s="147"/>
+      <c r="K35" s="147"/>
+      <c r="L35" s="147"/>
+      <c r="M35" s="147"/>
+      <c r="N35" s="148"/>
     </row>
     <row r="36" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="137" t="s">
+      <c r="A36" s="152" t="s">
         <v>486</v>
       </c>
-      <c r="B36" s="138"/>
-      <c r="C36" s="138"/>
-      <c r="D36" s="138"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="138"/>
-      <c r="K36" s="138"/>
-      <c r="L36" s="138"/>
-      <c r="M36" s="138"/>
-      <c r="N36" s="139"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="153"/>
+      <c r="H36" s="153"/>
+      <c r="I36" s="153"/>
+      <c r="J36" s="153"/>
+      <c r="K36" s="153"/>
+      <c r="L36" s="153"/>
+      <c r="M36" s="153"/>
+      <c r="N36" s="154"/>
     </row>
     <row r="116" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="117" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D117" s="140" t="s">
+      <c r="D117" s="155" t="s">
         <v>488</v>
       </c>
-      <c r="E117" s="141"/>
-      <c r="F117" s="141"/>
-      <c r="G117" s="141"/>
-      <c r="H117" s="141"/>
-      <c r="I117" s="141"/>
-      <c r="J117" s="141"/>
-      <c r="K117" s="141"/>
-      <c r="L117" s="141"/>
-      <c r="M117" s="141"/>
-      <c r="N117" s="141"/>
-      <c r="O117" s="141"/>
-      <c r="P117" s="142"/>
+      <c r="E117" s="156"/>
+      <c r="F117" s="156"/>
+      <c r="G117" s="156"/>
+      <c r="H117" s="156"/>
+      <c r="I117" s="156"/>
+      <c r="J117" s="156"/>
+      <c r="K117" s="156"/>
+      <c r="L117" s="156"/>
+      <c r="M117" s="156"/>
+      <c r="N117" s="156"/>
+      <c r="O117" s="156"/>
+      <c r="P117" s="157"/>
     </row>
     <row r="118" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D118" s="143"/>
-      <c r="E118" s="144"/>
-      <c r="F118" s="144"/>
-      <c r="G118" s="144"/>
-      <c r="H118" s="144"/>
-      <c r="I118" s="144"/>
-      <c r="J118" s="144"/>
-      <c r="K118" s="144"/>
-      <c r="L118" s="144"/>
-      <c r="M118" s="144"/>
-      <c r="N118" s="144"/>
-      <c r="O118" s="144"/>
-      <c r="P118" s="145"/>
+      <c r="D118" s="158"/>
+      <c r="E118" s="159"/>
+      <c r="F118" s="159"/>
+      <c r="G118" s="159"/>
+      <c r="H118" s="159"/>
+      <c r="I118" s="159"/>
+      <c r="J118" s="159"/>
+      <c r="K118" s="159"/>
+      <c r="L118" s="159"/>
+      <c r="M118" s="159"/>
+      <c r="N118" s="159"/>
+      <c r="O118" s="159"/>
+      <c r="P118" s="160"/>
     </row>
     <row r="119" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D119" s="143"/>
-      <c r="E119" s="144"/>
-      <c r="F119" s="144"/>
-      <c r="G119" s="144"/>
-      <c r="H119" s="144"/>
-      <c r="I119" s="144"/>
-      <c r="J119" s="144"/>
-      <c r="K119" s="144"/>
-      <c r="L119" s="144"/>
-      <c r="M119" s="144"/>
-      <c r="N119" s="144"/>
-      <c r="O119" s="144"/>
-      <c r="P119" s="145"/>
+      <c r="D119" s="158"/>
+      <c r="E119" s="159"/>
+      <c r="F119" s="159"/>
+      <c r="G119" s="159"/>
+      <c r="H119" s="159"/>
+      <c r="I119" s="159"/>
+      <c r="J119" s="159"/>
+      <c r="K119" s="159"/>
+      <c r="L119" s="159"/>
+      <c r="M119" s="159"/>
+      <c r="N119" s="159"/>
+      <c r="O119" s="159"/>
+      <c r="P119" s="160"/>
     </row>
     <row r="120" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D120" s="143"/>
-      <c r="E120" s="144"/>
-      <c r="F120" s="144"/>
-      <c r="G120" s="144"/>
-      <c r="H120" s="144"/>
-      <c r="I120" s="144"/>
-      <c r="J120" s="144"/>
-      <c r="K120" s="144"/>
-      <c r="L120" s="144"/>
-      <c r="M120" s="144"/>
-      <c r="N120" s="144"/>
-      <c r="O120" s="144"/>
-      <c r="P120" s="145"/>
+      <c r="D120" s="158"/>
+      <c r="E120" s="159"/>
+      <c r="F120" s="159"/>
+      <c r="G120" s="159"/>
+      <c r="H120" s="159"/>
+      <c r="I120" s="159"/>
+      <c r="J120" s="159"/>
+      <c r="K120" s="159"/>
+      <c r="L120" s="159"/>
+      <c r="M120" s="159"/>
+      <c r="N120" s="159"/>
+      <c r="O120" s="159"/>
+      <c r="P120" s="160"/>
     </row>
     <row r="121" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D121" s="143"/>
-      <c r="E121" s="144"/>
-      <c r="F121" s="144"/>
-      <c r="G121" s="144"/>
-      <c r="H121" s="144"/>
-      <c r="I121" s="144"/>
-      <c r="J121" s="144"/>
-      <c r="K121" s="144"/>
-      <c r="L121" s="144"/>
-      <c r="M121" s="144"/>
-      <c r="N121" s="144"/>
-      <c r="O121" s="144"/>
-      <c r="P121" s="145"/>
+      <c r="D121" s="158"/>
+      <c r="E121" s="159"/>
+      <c r="F121" s="159"/>
+      <c r="G121" s="159"/>
+      <c r="H121" s="159"/>
+      <c r="I121" s="159"/>
+      <c r="J121" s="159"/>
+      <c r="K121" s="159"/>
+      <c r="L121" s="159"/>
+      <c r="M121" s="159"/>
+      <c r="N121" s="159"/>
+      <c r="O121" s="159"/>
+      <c r="P121" s="160"/>
     </row>
     <row r="122" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D122" s="143"/>
-      <c r="E122" s="144"/>
-      <c r="F122" s="144"/>
-      <c r="G122" s="144"/>
-      <c r="H122" s="144"/>
-      <c r="I122" s="144"/>
-      <c r="J122" s="144"/>
-      <c r="K122" s="144"/>
-      <c r="L122" s="144"/>
-      <c r="M122" s="144"/>
-      <c r="N122" s="144"/>
-      <c r="O122" s="144"/>
-      <c r="P122" s="145"/>
+      <c r="D122" s="158"/>
+      <c r="E122" s="159"/>
+      <c r="F122" s="159"/>
+      <c r="G122" s="159"/>
+      <c r="H122" s="159"/>
+      <c r="I122" s="159"/>
+      <c r="J122" s="159"/>
+      <c r="K122" s="159"/>
+      <c r="L122" s="159"/>
+      <c r="M122" s="159"/>
+      <c r="N122" s="159"/>
+      <c r="O122" s="159"/>
+      <c r="P122" s="160"/>
     </row>
     <row r="123" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D123" s="143"/>
-      <c r="E123" s="144"/>
-      <c r="F123" s="144"/>
-      <c r="G123" s="144"/>
-      <c r="H123" s="144"/>
-      <c r="I123" s="144"/>
-      <c r="J123" s="144"/>
-      <c r="K123" s="144"/>
-      <c r="L123" s="144"/>
-      <c r="M123" s="144"/>
-      <c r="N123" s="144"/>
-      <c r="O123" s="144"/>
-      <c r="P123" s="145"/>
+      <c r="D123" s="158"/>
+      <c r="E123" s="159"/>
+      <c r="F123" s="159"/>
+      <c r="G123" s="159"/>
+      <c r="H123" s="159"/>
+      <c r="I123" s="159"/>
+      <c r="J123" s="159"/>
+      <c r="K123" s="159"/>
+      <c r="L123" s="159"/>
+      <c r="M123" s="159"/>
+      <c r="N123" s="159"/>
+      <c r="O123" s="159"/>
+      <c r="P123" s="160"/>
     </row>
     <row r="124" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D124" s="143"/>
-      <c r="E124" s="144"/>
-      <c r="F124" s="144"/>
-      <c r="G124" s="144"/>
-      <c r="H124" s="144"/>
-      <c r="I124" s="144"/>
-      <c r="J124" s="144"/>
-      <c r="K124" s="144"/>
-      <c r="L124" s="144"/>
-      <c r="M124" s="144"/>
-      <c r="N124" s="144"/>
-      <c r="O124" s="144"/>
-      <c r="P124" s="145"/>
+      <c r="D124" s="158"/>
+      <c r="E124" s="159"/>
+      <c r="F124" s="159"/>
+      <c r="G124" s="159"/>
+      <c r="H124" s="159"/>
+      <c r="I124" s="159"/>
+      <c r="J124" s="159"/>
+      <c r="K124" s="159"/>
+      <c r="L124" s="159"/>
+      <c r="M124" s="159"/>
+      <c r="N124" s="159"/>
+      <c r="O124" s="159"/>
+      <c r="P124" s="160"/>
     </row>
     <row r="125" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D125" s="143"/>
-      <c r="E125" s="144"/>
-      <c r="F125" s="144"/>
-      <c r="G125" s="144"/>
-      <c r="H125" s="144"/>
-      <c r="I125" s="144"/>
-      <c r="J125" s="144"/>
-      <c r="K125" s="144"/>
-      <c r="L125" s="144"/>
-      <c r="M125" s="144"/>
-      <c r="N125" s="144"/>
-      <c r="O125" s="144"/>
-      <c r="P125" s="145"/>
+      <c r="D125" s="158"/>
+      <c r="E125" s="159"/>
+      <c r="F125" s="159"/>
+      <c r="G125" s="159"/>
+      <c r="H125" s="159"/>
+      <c r="I125" s="159"/>
+      <c r="J125" s="159"/>
+      <c r="K125" s="159"/>
+      <c r="L125" s="159"/>
+      <c r="M125" s="159"/>
+      <c r="N125" s="159"/>
+      <c r="O125" s="159"/>
+      <c r="P125" s="160"/>
     </row>
     <row r="126" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D126" s="143"/>
-      <c r="E126" s="144"/>
-      <c r="F126" s="144"/>
-      <c r="G126" s="144"/>
-      <c r="H126" s="144"/>
-      <c r="I126" s="144"/>
-      <c r="J126" s="144"/>
-      <c r="K126" s="144"/>
-      <c r="L126" s="144"/>
-      <c r="M126" s="144"/>
-      <c r="N126" s="144"/>
-      <c r="O126" s="144"/>
-      <c r="P126" s="145"/>
+      <c r="D126" s="158"/>
+      <c r="E126" s="159"/>
+      <c r="F126" s="159"/>
+      <c r="G126" s="159"/>
+      <c r="H126" s="159"/>
+      <c r="I126" s="159"/>
+      <c r="J126" s="159"/>
+      <c r="K126" s="159"/>
+      <c r="L126" s="159"/>
+      <c r="M126" s="159"/>
+      <c r="N126" s="159"/>
+      <c r="O126" s="159"/>
+      <c r="P126" s="160"/>
     </row>
     <row r="127" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D127" s="143"/>
-      <c r="E127" s="144"/>
-      <c r="F127" s="144"/>
-      <c r="G127" s="144"/>
-      <c r="H127" s="144"/>
-      <c r="I127" s="144"/>
-      <c r="J127" s="144"/>
-      <c r="K127" s="144"/>
-      <c r="L127" s="144"/>
-      <c r="M127" s="144"/>
-      <c r="N127" s="144"/>
-      <c r="O127" s="144"/>
-      <c r="P127" s="145"/>
+      <c r="D127" s="158"/>
+      <c r="E127" s="159"/>
+      <c r="F127" s="159"/>
+      <c r="G127" s="159"/>
+      <c r="H127" s="159"/>
+      <c r="I127" s="159"/>
+      <c r="J127" s="159"/>
+      <c r="K127" s="159"/>
+      <c r="L127" s="159"/>
+      <c r="M127" s="159"/>
+      <c r="N127" s="159"/>
+      <c r="O127" s="159"/>
+      <c r="P127" s="160"/>
     </row>
     <row r="128" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D128" s="143"/>
-      <c r="E128" s="144"/>
-      <c r="F128" s="144"/>
-      <c r="G128" s="144"/>
-      <c r="H128" s="144"/>
-      <c r="I128" s="144"/>
-      <c r="J128" s="144"/>
-      <c r="K128" s="144"/>
-      <c r="L128" s="144"/>
-      <c r="M128" s="144"/>
-      <c r="N128" s="144"/>
-      <c r="O128" s="144"/>
-      <c r="P128" s="145"/>
+      <c r="D128" s="158"/>
+      <c r="E128" s="159"/>
+      <c r="F128" s="159"/>
+      <c r="G128" s="159"/>
+      <c r="H128" s="159"/>
+      <c r="I128" s="159"/>
+      <c r="J128" s="159"/>
+      <c r="K128" s="159"/>
+      <c r="L128" s="159"/>
+      <c r="M128" s="159"/>
+      <c r="N128" s="159"/>
+      <c r="O128" s="159"/>
+      <c r="P128" s="160"/>
     </row>
     <row r="129" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D129" s="143"/>
-      <c r="E129" s="144"/>
-      <c r="F129" s="144"/>
-      <c r="G129" s="144"/>
-      <c r="H129" s="144"/>
-      <c r="I129" s="144"/>
-      <c r="J129" s="144"/>
-      <c r="K129" s="144"/>
-      <c r="L129" s="144"/>
-      <c r="M129" s="144"/>
-      <c r="N129" s="144"/>
-      <c r="O129" s="144"/>
-      <c r="P129" s="145"/>
+      <c r="D129" s="158"/>
+      <c r="E129" s="159"/>
+      <c r="F129" s="159"/>
+      <c r="G129" s="159"/>
+      <c r="H129" s="159"/>
+      <c r="I129" s="159"/>
+      <c r="J129" s="159"/>
+      <c r="K129" s="159"/>
+      <c r="L129" s="159"/>
+      <c r="M129" s="159"/>
+      <c r="N129" s="159"/>
+      <c r="O129" s="159"/>
+      <c r="P129" s="160"/>
     </row>
     <row r="130" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D130" s="143"/>
-      <c r="E130" s="144"/>
-      <c r="F130" s="144"/>
-      <c r="G130" s="144"/>
-      <c r="H130" s="144"/>
-      <c r="I130" s="144"/>
-      <c r="J130" s="144"/>
-      <c r="K130" s="144"/>
-      <c r="L130" s="144"/>
-      <c r="M130" s="144"/>
-      <c r="N130" s="144"/>
-      <c r="O130" s="144"/>
-      <c r="P130" s="145"/>
+      <c r="D130" s="158"/>
+      <c r="E130" s="159"/>
+      <c r="F130" s="159"/>
+      <c r="G130" s="159"/>
+      <c r="H130" s="159"/>
+      <c r="I130" s="159"/>
+      <c r="J130" s="159"/>
+      <c r="K130" s="159"/>
+      <c r="L130" s="159"/>
+      <c r="M130" s="159"/>
+      <c r="N130" s="159"/>
+      <c r="O130" s="159"/>
+      <c r="P130" s="160"/>
     </row>
     <row r="131" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D131" s="143"/>
-      <c r="E131" s="144"/>
-      <c r="F131" s="144"/>
-      <c r="G131" s="144"/>
-      <c r="H131" s="144"/>
-      <c r="I131" s="144"/>
-      <c r="J131" s="144"/>
-      <c r="K131" s="144"/>
-      <c r="L131" s="144"/>
-      <c r="M131" s="144"/>
-      <c r="N131" s="144"/>
-      <c r="O131" s="144"/>
-      <c r="P131" s="145"/>
+      <c r="D131" s="158"/>
+      <c r="E131" s="159"/>
+      <c r="F131" s="159"/>
+      <c r="G131" s="159"/>
+      <c r="H131" s="159"/>
+      <c r="I131" s="159"/>
+      <c r="J131" s="159"/>
+      <c r="K131" s="159"/>
+      <c r="L131" s="159"/>
+      <c r="M131" s="159"/>
+      <c r="N131" s="159"/>
+      <c r="O131" s="159"/>
+      <c r="P131" s="160"/>
     </row>
     <row r="132" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D132" s="143"/>
-      <c r="E132" s="144"/>
-      <c r="F132" s="144"/>
-      <c r="G132" s="144"/>
-      <c r="H132" s="144"/>
-      <c r="I132" s="144"/>
-      <c r="J132" s="144"/>
-      <c r="K132" s="144"/>
-      <c r="L132" s="144"/>
-      <c r="M132" s="144"/>
-      <c r="N132" s="144"/>
-      <c r="O132" s="144"/>
-      <c r="P132" s="145"/>
+      <c r="D132" s="158"/>
+      <c r="E132" s="159"/>
+      <c r="F132" s="159"/>
+      <c r="G132" s="159"/>
+      <c r="H132" s="159"/>
+      <c r="I132" s="159"/>
+      <c r="J132" s="159"/>
+      <c r="K132" s="159"/>
+      <c r="L132" s="159"/>
+      <c r="M132" s="159"/>
+      <c r="N132" s="159"/>
+      <c r="O132" s="159"/>
+      <c r="P132" s="160"/>
     </row>
     <row r="133" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D133" s="143"/>
-      <c r="E133" s="144"/>
-      <c r="F133" s="144"/>
-      <c r="G133" s="144"/>
-      <c r="H133" s="144"/>
-      <c r="I133" s="144"/>
-      <c r="J133" s="144"/>
-      <c r="K133" s="144"/>
-      <c r="L133" s="144"/>
-      <c r="M133" s="144"/>
-      <c r="N133" s="144"/>
-      <c r="O133" s="144"/>
-      <c r="P133" s="145"/>
+      <c r="D133" s="158"/>
+      <c r="E133" s="159"/>
+      <c r="F133" s="159"/>
+      <c r="G133" s="159"/>
+      <c r="H133" s="159"/>
+      <c r="I133" s="159"/>
+      <c r="J133" s="159"/>
+      <c r="K133" s="159"/>
+      <c r="L133" s="159"/>
+      <c r="M133" s="159"/>
+      <c r="N133" s="159"/>
+      <c r="O133" s="159"/>
+      <c r="P133" s="160"/>
     </row>
     <row r="134" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D134" s="143"/>
-      <c r="E134" s="144"/>
-      <c r="F134" s="144"/>
-      <c r="G134" s="144"/>
-      <c r="H134" s="144"/>
-      <c r="I134" s="144"/>
-      <c r="J134" s="144"/>
-      <c r="K134" s="144"/>
-      <c r="L134" s="144"/>
-      <c r="M134" s="144"/>
-      <c r="N134" s="144"/>
-      <c r="O134" s="144"/>
-      <c r="P134" s="145"/>
+      <c r="D134" s="158"/>
+      <c r="E134" s="159"/>
+      <c r="F134" s="159"/>
+      <c r="G134" s="159"/>
+      <c r="H134" s="159"/>
+      <c r="I134" s="159"/>
+      <c r="J134" s="159"/>
+      <c r="K134" s="159"/>
+      <c r="L134" s="159"/>
+      <c r="M134" s="159"/>
+      <c r="N134" s="159"/>
+      <c r="O134" s="159"/>
+      <c r="P134" s="160"/>
     </row>
     <row r="135" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D135" s="143"/>
-      <c r="E135" s="144"/>
-      <c r="F135" s="144"/>
-      <c r="G135" s="144"/>
-      <c r="H135" s="144"/>
-      <c r="I135" s="144"/>
-      <c r="J135" s="144"/>
-      <c r="K135" s="144"/>
-      <c r="L135" s="144"/>
-      <c r="M135" s="144"/>
-      <c r="N135" s="144"/>
-      <c r="O135" s="144"/>
-      <c r="P135" s="145"/>
+      <c r="D135" s="158"/>
+      <c r="E135" s="159"/>
+      <c r="F135" s="159"/>
+      <c r="G135" s="159"/>
+      <c r="H135" s="159"/>
+      <c r="I135" s="159"/>
+      <c r="J135" s="159"/>
+      <c r="K135" s="159"/>
+      <c r="L135" s="159"/>
+      <c r="M135" s="159"/>
+      <c r="N135" s="159"/>
+      <c r="O135" s="159"/>
+      <c r="P135" s="160"/>
     </row>
     <row r="136" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D136" s="146"/>
-      <c r="E136" s="147"/>
-      <c r="F136" s="147"/>
-      <c r="G136" s="147"/>
-      <c r="H136" s="147"/>
-      <c r="I136" s="147"/>
-      <c r="J136" s="147"/>
-      <c r="K136" s="147"/>
-      <c r="L136" s="147"/>
-      <c r="M136" s="147"/>
-      <c r="N136" s="147"/>
-      <c r="O136" s="147"/>
-      <c r="P136" s="148"/>
+      <c r="D136" s="161"/>
+      <c r="E136" s="162"/>
+      <c r="F136" s="162"/>
+      <c r="G136" s="162"/>
+      <c r="H136" s="162"/>
+      <c r="I136" s="162"/>
+      <c r="J136" s="162"/>
+      <c r="K136" s="162"/>
+      <c r="L136" s="162"/>
+      <c r="M136" s="162"/>
+      <c r="N136" s="162"/>
+      <c r="O136" s="162"/>
+      <c r="P136" s="163"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="F18:N18"/>
-    <mergeCell ref="F19:N19"/>
-    <mergeCell ref="F20:N20"/>
-    <mergeCell ref="F21:N21"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="D117:P136"/>
+    <mergeCell ref="F33:N33"/>
+    <mergeCell ref="F35:N35"/>
+    <mergeCell ref="F28:N28"/>
+    <mergeCell ref="F29:N29"/>
+    <mergeCell ref="F30:N30"/>
+    <mergeCell ref="F31:N31"/>
+    <mergeCell ref="F32:N32"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="F24:N24"/>
+    <mergeCell ref="F25:N25"/>
+    <mergeCell ref="F26:N26"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F3:N3"/>
+    <mergeCell ref="F4:N4"/>
+    <mergeCell ref="F5:N5"/>
     <mergeCell ref="F17:N17"/>
     <mergeCell ref="F6:N6"/>
     <mergeCell ref="F7:N7"/>
@@ -17758,25 +17772,11 @@
     <mergeCell ref="F14:N14"/>
     <mergeCell ref="F15:N15"/>
     <mergeCell ref="F16:N16"/>
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="F3:N3"/>
-    <mergeCell ref="F4:N4"/>
-    <mergeCell ref="F5:N5"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="F24:N24"/>
-    <mergeCell ref="F25:N25"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="D117:P136"/>
-    <mergeCell ref="F33:N33"/>
-    <mergeCell ref="F35:N35"/>
-    <mergeCell ref="F28:N28"/>
-    <mergeCell ref="F29:N29"/>
-    <mergeCell ref="F30:N30"/>
-    <mergeCell ref="F31:N31"/>
-    <mergeCell ref="F32:N32"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="F18:N18"/>
+    <mergeCell ref="F19:N19"/>
+    <mergeCell ref="F20:N20"/>
+    <mergeCell ref="F21:N21"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
+++ b/docs/玩觅出入库分拣系统上位机-RCS通信协议V1.0D(杨文成 20260518).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LinWenTao\Desktop\Outbound_station\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464383F3-D059-4B33-9899-964BB28414AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFB8F85-87CD-4E1A-804D-917F42861887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3533,17 +3533,20 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3557,16 +3560,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3575,38 +3585,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3624,10 +3609,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3642,37 +3639,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3709,9 +3678,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4259,50 +4259,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
     </row>
     <row r="2" spans="1:8" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
       <c r="G2" s="20"/>
       <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
     </row>
     <row r="4" spans="1:8" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
       <c r="G4" s="21" t="s">
         <v>711</v>
       </c>
@@ -4311,14 +4311,14 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="108" t="s">
         <v>409</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
       <c r="G5" s="21" t="s">
         <v>710</v>
       </c>
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="6" spans="1:8" s="49" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="108" t="s">
         <v>712</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
       <c r="F6" s="20"/>
       <c r="G6" s="20"/>
       <c r="H6" s="20"/>
@@ -4349,26 +4349,26 @@
       <c r="H7" s="20"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="98"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="20"/>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="105"/>
       <c r="G9" s="22"/>
       <c r="H9" s="20"/>
     </row>
@@ -4383,10 +4383,10 @@
       <c r="D10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="103" t="s">
+      <c r="E10" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="104"/>
+      <c r="F10" s="105"/>
       <c r="G10" s="22"/>
       <c r="H10" s="20"/>
     </row>
@@ -4401,10 +4401,10 @@
       <c r="D11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="105" t="s">
+      <c r="E11" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="106"/>
+      <c r="F11" s="101"/>
       <c r="G11" s="22"/>
       <c r="H11" s="20"/>
     </row>
@@ -4419,10 +4419,10 @@
       <c r="D12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="105" t="s">
+      <c r="E12" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="106"/>
+      <c r="F12" s="101"/>
       <c r="G12" s="22"/>
       <c r="H12" s="20"/>
     </row>
@@ -4435,10 +4435,10 @@
       <c r="D13" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="105" t="s">
+      <c r="E13" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="106"/>
+      <c r="F13" s="101"/>
       <c r="G13" s="22"/>
       <c r="H13" s="20"/>
     </row>
@@ -4451,10 +4451,10 @@
       <c r="D14" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="108" t="s">
+      <c r="E14" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="106"/>
+      <c r="F14" s="101"/>
       <c r="G14" s="22"/>
       <c r="H14" s="20"/>
     </row>
@@ -4467,10 +4467,10 @@
       <c r="D15" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="108" t="s">
+      <c r="E15" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="106"/>
+      <c r="F15" s="101"/>
       <c r="G15" s="22"/>
       <c r="H15" s="20"/>
     </row>
@@ -4483,10 +4483,10 @@
       <c r="D16" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="108" t="s">
+      <c r="E16" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="106"/>
+      <c r="F16" s="101"/>
       <c r="G16" s="22"/>
       <c r="H16" s="20"/>
     </row>
@@ -4501,15 +4501,15 @@
       <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="109" t="s">
+      <c r="A18" s="102" t="s">
         <v>418</v>
       </c>
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="102"/>
       <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -4533,11 +4533,11 @@
       <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="107"/>
-      <c r="B21" s="107"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
+      <c r="A21" s="98"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
       <c r="H21" s="29"/>
@@ -4613,11 +4613,11 @@
       <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="107"/>
-      <c r="B29" s="107"/>
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
-      <c r="E29" s="107"/>
+      <c r="A29" s="98"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
@@ -4733,17 +4733,29 @@
       <c r="H40" s="20"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="100"/>
-      <c r="B41" s="100"/>
-      <c r="C41" s="100"/>
-      <c r="D41" s="100"/>
-      <c r="E41" s="100"/>
-      <c r="F41" s="100"/>
-      <c r="G41" s="100"/>
-      <c r="H41" s="100"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="99"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="99"/>
+      <c r="E41" s="99"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="99"/>
+      <c r="H41" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="E14:F14"/>
@@ -4751,18 +4763,6 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4780,13 +4780,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="116" t="s">
         <v>672</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -4795,11 +4795,11 @@
       <c r="B2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
@@ -4808,11 +4808,11 @@
       <c r="B3" s="19">
         <v>11000</v>
       </c>
-      <c r="C3" s="112" t="s">
+      <c r="C3" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
@@ -4821,11 +4821,11 @@
       <c r="B4" s="19">
         <v>11001</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
@@ -4834,11 +4834,11 @@
       <c r="B5" s="19">
         <v>11002</v>
       </c>
-      <c r="C5" s="112" t="s">
+      <c r="C5" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="112"/>
-      <c r="E5" s="112"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
     </row>
     <row r="6" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
@@ -4847,11 +4847,11 @@
       <c r="B6" s="19">
         <v>11003</v>
       </c>
-      <c r="C6" s="113" t="s">
+      <c r="C6" s="110" t="s">
         <v>665</v>
       </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
@@ -4860,11 +4860,11 @@
       <c r="B7" s="19">
         <v>11004</v>
       </c>
-      <c r="C7" s="112" t="s">
+      <c r="C7" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
@@ -4873,11 +4873,11 @@
       <c r="B8" s="19">
         <v>11005</v>
       </c>
-      <c r="C8" s="112" t="s">
+      <c r="C8" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
@@ -4886,11 +4886,11 @@
       <c r="B9" s="19">
         <v>11006</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
@@ -4899,27 +4899,27 @@
       <c r="B10" s="19">
         <v>11007</v>
       </c>
-      <c r="C10" s="113" t="s">
+      <c r="C10" s="110" t="s">
         <v>666</v>
       </c>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="19"/>
       <c r="B11" s="19"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
+      <c r="B14" s="114"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -4929,11 +4929,11 @@
         <f t="shared" ref="B15:B16" si="0">A15+10000</f>
         <v>11100</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="115" t="s">
         <v>667</v>
       </c>
-      <c r="D15" s="100"/>
-      <c r="E15" s="100"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
     </row>
     <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -4943,20 +4943,20 @@
         <f t="shared" si="0"/>
         <v>11101</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="115" t="s">
         <v>668</v>
       </c>
-      <c r="D16" s="100"/>
-      <c r="E16" s="100"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="110" t="s">
+      <c r="A19" s="116" t="s">
         <v>673</v>
       </c>
-      <c r="B19" s="111"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="111"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
@@ -4965,11 +4965,11 @@
       <c r="B20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="100" t="s">
+      <c r="C20" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
@@ -4978,11 +4978,11 @@
       <c r="B21" s="19">
         <v>12000</v>
       </c>
-      <c r="C21" s="112" t="s">
+      <c r="C21" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="112"/>
-      <c r="E21" s="112"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
     </row>
     <row r="22" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
@@ -4991,41 +4991,41 @@
       <c r="B22" s="19">
         <v>12001</v>
       </c>
-      <c r="C22" s="112" t="s">
+      <c r="C22" s="113" t="s">
         <v>671</v>
       </c>
-      <c r="D22" s="112"/>
-      <c r="E22" s="112"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="19"/>
       <c r="B23" s="19"/>
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="19"/>
       <c r="B24" s="19"/>
-      <c r="C24" s="115"/>
-      <c r="D24" s="115"/>
-      <c r="E24" s="115"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19"/>
       <c r="B25" s="19"/>
-      <c r="C25" s="115"/>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="110" t="s">
+      <c r="A26" s="116" t="s">
         <v>687</v>
       </c>
-      <c r="B26" s="111"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
@@ -5034,11 +5034,11 @@
       <c r="B27" s="19">
         <v>13000</v>
       </c>
-      <c r="C27" s="113" t="s">
+      <c r="C27" s="110" t="s">
         <v>690</v>
       </c>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="19">
@@ -5047,11 +5047,11 @@
       <c r="B28" s="19">
         <v>13001</v>
       </c>
-      <c r="C28" s="113" t="s">
+      <c r="C28" s="110" t="s">
         <v>691</v>
       </c>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19">
@@ -5060,11 +5060,11 @@
       <c r="B29" s="19">
         <v>13002</v>
       </c>
-      <c r="C29" s="113" t="s">
+      <c r="C29" s="110" t="s">
         <v>692</v>
       </c>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
+      <c r="D29" s="111"/>
+      <c r="E29" s="111"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="19">
@@ -5073,11 +5073,11 @@
       <c r="B30" s="19">
         <v>13003</v>
       </c>
-      <c r="C30" s="113" t="s">
+      <c r="C30" s="110" t="s">
         <v>693</v>
       </c>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19">
@@ -5086,11 +5086,11 @@
       <c r="B31" s="19">
         <v>13004</v>
       </c>
-      <c r="C31" s="113" t="s">
+      <c r="C31" s="110" t="s">
         <v>699</v>
       </c>
-      <c r="D31" s="113"/>
-      <c r="E31" s="113"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
@@ -5099,11 +5099,11 @@
       <c r="B32" s="19">
         <v>13005</v>
       </c>
-      <c r="C32" s="113" t="s">
+      <c r="C32" s="110" t="s">
         <v>701</v>
       </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
+      <c r="D32" s="110"/>
+      <c r="E32" s="110"/>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="19">
@@ -5112,11 +5112,11 @@
       <c r="B33" s="19">
         <v>13006</v>
       </c>
-      <c r="C33" s="113" t="s">
+      <c r="C33" s="110" t="s">
         <v>703</v>
       </c>
-      <c r="D33" s="113"/>
-      <c r="E33" s="113"/>
+      <c r="D33" s="110"/>
+      <c r="E33" s="110"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="19">
@@ -5125,11 +5125,11 @@
       <c r="B34" s="19">
         <v>13007</v>
       </c>
-      <c r="C34" s="113" t="s">
+      <c r="C34" s="110" t="s">
         <v>704</v>
       </c>
-      <c r="D34" s="113"/>
-      <c r="E34" s="113"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="110"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
@@ -5138,11 +5138,11 @@
       <c r="B35" s="19">
         <v>13008</v>
       </c>
-      <c r="C35" s="113" t="s">
+      <c r="C35" s="110" t="s">
         <v>706</v>
       </c>
-      <c r="D35" s="113"/>
-      <c r="E35" s="113"/>
+      <c r="D35" s="110"/>
+      <c r="E35" s="110"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
@@ -5151,11 +5151,11 @@
       <c r="B36" s="19">
         <v>13009</v>
       </c>
-      <c r="C36" s="113" t="s">
+      <c r="C36" s="110" t="s">
         <v>709</v>
       </c>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="110"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
@@ -5164,9 +5164,9 @@
       <c r="B37" s="19">
         <v>13010</v>
       </c>
-      <c r="C37" s="115"/>
-      <c r="D37" s="115"/>
-      <c r="E37" s="115"/>
+      <c r="C37" s="111"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="111"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
@@ -5175,9 +5175,9 @@
       <c r="B38" s="19">
         <v>13011</v>
       </c>
-      <c r="C38" s="115"/>
-      <c r="D38" s="115"/>
-      <c r="E38" s="115"/>
+      <c r="C38" s="111"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="111"/>
     </row>
     <row r="39" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="19"/>
@@ -5208,13 +5208,13 @@
       <c r="E42" s="81"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="110" t="s">
+      <c r="A43" s="116" t="s">
         <v>688</v>
       </c>
-      <c r="B43" s="111"/>
-      <c r="C43" s="111"/>
-      <c r="D43" s="111"/>
-      <c r="E43" s="111"/>
+      <c r="B43" s="117"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="18" t="s">
@@ -5223,11 +5223,11 @@
       <c r="B44" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="100" t="s">
+      <c r="C44" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="19">
@@ -5236,11 +5236,11 @@
       <c r="B45" s="19">
         <v>14000</v>
       </c>
-      <c r="C45" s="115" t="s">
+      <c r="C45" s="111" t="s">
         <v>232</v>
       </c>
-      <c r="D45" s="115"/>
-      <c r="E45" s="115"/>
+      <c r="D45" s="111"/>
+      <c r="E45" s="111"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="19">
@@ -5249,11 +5249,11 @@
       <c r="B46" s="19">
         <v>14001</v>
       </c>
-      <c r="C46" s="113" t="s">
+      <c r="C46" s="110" t="s">
         <v>689</v>
       </c>
-      <c r="D46" s="115"/>
-      <c r="E46" s="115"/>
+      <c r="D46" s="111"/>
+      <c r="E46" s="111"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="19"/>
@@ -5277,6 +5277,28 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="C46:E46"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="C28:E28"/>
@@ -5291,30 +5313,8 @@
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A19:E19"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="A43:E43"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5335,16 +5335,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -5501,16 +5501,16 @@
     </row>
     <row r="11" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="13" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="109" t="s">
+      <c r="A13" s="102" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="100"/>
-      <c r="C13" s="100"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -5675,13 +5675,13 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="119" t="s">
+      <c r="A26" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="119"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
+      <c r="B26" s="120"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="120"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -5829,16 +5829,16 @@
       <c r="E36" s="17"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="100" t="s">
+      <c r="A37" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="100"/>
-      <c r="C37" s="100"/>
-      <c r="D37" s="100"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="100"/>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -5905,16 +5905,16 @@
       </c>
     </row>
     <row r="48" spans="1:8" s="82" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="117" t="s">
+      <c r="A48" s="115" t="s">
         <v>659</v>
       </c>
-      <c r="B48" s="100"/>
-      <c r="C48" s="100"/>
-      <c r="D48" s="100"/>
-      <c r="E48" s="100"/>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
+      <c r="B48" s="99"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
     </row>
     <row r="49" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
@@ -6302,16 +6302,16 @@
     <row r="72" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="117" t="s">
+      <c r="A74" s="115" t="s">
         <v>660</v>
       </c>
-      <c r="B74" s="100"/>
-      <c r="C74" s="100"/>
-      <c r="D74" s="100"/>
-      <c r="E74" s="100"/>
-      <c r="F74" s="100"/>
-      <c r="G74" s="100"/>
-      <c r="H74" s="100"/>
+      <c r="B74" s="99"/>
+      <c r="C74" s="99"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="99"/>
+      <c r="G74" s="99"/>
+      <c r="H74" s="99"/>
     </row>
     <row r="75" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
@@ -6468,16 +6468,16 @@
     </row>
     <row r="84" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="86" spans="1:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="117" t="s">
+      <c r="A86" s="115" t="s">
         <v>661</v>
       </c>
-      <c r="B86" s="100"/>
-      <c r="C86" s="100"/>
-      <c r="D86" s="100"/>
-      <c r="E86" s="100"/>
-      <c r="F86" s="100"/>
-      <c r="G86" s="100"/>
-      <c r="H86" s="100"/>
+      <c r="B86" s="99"/>
+      <c r="C86" s="99"/>
+      <c r="D86" s="99"/>
+      <c r="E86" s="99"/>
+      <c r="F86" s="99"/>
+      <c r="G86" s="99"/>
+      <c r="H86" s="99"/>
     </row>
     <row r="87" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
@@ -6642,13 +6642,13 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="120" t="s">
+      <c r="A99" s="119" t="s">
         <v>662</v>
       </c>
-      <c r="B99" s="119"/>
-      <c r="C99" s="119"/>
-      <c r="D99" s="119"/>
-      <c r="E99" s="119"/>
+      <c r="B99" s="120"/>
+      <c r="C99" s="120"/>
+      <c r="D99" s="120"/>
+      <c r="E99" s="120"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -6870,16 +6870,16 @@
       </c>
     </row>
     <row r="120" spans="1:8" s="82" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="117" t="s">
+      <c r="A120" s="115" t="s">
         <v>663</v>
       </c>
-      <c r="B120" s="100"/>
-      <c r="C120" s="100"/>
-      <c r="D120" s="100"/>
-      <c r="E120" s="100"/>
-      <c r="F120" s="100"/>
-      <c r="G120" s="100"/>
-      <c r="H120" s="100"/>
+      <c r="B120" s="99"/>
+      <c r="C120" s="99"/>
+      <c r="D120" s="99"/>
+      <c r="E120" s="99"/>
+      <c r="F120" s="99"/>
+      <c r="G120" s="99"/>
+      <c r="H120" s="99"/>
     </row>
     <row r="121" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
@@ -7267,16 +7267,16 @@
     <row r="144" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="145" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="146" spans="1:8" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="117" t="s">
+      <c r="A146" s="115" t="s">
         <v>583</v>
       </c>
-      <c r="B146" s="100"/>
-      <c r="C146" s="100"/>
-      <c r="D146" s="100"/>
-      <c r="E146" s="100"/>
-      <c r="F146" s="100"/>
-      <c r="G146" s="100"/>
-      <c r="H146" s="100"/>
+      <c r="B146" s="99"/>
+      <c r="C146" s="99"/>
+      <c r="D146" s="99"/>
+      <c r="E146" s="99"/>
+      <c r="F146" s="99"/>
+      <c r="G146" s="99"/>
+      <c r="H146" s="99"/>
     </row>
     <row r="147" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
@@ -8165,13 +8165,13 @@
       <c r="E201" s="91"/>
     </row>
     <row r="202" spans="1:5" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="120" t="s">
+      <c r="A202" s="119" t="s">
         <v>584</v>
       </c>
-      <c r="B202" s="120"/>
-      <c r="C202" s="120"/>
-      <c r="D202" s="120"/>
-      <c r="E202" s="120"/>
+      <c r="B202" s="119"/>
+      <c r="C202" s="119"/>
+      <c r="D202" s="119"/>
+      <c r="E202" s="119"/>
     </row>
     <row r="203" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
@@ -9007,6 +9007,18 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A236:E236"/>
+    <mergeCell ref="A231:E231"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="A176:E176"/>
+    <mergeCell ref="A202:E202"/>
+    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A225:E225"/>
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A120:H120"/>
@@ -9018,18 +9030,6 @@
     <mergeCell ref="A86:H86"/>
     <mergeCell ref="A92:E92"/>
     <mergeCell ref="A99:E99"/>
-    <mergeCell ref="A236:E236"/>
-    <mergeCell ref="A231:E231"/>
-    <mergeCell ref="A170:E170"/>
-    <mergeCell ref="A176:E176"/>
-    <mergeCell ref="A202:E202"/>
-    <mergeCell ref="A219:E219"/>
-    <mergeCell ref="A225:E225"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9050,16 +9050,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="102" t="s">
         <v>434</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -9289,14 +9289,14 @@
       <c r="E12" s="78" t="s">
         <v>290</v>
       </c>
-      <c r="F12" s="122" t="s">
+      <c r="F12" s="127" t="s">
         <v>206</v>
       </c>
-      <c r="G12" s="122"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="122"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9315,16 +9315,16 @@
       <c r="E13" s="78" t="s">
         <v>293</v>
       </c>
-      <c r="F13" s="129" t="s">
+      <c r="F13" s="124" t="s">
         <v>565</v>
       </c>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="121" t="s">
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="126" t="s">
         <v>570</v>
       </c>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
       <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9343,12 +9343,12 @@
       <c r="E14" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9367,12 +9367,12 @@
       <c r="E15" s="79" t="s">
         <v>299</v>
       </c>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="126"/>
+      <c r="K15" s="126"/>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9391,12 +9391,12 @@
       <c r="E16" s="78" t="s">
         <v>211</v>
       </c>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="121"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="121"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="126"/>
+      <c r="J16" s="126"/>
+      <c r="K16" s="126"/>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9415,12 +9415,12 @@
       <c r="E17" s="78" t="s">
         <v>210</v>
       </c>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="126"/>
+      <c r="K17" s="126"/>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
@@ -9439,12 +9439,12 @@
       <c r="E18" s="78" t="s">
         <v>306</v>
       </c>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126"/>
+      <c r="J18" s="126"/>
+      <c r="K18" s="126"/>
       <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" s="73" customFormat="1" ht="33" x14ac:dyDescent="0.2">
@@ -9463,22 +9463,22 @@
       <c r="E19" s="79" t="s">
         <v>559</v>
       </c>
-      <c r="F19" s="130"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="121"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="121"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="126"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A20" s="126" t="s">
+      <c r="A20" s="121" t="s">
         <v>566</v>
       </c>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="128"/>
+      <c r="B20" s="122"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="123"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
@@ -9549,13 +9549,13 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="126" t="s">
+      <c r="A25" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="128"/>
+      <c r="B25" s="122"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="123"/>
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
       <c r="H25" s="41"/>
@@ -9614,13 +9614,13 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="126" t="s">
+      <c r="A30" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="127"/>
-      <c r="C30" s="127"/>
-      <c r="D30" s="127"/>
-      <c r="E30" s="128"/>
+      <c r="B30" s="122"/>
+      <c r="C30" s="122"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="123"/>
     </row>
     <row r="31" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
@@ -9691,16 +9691,16 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A37" s="123" t="s">
+      <c r="A37" s="128" t="s">
         <v>218</v>
       </c>
-      <c r="B37" s="124"/>
-      <c r="C37" s="124"/>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="125"/>
+      <c r="B37" s="129"/>
+      <c r="C37" s="129"/>
+      <c r="D37" s="129"/>
+      <c r="E37" s="129"/>
+      <c r="F37" s="129"/>
+      <c r="G37" s="129"/>
+      <c r="H37" s="130"/>
     </row>
     <row r="38" spans="1:8" ht="49.5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
@@ -10068,13 +10068,13 @@
     </row>
     <row r="53" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="117" t="s">
+      <c r="A54" s="115" t="s">
         <v>435</v>
       </c>
-      <c r="B54" s="100"/>
-      <c r="C54" s="100"/>
-      <c r="D54" s="100"/>
-      <c r="E54" s="100"/>
+      <c r="B54" s="99"/>
+      <c r="C54" s="99"/>
+      <c r="D54" s="99"/>
+      <c r="E54" s="99"/>
     </row>
     <row r="55" spans="1:8" s="52" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A55" s="59" t="s">
@@ -10147,13 +10147,13 @@
     <row r="59" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="61" spans="1:8" s="82" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="117" t="s">
+      <c r="A61" s="115" t="s">
         <v>748</v>
       </c>
-      <c r="B61" s="100"/>
-      <c r="C61" s="100"/>
-      <c r="D61" s="100"/>
-      <c r="E61" s="100"/>
+      <c r="B61" s="99"/>
+      <c r="C61" s="99"/>
+      <c r="D61" s="99"/>
+      <c r="E61" s="99"/>
     </row>
     <row r="62" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="59" t="s">
@@ -10209,13 +10209,13 @@
     <row r="65" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="67" spans="1:8" s="82" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="117" t="s">
+      <c r="A67" s="115" t="s">
         <v>749</v>
       </c>
-      <c r="B67" s="100"/>
-      <c r="C67" s="100"/>
-      <c r="D67" s="100"/>
-      <c r="E67" s="100"/>
+      <c r="B67" s="99"/>
+      <c r="C67" s="99"/>
+      <c r="D67" s="99"/>
+      <c r="E67" s="99"/>
     </row>
     <row r="68" spans="1:8" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A68" s="59" t="s">
@@ -10293,9 +10293,9 @@
       <c r="C74" s="82"/>
       <c r="D74" s="82"/>
       <c r="E74" s="82"/>
-      <c r="F74" s="109"/>
-      <c r="G74" s="100"/>
-      <c r="H74" s="100"/>
+      <c r="F74" s="102"/>
+      <c r="G74" s="99"/>
+      <c r="H74" s="99"/>
     </row>
     <row r="75" spans="1:8" s="52" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="82"/>
@@ -10425,12 +10425,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="F13:H19"/>
     <mergeCell ref="I13:K19"/>
     <mergeCell ref="F12:K12"/>
     <mergeCell ref="F74:H74"/>
@@ -10438,6 +10432,12 @@
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="F13:H19"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10457,13 +10457,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="119" t="s">
         <v>694</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -10919,13 +10919,13 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A31" s="126" t="s">
+      <c r="A31" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="127"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="128"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="122"/>
+      <c r="E31" s="123"/>
     </row>
     <row r="32" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
@@ -11027,13 +11027,13 @@
       <c r="E40" s="82"/>
     </row>
     <row r="41" spans="1:5" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="120" t="s">
+      <c r="A41" s="119" t="s">
         <v>695</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
+      <c r="B41" s="120"/>
+      <c r="C41" s="120"/>
+      <c r="D41" s="120"/>
+      <c r="E41" s="120"/>
     </row>
     <row r="42" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
@@ -11874,13 +11874,13 @@
       <c r="E96" s="43"/>
     </row>
     <row r="97" spans="1:5" s="82" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="120" t="s">
+      <c r="A97" s="119" t="s">
         <v>696</v>
       </c>
-      <c r="B97" s="119"/>
-      <c r="C97" s="119"/>
-      <c r="D97" s="119"/>
-      <c r="E97" s="119"/>
+      <c r="B97" s="120"/>
+      <c r="C97" s="120"/>
+      <c r="D97" s="120"/>
+      <c r="E97" s="120"/>
     </row>
     <row r="98" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
@@ -12703,13 +12703,13 @@
     <row r="153" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="154" spans="1:5" s="82" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="155" spans="1:5" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="120" t="s">
+      <c r="A155" s="119" t="s">
         <v>697</v>
       </c>
-      <c r="B155" s="119"/>
-      <c r="C155" s="119"/>
-      <c r="D155" s="119"/>
-      <c r="E155" s="119"/>
+      <c r="B155" s="120"/>
+      <c r="C155" s="120"/>
+      <c r="D155" s="120"/>
+      <c r="E155" s="120"/>
     </row>
     <row r="156" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
@@ -13097,13 +13097,13 @@
       </c>
     </row>
     <row r="184" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="120" t="s">
+      <c r="A184" s="119" t="s">
         <v>698</v>
       </c>
-      <c r="B184" s="119"/>
-      <c r="C184" s="119"/>
-      <c r="D184" s="119"/>
-      <c r="E184" s="119"/>
+      <c r="B184" s="120"/>
+      <c r="C184" s="120"/>
+      <c r="D184" s="120"/>
+      <c r="E184" s="120"/>
     </row>
     <row r="185" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
@@ -13479,13 +13479,13 @@
       <c r="E209" s="82"/>
     </row>
     <row r="210" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="120" t="s">
+      <c r="A210" s="119" t="s">
         <v>700</v>
       </c>
-      <c r="B210" s="119"/>
-      <c r="C210" s="119"/>
-      <c r="D210" s="119"/>
-      <c r="E210" s="119"/>
+      <c r="B210" s="120"/>
+      <c r="C210" s="120"/>
+      <c r="D210" s="120"/>
+      <c r="E210" s="120"/>
     </row>
     <row r="211" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
@@ -13875,83 +13875,83 @@
       <c r="E237" s="82"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A238" s="135" t="s">
+      <c r="A238" s="134" t="s">
         <v>281</v>
       </c>
-      <c r="B238" s="136"/>
-      <c r="C238" s="136"/>
-      <c r="D238" s="136"/>
-      <c r="E238" s="136"/>
+      <c r="B238" s="135"/>
+      <c r="C238" s="135"/>
+      <c r="D238" s="135"/>
+      <c r="E238" s="135"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A239" s="136"/>
-      <c r="B239" s="136"/>
-      <c r="C239" s="136"/>
-      <c r="D239" s="136"/>
-      <c r="E239" s="136"/>
+      <c r="A239" s="135"/>
+      <c r="B239" s="135"/>
+      <c r="C239" s="135"/>
+      <c r="D239" s="135"/>
+      <c r="E239" s="135"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A240" s="136"/>
-      <c r="B240" s="136"/>
-      <c r="C240" s="136"/>
-      <c r="D240" s="136"/>
-      <c r="E240" s="136"/>
+      <c r="A240" s="135"/>
+      <c r="B240" s="135"/>
+      <c r="C240" s="135"/>
+      <c r="D240" s="135"/>
+      <c r="E240" s="135"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A241" s="136"/>
-      <c r="B241" s="136"/>
-      <c r="C241" s="136"/>
-      <c r="D241" s="136"/>
-      <c r="E241" s="136"/>
+      <c r="A241" s="135"/>
+      <c r="B241" s="135"/>
+      <c r="C241" s="135"/>
+      <c r="D241" s="135"/>
+      <c r="E241" s="135"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A242" s="136"/>
-      <c r="B242" s="136"/>
-      <c r="C242" s="136"/>
-      <c r="D242" s="136"/>
-      <c r="E242" s="136"/>
+      <c r="A242" s="135"/>
+      <c r="B242" s="135"/>
+      <c r="C242" s="135"/>
+      <c r="D242" s="135"/>
+      <c r="E242" s="135"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A243" s="136"/>
-      <c r="B243" s="136"/>
-      <c r="C243" s="136"/>
-      <c r="D243" s="136"/>
-      <c r="E243" s="136"/>
+      <c r="A243" s="135"/>
+      <c r="B243" s="135"/>
+      <c r="C243" s="135"/>
+      <c r="D243" s="135"/>
+      <c r="E243" s="135"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A244" s="136"/>
-      <c r="B244" s="136"/>
-      <c r="C244" s="136"/>
-      <c r="D244" s="136"/>
-      <c r="E244" s="136"/>
+      <c r="A244" s="135"/>
+      <c r="B244" s="135"/>
+      <c r="C244" s="135"/>
+      <c r="D244" s="135"/>
+      <c r="E244" s="135"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A245" s="136"/>
-      <c r="B245" s="136"/>
-      <c r="C245" s="136"/>
-      <c r="D245" s="136"/>
-      <c r="E245" s="136"/>
+      <c r="A245" s="135"/>
+      <c r="B245" s="135"/>
+      <c r="C245" s="135"/>
+      <c r="D245" s="135"/>
+      <c r="E245" s="135"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A246" s="136"/>
-      <c r="B246" s="136"/>
-      <c r="C246" s="136"/>
-      <c r="D246" s="136"/>
-      <c r="E246" s="136"/>
+      <c r="A246" s="135"/>
+      <c r="B246" s="135"/>
+      <c r="C246" s="135"/>
+      <c r="D246" s="135"/>
+      <c r="E246" s="135"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A247" s="136"/>
-      <c r="B247" s="136"/>
-      <c r="C247" s="136"/>
-      <c r="D247" s="136"/>
-      <c r="E247" s="136"/>
+      <c r="A247" s="135"/>
+      <c r="B247" s="135"/>
+      <c r="C247" s="135"/>
+      <c r="D247" s="135"/>
+      <c r="E247" s="135"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248" s="136"/>
-      <c r="B248" s="136"/>
-      <c r="C248" s="136"/>
-      <c r="D248" s="136"/>
-      <c r="E248" s="136"/>
+      <c r="A248" s="135"/>
+      <c r="B248" s="135"/>
+      <c r="C248" s="135"/>
+      <c r="D248" s="135"/>
+      <c r="E248" s="135"/>
     </row>
     <row r="249" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A249" s="14"/>
@@ -13968,13 +13968,13 @@
       <c r="E250" s="82"/>
     </row>
     <row r="251" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A251" s="126" t="s">
+      <c r="A251" s="121" t="s">
         <v>392</v>
       </c>
-      <c r="B251" s="133"/>
-      <c r="C251" s="133"/>
-      <c r="D251" s="133"/>
-      <c r="E251" s="134"/>
+      <c r="B251" s="132"/>
+      <c r="C251" s="132"/>
+      <c r="D251" s="132"/>
+      <c r="E251" s="133"/>
     </row>
     <row r="252" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A252" s="6" t="s">
@@ -14235,13 +14235,13 @@
       <c r="E276" s="42"/>
     </row>
     <row r="277" spans="1:5" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="120" t="s">
+      <c r="A277" s="119" t="s">
         <v>702</v>
       </c>
-      <c r="B277" s="119"/>
-      <c r="C277" s="119"/>
-      <c r="D277" s="119"/>
-      <c r="E277" s="119"/>
+      <c r="B277" s="120"/>
+      <c r="C277" s="120"/>
+      <c r="D277" s="120"/>
+      <c r="E277" s="120"/>
     </row>
     <row r="278" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
@@ -14380,13 +14380,13 @@
       </c>
     </row>
     <row r="286" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A286" s="126" t="s">
+      <c r="A286" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="B286" s="127"/>
-      <c r="C286" s="127"/>
-      <c r="D286" s="127"/>
-      <c r="E286" s="128"/>
+      <c r="B286" s="122"/>
+      <c r="C286" s="122"/>
+      <c r="D286" s="122"/>
+      <c r="E286" s="123"/>
     </row>
     <row r="287" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A287" s="6" t="s">
@@ -14812,13 +14812,13 @@
       <c r="E317" s="82"/>
     </row>
     <row r="318" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="120" t="s">
+      <c r="A318" s="119" t="s">
         <v>705</v>
       </c>
-      <c r="B318" s="119"/>
-      <c r="C318" s="119"/>
-      <c r="D318" s="119"/>
-      <c r="E318" s="119"/>
+      <c r="B318" s="120"/>
+      <c r="C318" s="120"/>
+      <c r="D318" s="120"/>
+      <c r="E318" s="120"/>
     </row>
     <row r="319" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
@@ -15255,13 +15255,13 @@
       <c r="E348" s="82"/>
     </row>
     <row r="349" spans="1:5" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A349" s="120" t="s">
+      <c r="A349" s="119" t="s">
         <v>707</v>
       </c>
-      <c r="B349" s="119"/>
-      <c r="C349" s="119"/>
-      <c r="D349" s="119"/>
-      <c r="E349" s="119"/>
+      <c r="B349" s="120"/>
+      <c r="C349" s="120"/>
+      <c r="D349" s="120"/>
+      <c r="E349" s="120"/>
     </row>
     <row r="350" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
@@ -15651,13 +15651,13 @@
       <c r="E376" s="82"/>
     </row>
     <row r="377" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A377" s="120" t="s">
+      <c r="A377" s="119" t="s">
         <v>708</v>
       </c>
-      <c r="B377" s="119"/>
-      <c r="C377" s="119"/>
-      <c r="D377" s="119"/>
-      <c r="E377" s="119"/>
+      <c r="B377" s="120"/>
+      <c r="C377" s="120"/>
+      <c r="D377" s="120"/>
+      <c r="E377" s="120"/>
     </row>
     <row r="378" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A378" s="2" t="s">
@@ -16047,13 +16047,13 @@
       <c r="E404" s="82"/>
     </row>
     <row r="405" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A405" s="132" t="s">
+      <c r="A405" s="136" t="s">
         <v>406</v>
       </c>
-      <c r="B405" s="133"/>
-      <c r="C405" s="133"/>
-      <c r="D405" s="133"/>
-      <c r="E405" s="134"/>
+      <c r="B405" s="132"/>
+      <c r="C405" s="132"/>
+      <c r="D405" s="132"/>
+      <c r="E405" s="133"/>
     </row>
     <row r="406" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A406" s="6" t="s">
@@ -16225,24 +16225,22 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A134:E134"/>
-    <mergeCell ref="A139:E139"/>
-    <mergeCell ref="A368:E368"/>
-    <mergeCell ref="A377:E377"/>
-    <mergeCell ref="A386:E386"/>
-    <mergeCell ref="A391:E391"/>
-    <mergeCell ref="A184:E184"/>
-    <mergeCell ref="A251:E251"/>
-    <mergeCell ref="A238:E248"/>
-    <mergeCell ref="A224:E224"/>
-    <mergeCell ref="A210:E210"/>
-    <mergeCell ref="A193:E193"/>
-    <mergeCell ref="A198:E198"/>
-    <mergeCell ref="A203:E203"/>
-    <mergeCell ref="A231:E231"/>
-    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="A164:E164"/>
+    <mergeCell ref="A169:E169"/>
+    <mergeCell ref="A177:E177"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A97:E97"/>
     <mergeCell ref="A405:E405"/>
     <mergeCell ref="A305:E305"/>
     <mergeCell ref="A310:E310"/>
@@ -16259,22 +16257,24 @@
     <mergeCell ref="A318:E318"/>
     <mergeCell ref="A337:E337"/>
     <mergeCell ref="A342:E342"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A155:E155"/>
-    <mergeCell ref="A164:E164"/>
-    <mergeCell ref="A169:E169"/>
-    <mergeCell ref="A177:E177"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A83:E83"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A97:E97"/>
+    <mergeCell ref="A377:E377"/>
+    <mergeCell ref="A386:E386"/>
+    <mergeCell ref="A391:E391"/>
+    <mergeCell ref="A184:E184"/>
+    <mergeCell ref="A251:E251"/>
+    <mergeCell ref="A238:E248"/>
+    <mergeCell ref="A224:E224"/>
+    <mergeCell ref="A210:E210"/>
+    <mergeCell ref="A193:E193"/>
+    <mergeCell ref="A198:E198"/>
+    <mergeCell ref="A203:E203"/>
+    <mergeCell ref="A231:E231"/>
+    <mergeCell ref="A219:E219"/>
+    <mergeCell ref="A106:E106"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A134:E134"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A368:E368"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16294,13 +16294,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="115" t="s">
         <v>683</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
     </row>
     <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -16388,13 +16388,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="132" t="s">
+      <c r="A7" s="136" t="s">
         <v>223</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="128"/>
+      <c r="B7" s="122"/>
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
     </row>
     <row r="8" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -16445,13 +16445,13 @@
       <c r="E11" s="82"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="115" t="s">
         <v>684</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
     </row>
     <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="59" t="s">
@@ -16522,13 +16522,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="117" t="s">
+      <c r="A19" s="115" t="s">
         <v>685</v>
       </c>
-      <c r="B19" s="100"/>
-      <c r="C19" s="100"/>
-      <c r="D19" s="100"/>
-      <c r="E19" s="100"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
     </row>
     <row r="20" spans="1:5" s="82" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="59" t="s">
@@ -16565,13 +16565,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="117" t="s">
+      <c r="A24" s="115" t="s">
         <v>686</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
     </row>
     <row r="25" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="59" t="s">
@@ -16671,22 +16671,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="156" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
     </row>
     <row r="2" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A2" s="65" t="s">
@@ -16704,17 +16704,17 @@
       <c r="E2" s="66" t="s">
         <v>423</v>
       </c>
-      <c r="F2" s="140" t="s">
+      <c r="F2" s="157" t="s">
         <v>424</v>
       </c>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="142"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="151"/>
     </row>
     <row r="3" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A3" s="65"/>
@@ -16726,17 +16726,17 @@
         <v>184</v>
       </c>
       <c r="E3" s="66"/>
-      <c r="F3" s="140" t="s">
+      <c r="F3" s="157" t="s">
         <v>445</v>
       </c>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="142"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="150"/>
+      <c r="N3" s="151"/>
     </row>
     <row r="4" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A4" s="65"/>
@@ -16748,17 +16748,17 @@
         <v>184</v>
       </c>
       <c r="E4" s="66"/>
-      <c r="F4" s="140" t="s">
+      <c r="F4" s="157" t="s">
         <v>441</v>
       </c>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
-      <c r="J4" s="141"/>
-      <c r="K4" s="141"/>
-      <c r="L4" s="141"/>
-      <c r="M4" s="141"/>
-      <c r="N4" s="142"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="150"/>
+      <c r="N4" s="151"/>
     </row>
     <row r="5" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A5" s="65"/>
@@ -16770,17 +16770,17 @@
         <v>184</v>
       </c>
       <c r="E5" s="66"/>
-      <c r="F5" s="140" t="s">
+      <c r="F5" s="157" t="s">
         <v>443</v>
       </c>
-      <c r="G5" s="141"/>
-      <c r="H5" s="141"/>
-      <c r="I5" s="141"/>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
-      <c r="L5" s="141"/>
-      <c r="M5" s="141"/>
-      <c r="N5" s="142"/>
+      <c r="G5" s="150"/>
+      <c r="H5" s="150"/>
+      <c r="I5" s="150"/>
+      <c r="J5" s="150"/>
+      <c r="K5" s="150"/>
+      <c r="L5" s="150"/>
+      <c r="M5" s="150"/>
+      <c r="N5" s="151"/>
     </row>
     <row r="6" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="65"/>
@@ -16792,17 +16792,17 @@
         <v>184</v>
       </c>
       <c r="E6" s="66"/>
-      <c r="F6" s="140" t="s">
+      <c r="F6" s="157" t="s">
         <v>444</v>
       </c>
-      <c r="G6" s="141"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="141"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="141"/>
-      <c r="L6" s="141"/>
-      <c r="M6" s="141"/>
-      <c r="N6" s="142"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="150"/>
+      <c r="I6" s="150"/>
+      <c r="J6" s="150"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="150"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="151"/>
     </row>
     <row r="7" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="65"/>
@@ -16814,17 +16814,17 @@
         <v>184</v>
       </c>
       <c r="E7" s="66"/>
-      <c r="F7" s="140" t="s">
+      <c r="F7" s="157" t="s">
         <v>447</v>
       </c>
-      <c r="G7" s="141"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="141"/>
-      <c r="M7" s="141"/>
-      <c r="N7" s="142"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="150"/>
+      <c r="J7" s="150"/>
+      <c r="K7" s="150"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="150"/>
+      <c r="N7" s="151"/>
     </row>
     <row r="8" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="65"/>
@@ -16836,17 +16836,17 @@
         <v>184</v>
       </c>
       <c r="E8" s="66"/>
-      <c r="F8" s="140" t="s">
+      <c r="F8" s="157" t="s">
         <v>448</v>
       </c>
-      <c r="G8" s="141"/>
-      <c r="H8" s="141"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="141"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="142"/>
+      <c r="G8" s="150"/>
+      <c r="H8" s="150"/>
+      <c r="I8" s="150"/>
+      <c r="J8" s="150"/>
+      <c r="K8" s="150"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="150"/>
+      <c r="N8" s="151"/>
     </row>
     <row r="9" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="65"/>
@@ -16858,17 +16858,17 @@
         <v>184</v>
       </c>
       <c r="E9" s="66"/>
-      <c r="F9" s="140" t="s">
+      <c r="F9" s="157" t="s">
         <v>450</v>
       </c>
-      <c r="G9" s="141"/>
-      <c r="H9" s="141"/>
-      <c r="I9" s="141"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="141"/>
-      <c r="L9" s="141"/>
-      <c r="M9" s="141"/>
-      <c r="N9" s="142"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="150"/>
+      <c r="J9" s="150"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="150"/>
+      <c r="N9" s="151"/>
     </row>
     <row r="10" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="65"/>
@@ -16880,17 +16880,17 @@
         <v>451</v>
       </c>
       <c r="E10" s="66"/>
-      <c r="F10" s="140" t="s">
+      <c r="F10" s="157" t="s">
         <v>452</v>
       </c>
-      <c r="G10" s="141"/>
-      <c r="H10" s="141"/>
-      <c r="I10" s="141"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="141"/>
-      <c r="L10" s="141"/>
-      <c r="M10" s="141"/>
-      <c r="N10" s="142"/>
+      <c r="G10" s="150"/>
+      <c r="H10" s="150"/>
+      <c r="I10" s="150"/>
+      <c r="J10" s="150"/>
+      <c r="K10" s="150"/>
+      <c r="L10" s="150"/>
+      <c r="M10" s="150"/>
+      <c r="N10" s="151"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="65"/>
@@ -16902,17 +16902,17 @@
         <v>184</v>
       </c>
       <c r="E11" s="66"/>
-      <c r="F11" s="140" t="s">
+      <c r="F11" s="157" t="s">
         <v>454</v>
       </c>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="142"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="150"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="150"/>
+      <c r="N11" s="151"/>
     </row>
     <row r="12" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="65"/>
@@ -16924,17 +16924,17 @@
         <v>455</v>
       </c>
       <c r="E12" s="66"/>
-      <c r="F12" s="146" t="s">
+      <c r="F12" s="158" t="s">
         <v>554</v>
       </c>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="148"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="154"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="65"/>
@@ -16946,17 +16946,17 @@
         <v>489</v>
       </c>
       <c r="E13" s="66"/>
-      <c r="F13" s="140" t="s">
+      <c r="F13" s="157" t="s">
         <v>456</v>
       </c>
-      <c r="G13" s="141"/>
-      <c r="H13" s="141"/>
-      <c r="I13" s="141"/>
-      <c r="J13" s="141"/>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-      <c r="M13" s="141"/>
-      <c r="N13" s="142"/>
+      <c r="G13" s="150"/>
+      <c r="H13" s="150"/>
+      <c r="I13" s="150"/>
+      <c r="J13" s="150"/>
+      <c r="K13" s="150"/>
+      <c r="L13" s="150"/>
+      <c r="M13" s="150"/>
+      <c r="N13" s="151"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="65"/>
@@ -16968,17 +16968,17 @@
         <v>457</v>
       </c>
       <c r="E14" s="66"/>
-      <c r="F14" s="140" t="s">
+      <c r="F14" s="157" t="s">
         <v>458</v>
       </c>
-      <c r="G14" s="141"/>
-      <c r="H14" s="141"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="141"/>
-      <c r="L14" s="141"/>
-      <c r="M14" s="141"/>
-      <c r="N14" s="142"/>
+      <c r="G14" s="150"/>
+      <c r="H14" s="150"/>
+      <c r="I14" s="150"/>
+      <c r="J14" s="150"/>
+      <c r="K14" s="150"/>
+      <c r="L14" s="150"/>
+      <c r="M14" s="150"/>
+      <c r="N14" s="151"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="65"/>
@@ -16990,17 +16990,17 @@
         <v>459</v>
       </c>
       <c r="E15" s="66"/>
-      <c r="F15" s="140" t="s">
+      <c r="F15" s="157" t="s">
         <v>460</v>
       </c>
-      <c r="G15" s="141"/>
-      <c r="H15" s="141"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
-      <c r="M15" s="141"/>
-      <c r="N15" s="142"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="150"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="150"/>
+      <c r="M15" s="150"/>
+      <c r="N15" s="151"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="65"/>
@@ -17012,17 +17012,17 @@
         <v>462</v>
       </c>
       <c r="E16" s="66"/>
-      <c r="F16" s="140" t="s">
+      <c r="F16" s="157" t="s">
         <v>464</v>
       </c>
-      <c r="G16" s="141"/>
-      <c r="H16" s="141"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="141"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="142"/>
+      <c r="G16" s="150"/>
+      <c r="H16" s="150"/>
+      <c r="I16" s="150"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="150"/>
+      <c r="N16" s="151"/>
     </row>
     <row r="17" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="65"/>
@@ -17034,17 +17034,17 @@
         <v>461</v>
       </c>
       <c r="E17" s="66"/>
-      <c r="F17" s="140" t="s">
+      <c r="F17" s="157" t="s">
         <v>463</v>
       </c>
-      <c r="G17" s="141"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="142"/>
+      <c r="G17" s="150"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="150"/>
+      <c r="J17" s="150"/>
+      <c r="K17" s="150"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="150"/>
+      <c r="N17" s="151"/>
     </row>
     <row r="18" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="65"/>
@@ -17056,17 +17056,17 @@
         <v>465</v>
       </c>
       <c r="E18" s="66"/>
-      <c r="F18" s="140" t="s">
+      <c r="F18" s="157" t="s">
         <v>466</v>
       </c>
-      <c r="G18" s="141"/>
-      <c r="H18" s="141"/>
-      <c r="I18" s="141"/>
-      <c r="J18" s="141"/>
-      <c r="K18" s="141"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="141"/>
-      <c r="N18" s="142"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="150"/>
+      <c r="L18" s="150"/>
+      <c r="M18" s="150"/>
+      <c r="N18" s="151"/>
     </row>
     <row r="19" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="65"/>
@@ -17078,17 +17078,17 @@
         <v>467</v>
       </c>
       <c r="E19" s="66"/>
-      <c r="F19" s="140" t="s">
+      <c r="F19" s="157" t="s">
         <v>468</v>
       </c>
-      <c r="G19" s="141"/>
-      <c r="H19" s="141"/>
-      <c r="I19" s="141"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
-      <c r="L19" s="141"/>
-      <c r="M19" s="141"/>
-      <c r="N19" s="142"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="150"/>
+      <c r="J19" s="150"/>
+      <c r="K19" s="150"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="150"/>
+      <c r="N19" s="151"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="65"/>
@@ -17096,17 +17096,17 @@
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
       <c r="E20" s="66"/>
-      <c r="F20" s="140">
+      <c r="F20" s="157">
         <v>1</v>
       </c>
-      <c r="G20" s="141"/>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="142"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="150"/>
+      <c r="I20" s="150"/>
+      <c r="J20" s="150"/>
+      <c r="K20" s="150"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="150"/>
+      <c r="N20" s="151"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="57"/>
@@ -17114,51 +17114,51 @@
       <c r="C21" s="57"/>
       <c r="D21" s="57"/>
       <c r="E21" s="58"/>
-      <c r="F21" s="143"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="144"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="145"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="163"/>
+      <c r="H21" s="163"/>
+      <c r="I21" s="163"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="163"/>
+      <c r="L21" s="163"/>
+      <c r="M21" s="163"/>
+      <c r="N21" s="164"/>
     </row>
     <row r="22" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="137" t="s">
+      <c r="A22" s="159" t="s">
         <v>487</v>
       </c>
-      <c r="B22" s="138"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138"/>
-      <c r="M22" s="138"/>
-      <c r="N22" s="139"/>
+      <c r="B22" s="160"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="160"/>
+      <c r="I22" s="160"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="160"/>
+      <c r="L22" s="160"/>
+      <c r="M22" s="160"/>
+      <c r="N22" s="161"/>
     </row>
     <row r="23" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="150" t="s">
+      <c r="A23" s="155" t="s">
         <v>471</v>
       </c>
-      <c r="B23" s="149"/>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="149"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="149"/>
-      <c r="I23" s="149"/>
-      <c r="J23" s="149"/>
-      <c r="K23" s="149"/>
-      <c r="L23" s="149"/>
-      <c r="M23" s="149"/>
-      <c r="N23" s="149"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="156"/>
+      <c r="H23" s="156"/>
+      <c r="I23" s="156"/>
+      <c r="J23" s="156"/>
+      <c r="K23" s="156"/>
+      <c r="L23" s="156"/>
+      <c r="M23" s="156"/>
+      <c r="N23" s="156"/>
     </row>
     <row r="24" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="65" t="s">
@@ -17176,17 +17176,17 @@
       <c r="E24" s="66" t="s">
         <v>423</v>
       </c>
-      <c r="F24" s="151" t="s">
+      <c r="F24" s="149" t="s">
         <v>472</v>
       </c>
-      <c r="G24" s="141"/>
-      <c r="H24" s="141"/>
-      <c r="I24" s="141"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="141"/>
-      <c r="M24" s="141"/>
-      <c r="N24" s="142"/>
+      <c r="G24" s="150"/>
+      <c r="H24" s="150"/>
+      <c r="I24" s="150"/>
+      <c r="J24" s="150"/>
+      <c r="K24" s="150"/>
+      <c r="L24" s="150"/>
+      <c r="M24" s="150"/>
+      <c r="N24" s="151"/>
     </row>
     <row r="25" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A25" s="65"/>
@@ -17198,17 +17198,17 @@
         <v>473</v>
       </c>
       <c r="E25" s="66"/>
-      <c r="F25" s="151" t="s">
+      <c r="F25" s="149" t="s">
         <v>474</v>
       </c>
-      <c r="G25" s="141"/>
-      <c r="H25" s="141"/>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="141"/>
-      <c r="L25" s="141"/>
-      <c r="M25" s="141"/>
-      <c r="N25" s="142"/>
+      <c r="G25" s="150"/>
+      <c r="H25" s="150"/>
+      <c r="I25" s="150"/>
+      <c r="J25" s="150"/>
+      <c r="K25" s="150"/>
+      <c r="L25" s="150"/>
+      <c r="M25" s="150"/>
+      <c r="N25" s="151"/>
     </row>
     <row r="26" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A26" s="65"/>
@@ -17220,17 +17220,17 @@
         <v>475</v>
       </c>
       <c r="E26" s="66"/>
-      <c r="F26" s="151" t="s">
+      <c r="F26" s="149" t="s">
         <v>476</v>
       </c>
-      <c r="G26" s="141"/>
-      <c r="H26" s="141"/>
-      <c r="I26" s="141"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="141"/>
-      <c r="L26" s="141"/>
-      <c r="M26" s="141"/>
-      <c r="N26" s="142"/>
+      <c r="G26" s="150"/>
+      <c r="H26" s="150"/>
+      <c r="I26" s="150"/>
+      <c r="J26" s="150"/>
+      <c r="K26" s="150"/>
+      <c r="L26" s="150"/>
+      <c r="M26" s="150"/>
+      <c r="N26" s="151"/>
     </row>
     <row r="27" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A27" s="65"/>
@@ -17242,17 +17242,17 @@
         <v>184</v>
       </c>
       <c r="E27" s="66"/>
-      <c r="F27" s="151" t="s">
+      <c r="F27" s="149" t="s">
         <v>478</v>
       </c>
-      <c r="G27" s="141"/>
-      <c r="H27" s="141"/>
-      <c r="I27" s="141"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="141"/>
-      <c r="N27" s="142"/>
+      <c r="G27" s="150"/>
+      <c r="H27" s="150"/>
+      <c r="I27" s="150"/>
+      <c r="J27" s="150"/>
+      <c r="K27" s="150"/>
+      <c r="L27" s="150"/>
+      <c r="M27" s="150"/>
+      <c r="N27" s="151"/>
     </row>
     <row r="28" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A28" s="65"/>
@@ -17264,17 +17264,17 @@
         <v>473</v>
       </c>
       <c r="E28" s="66"/>
-      <c r="F28" s="151" t="s">
+      <c r="F28" s="149" t="s">
         <v>477</v>
       </c>
-      <c r="G28" s="141"/>
-      <c r="H28" s="141"/>
-      <c r="I28" s="141"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="141"/>
-      <c r="L28" s="141"/>
-      <c r="M28" s="141"/>
-      <c r="N28" s="142"/>
+      <c r="G28" s="150"/>
+      <c r="H28" s="150"/>
+      <c r="I28" s="150"/>
+      <c r="J28" s="150"/>
+      <c r="K28" s="150"/>
+      <c r="L28" s="150"/>
+      <c r="M28" s="150"/>
+      <c r="N28" s="151"/>
     </row>
     <row r="29" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A29" s="65"/>
@@ -17286,17 +17286,17 @@
         <v>473</v>
       </c>
       <c r="E29" s="66"/>
-      <c r="F29" s="151" t="s">
+      <c r="F29" s="149" t="s">
         <v>479</v>
       </c>
-      <c r="G29" s="141"/>
-      <c r="H29" s="141"/>
-      <c r="I29" s="141"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="141"/>
-      <c r="N29" s="142"/>
+      <c r="G29" s="150"/>
+      <c r="H29" s="150"/>
+      <c r="I29" s="150"/>
+      <c r="J29" s="150"/>
+      <c r="K29" s="150"/>
+      <c r="L29" s="150"/>
+      <c r="M29" s="150"/>
+      <c r="N29" s="151"/>
     </row>
     <row r="30" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A30" s="65"/>
@@ -17308,17 +17308,17 @@
         <v>184</v>
       </c>
       <c r="E30" s="66"/>
-      <c r="F30" s="151" t="s">
+      <c r="F30" s="149" t="s">
         <v>481</v>
       </c>
-      <c r="G30" s="141"/>
-      <c r="H30" s="141"/>
-      <c r="I30" s="141"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="141"/>
-      <c r="L30" s="141"/>
-      <c r="M30" s="141"/>
-      <c r="N30" s="142"/>
+      <c r="G30" s="150"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="150"/>
+      <c r="K30" s="150"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="150"/>
+      <c r="N30" s="151"/>
     </row>
     <row r="31" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="65"/>
@@ -17330,17 +17330,17 @@
         <v>184</v>
       </c>
       <c r="E31" s="66"/>
-      <c r="F31" s="151" t="s">
+      <c r="F31" s="149" t="s">
         <v>483</v>
       </c>
-      <c r="G31" s="141"/>
-      <c r="H31" s="141"/>
-      <c r="I31" s="141"/>
-      <c r="J31" s="141"/>
-      <c r="K31" s="141"/>
-      <c r="L31" s="141"/>
-      <c r="M31" s="141"/>
-      <c r="N31" s="142"/>
+      <c r="G31" s="150"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="150"/>
+      <c r="J31" s="150"/>
+      <c r="K31" s="150"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="151"/>
     </row>
     <row r="32" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A32" s="65"/>
@@ -17352,17 +17352,17 @@
         <v>184</v>
       </c>
       <c r="E32" s="66"/>
-      <c r="F32" s="151" t="s">
+      <c r="F32" s="149" t="s">
         <v>484</v>
       </c>
-      <c r="G32" s="141"/>
-      <c r="H32" s="141"/>
-      <c r="I32" s="141"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="141"/>
-      <c r="L32" s="141"/>
-      <c r="M32" s="141"/>
-      <c r="N32" s="142"/>
+      <c r="G32" s="150"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="150"/>
+      <c r="J32" s="150"/>
+      <c r="K32" s="150"/>
+      <c r="L32" s="150"/>
+      <c r="M32" s="150"/>
+      <c r="N32" s="151"/>
     </row>
     <row r="33" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A33" s="65"/>
@@ -17374,17 +17374,17 @@
         <v>184</v>
       </c>
       <c r="E33" s="66"/>
-      <c r="F33" s="151" t="s">
+      <c r="F33" s="149" t="s">
         <v>485</v>
       </c>
-      <c r="G33" s="141"/>
-      <c r="H33" s="141"/>
-      <c r="I33" s="141"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="141"/>
-      <c r="L33" s="141"/>
-      <c r="M33" s="141"/>
-      <c r="N33" s="142"/>
+      <c r="G33" s="150"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="150"/>
+      <c r="J33" s="150"/>
+      <c r="K33" s="150"/>
+      <c r="L33" s="150"/>
+      <c r="M33" s="150"/>
+      <c r="N33" s="151"/>
     </row>
     <row r="34" spans="1:14" s="53" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A34" s="65"/>
@@ -17408,358 +17408,344 @@
       <c r="C35" s="65"/>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
-      <c r="F35" s="164"/>
-      <c r="G35" s="147"/>
-      <c r="H35" s="147"/>
-      <c r="I35" s="147"/>
-      <c r="J35" s="147"/>
-      <c r="K35" s="147"/>
-      <c r="L35" s="147"/>
-      <c r="M35" s="147"/>
-      <c r="N35" s="148"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="153"/>
+      <c r="H35" s="153"/>
+      <c r="I35" s="153"/>
+      <c r="J35" s="153"/>
+      <c r="K35" s="153"/>
+      <c r="L35" s="153"/>
+      <c r="M35" s="153"/>
+      <c r="N35" s="154"/>
     </row>
     <row r="36" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="152" t="s">
+      <c r="A36" s="137" t="s">
         <v>486</v>
       </c>
-      <c r="B36" s="153"/>
-      <c r="C36" s="153"/>
-      <c r="D36" s="153"/>
-      <c r="E36" s="153"/>
-      <c r="F36" s="153"/>
-      <c r="G36" s="153"/>
-      <c r="H36" s="153"/>
-      <c r="I36" s="153"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="153"/>
-      <c r="L36" s="153"/>
-      <c r="M36" s="153"/>
-      <c r="N36" s="154"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="138"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="138"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
+      <c r="M36" s="138"/>
+      <c r="N36" s="139"/>
     </row>
     <row r="116" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="117" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D117" s="155" t="s">
+      <c r="D117" s="140" t="s">
         <v>488</v>
       </c>
-      <c r="E117" s="156"/>
-      <c r="F117" s="156"/>
-      <c r="G117" s="156"/>
-      <c r="H117" s="156"/>
-      <c r="I117" s="156"/>
-      <c r="J117" s="156"/>
-      <c r="K117" s="156"/>
-      <c r="L117" s="156"/>
-      <c r="M117" s="156"/>
-      <c r="N117" s="156"/>
-      <c r="O117" s="156"/>
-      <c r="P117" s="157"/>
+      <c r="E117" s="141"/>
+      <c r="F117" s="141"/>
+      <c r="G117" s="141"/>
+      <c r="H117" s="141"/>
+      <c r="I117" s="141"/>
+      <c r="J117" s="141"/>
+      <c r="K117" s="141"/>
+      <c r="L117" s="141"/>
+      <c r="M117" s="141"/>
+      <c r="N117" s="141"/>
+      <c r="O117" s="141"/>
+      <c r="P117" s="142"/>
     </row>
     <row r="118" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D118" s="158"/>
-      <c r="E118" s="159"/>
-      <c r="F118" s="159"/>
-      <c r="G118" s="159"/>
-      <c r="H118" s="159"/>
-      <c r="I118" s="159"/>
-      <c r="J118" s="159"/>
-      <c r="K118" s="159"/>
-      <c r="L118" s="159"/>
-      <c r="M118" s="159"/>
-      <c r="N118" s="159"/>
-      <c r="O118" s="159"/>
-      <c r="P118" s="160"/>
+      <c r="D118" s="143"/>
+      <c r="E118" s="144"/>
+      <c r="F118" s="144"/>
+      <c r="G118" s="144"/>
+      <c r="H118" s="144"/>
+      <c r="I118" s="144"/>
+      <c r="J118" s="144"/>
+      <c r="K118" s="144"/>
+      <c r="L118" s="144"/>
+      <c r="M118" s="144"/>
+      <c r="N118" s="144"/>
+      <c r="O118" s="144"/>
+      <c r="P118" s="145"/>
     </row>
     <row r="119" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D119" s="158"/>
-      <c r="E119" s="159"/>
-      <c r="F119" s="159"/>
-      <c r="G119" s="159"/>
-      <c r="H119" s="159"/>
-      <c r="I119" s="159"/>
-      <c r="J119" s="159"/>
-      <c r="K119" s="159"/>
-      <c r="L119" s="159"/>
-      <c r="M119" s="159"/>
-      <c r="N119" s="159"/>
-      <c r="O119" s="159"/>
-      <c r="P119" s="160"/>
+      <c r="D119" s="143"/>
+      <c r="E119" s="144"/>
+      <c r="F119" s="144"/>
+      <c r="G119" s="144"/>
+      <c r="H119" s="144"/>
+      <c r="I119" s="144"/>
+      <c r="J119" s="144"/>
+      <c r="K119" s="144"/>
+      <c r="L119" s="144"/>
+      <c r="M119" s="144"/>
+      <c r="N119" s="144"/>
+      <c r="O119" s="144"/>
+      <c r="P119" s="145"/>
     </row>
     <row r="120" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D120" s="158"/>
-      <c r="E120" s="159"/>
-      <c r="F120" s="159"/>
-      <c r="G120" s="159"/>
-      <c r="H120" s="159"/>
-      <c r="I120" s="159"/>
-      <c r="J120" s="159"/>
-      <c r="K120" s="159"/>
-      <c r="L120" s="159"/>
-      <c r="M120" s="159"/>
-      <c r="N120" s="159"/>
-      <c r="O120" s="159"/>
-      <c r="P120" s="160"/>
+      <c r="D120" s="143"/>
+      <c r="E120" s="144"/>
+      <c r="F120" s="144"/>
+      <c r="G120" s="144"/>
+      <c r="H120" s="144"/>
+      <c r="I120" s="144"/>
+      <c r="J120" s="144"/>
+      <c r="K120" s="144"/>
+      <c r="L120" s="144"/>
+      <c r="M120" s="144"/>
+      <c r="N120" s="144"/>
+      <c r="O120" s="144"/>
+      <c r="P120" s="145"/>
     </row>
     <row r="121" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D121" s="158"/>
-      <c r="E121" s="159"/>
-      <c r="F121" s="159"/>
-      <c r="G121" s="159"/>
-      <c r="H121" s="159"/>
-      <c r="I121" s="159"/>
-      <c r="J121" s="159"/>
-      <c r="K121" s="159"/>
-      <c r="L121" s="159"/>
-      <c r="M121" s="159"/>
-      <c r="N121" s="159"/>
-      <c r="O121" s="159"/>
-      <c r="P121" s="160"/>
+      <c r="D121" s="143"/>
+      <c r="E121" s="144"/>
+      <c r="F121" s="144"/>
+      <c r="G121" s="144"/>
+      <c r="H121" s="144"/>
+      <c r="I121" s="144"/>
+      <c r="J121" s="144"/>
+      <c r="K121" s="144"/>
+      <c r="L121" s="144"/>
+      <c r="M121" s="144"/>
+      <c r="N121" s="144"/>
+      <c r="O121" s="144"/>
+      <c r="P121" s="145"/>
     </row>
     <row r="122" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D122" s="158"/>
-      <c r="E122" s="159"/>
-      <c r="F122" s="159"/>
-      <c r="G122" s="159"/>
-      <c r="H122" s="159"/>
-      <c r="I122" s="159"/>
-      <c r="J122" s="159"/>
-      <c r="K122" s="159"/>
-      <c r="L122" s="159"/>
-      <c r="M122" s="159"/>
-      <c r="N122" s="159"/>
-      <c r="O122" s="159"/>
-      <c r="P122" s="160"/>
+      <c r="D122" s="143"/>
+      <c r="E122" s="144"/>
+      <c r="F122" s="144"/>
+      <c r="G122" s="144"/>
+      <c r="H122" s="144"/>
+      <c r="I122" s="144"/>
+      <c r="J122" s="144"/>
+      <c r="K122" s="144"/>
+      <c r="L122" s="144"/>
+      <c r="M122" s="144"/>
+      <c r="N122" s="144"/>
+      <c r="O122" s="144"/>
+      <c r="P122" s="145"/>
     </row>
     <row r="123" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D123" s="158"/>
-      <c r="E123" s="159"/>
-      <c r="F123" s="159"/>
-      <c r="G123" s="159"/>
-      <c r="H123" s="159"/>
-      <c r="I123" s="159"/>
-      <c r="J123" s="159"/>
-      <c r="K123" s="159"/>
-      <c r="L123" s="159"/>
-      <c r="M123" s="159"/>
-      <c r="N123" s="159"/>
-      <c r="O123" s="159"/>
-      <c r="P123" s="160"/>
+      <c r="D123" s="143"/>
+      <c r="E123" s="144"/>
+      <c r="F123" s="144"/>
+      <c r="G123" s="144"/>
+      <c r="H123" s="144"/>
+      <c r="I123" s="144"/>
+      <c r="J123" s="144"/>
+      <c r="K123" s="144"/>
+      <c r="L123" s="144"/>
+      <c r="M123" s="144"/>
+      <c r="N123" s="144"/>
+      <c r="O123" s="144"/>
+      <c r="P123" s="145"/>
     </row>
     <row r="124" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D124" s="158"/>
-      <c r="E124" s="159"/>
-      <c r="F124" s="159"/>
-      <c r="G124" s="159"/>
-      <c r="H124" s="159"/>
-      <c r="I124" s="159"/>
-      <c r="J124" s="159"/>
-      <c r="K124" s="159"/>
-      <c r="L124" s="159"/>
-      <c r="M124" s="159"/>
-      <c r="N124" s="159"/>
-      <c r="O124" s="159"/>
-      <c r="P124" s="160"/>
+      <c r="D124" s="143"/>
+      <c r="E124" s="144"/>
+      <c r="F124" s="144"/>
+      <c r="G124" s="144"/>
+      <c r="H124" s="144"/>
+      <c r="I124" s="144"/>
+      <c r="J124" s="144"/>
+      <c r="K124" s="144"/>
+      <c r="L124" s="144"/>
+      <c r="M124" s="144"/>
+      <c r="N124" s="144"/>
+      <c r="O124" s="144"/>
+      <c r="P124" s="145"/>
     </row>
     <row r="125" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D125" s="158"/>
-      <c r="E125" s="159"/>
-      <c r="F125" s="159"/>
-      <c r="G125" s="159"/>
-      <c r="H125" s="159"/>
-      <c r="I125" s="159"/>
-      <c r="J125" s="159"/>
-      <c r="K125" s="159"/>
-      <c r="L125" s="159"/>
-      <c r="M125" s="159"/>
-      <c r="N125" s="159"/>
-      <c r="O125" s="159"/>
-      <c r="P125" s="160"/>
+      <c r="D125" s="143"/>
+      <c r="E125" s="144"/>
+      <c r="F125" s="144"/>
+      <c r="G125" s="144"/>
+      <c r="H125" s="144"/>
+      <c r="I125" s="144"/>
+      <c r="J125" s="144"/>
+      <c r="K125" s="144"/>
+      <c r="L125" s="144"/>
+      <c r="M125" s="144"/>
+      <c r="N125" s="144"/>
+      <c r="O125" s="144"/>
+      <c r="P125" s="145"/>
     </row>
     <row r="126" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D126" s="158"/>
-      <c r="E126" s="159"/>
-      <c r="F126" s="159"/>
-      <c r="G126" s="159"/>
-      <c r="H126" s="159"/>
-      <c r="I126" s="159"/>
-      <c r="J126" s="159"/>
-      <c r="K126" s="159"/>
-      <c r="L126" s="159"/>
-      <c r="M126" s="159"/>
-      <c r="N126" s="159"/>
-      <c r="O126" s="159"/>
-      <c r="P126" s="160"/>
+      <c r="D126" s="143"/>
+      <c r="E126" s="144"/>
+      <c r="F126" s="144"/>
+      <c r="G126" s="144"/>
+      <c r="H126" s="144"/>
+      <c r="I126" s="144"/>
+      <c r="J126" s="144"/>
+      <c r="K126" s="144"/>
+      <c r="L126" s="144"/>
+      <c r="M126" s="144"/>
+      <c r="N126" s="144"/>
+      <c r="O126" s="144"/>
+      <c r="P126" s="145"/>
     </row>
     <row r="127" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D127" s="158"/>
-      <c r="E127" s="159"/>
-      <c r="F127" s="159"/>
-      <c r="G127" s="159"/>
-      <c r="H127" s="159"/>
-      <c r="I127" s="159"/>
-      <c r="J127" s="159"/>
-      <c r="K127" s="159"/>
-      <c r="L127" s="159"/>
-      <c r="M127" s="159"/>
-      <c r="N127" s="159"/>
-      <c r="O127" s="159"/>
-      <c r="P127" s="160"/>
+      <c r="D127" s="143"/>
+      <c r="E127" s="144"/>
+      <c r="F127" s="144"/>
+      <c r="G127" s="144"/>
+      <c r="H127" s="144"/>
+      <c r="I127" s="144"/>
+      <c r="J127" s="144"/>
+      <c r="K127" s="144"/>
+      <c r="L127" s="144"/>
+      <c r="M127" s="144"/>
+      <c r="N127" s="144"/>
+      <c r="O127" s="144"/>
+      <c r="P127" s="145"/>
     </row>
     <row r="128" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D128" s="158"/>
-      <c r="E128" s="159"/>
-      <c r="F128" s="159"/>
-      <c r="G128" s="159"/>
-      <c r="H128" s="159"/>
-      <c r="I128" s="159"/>
-      <c r="J128" s="159"/>
-      <c r="K128" s="159"/>
-      <c r="L128" s="159"/>
-      <c r="M128" s="159"/>
-      <c r="N128" s="159"/>
-      <c r="O128" s="159"/>
-      <c r="P128" s="160"/>
+      <c r="D128" s="143"/>
+      <c r="E128" s="144"/>
+      <c r="F128" s="144"/>
+      <c r="G128" s="144"/>
+      <c r="H128" s="144"/>
+      <c r="I128" s="144"/>
+      <c r="J128" s="144"/>
+      <c r="K128" s="144"/>
+      <c r="L128" s="144"/>
+      <c r="M128" s="144"/>
+      <c r="N128" s="144"/>
+      <c r="O128" s="144"/>
+      <c r="P128" s="145"/>
     </row>
     <row r="129" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D129" s="158"/>
-      <c r="E129" s="159"/>
-      <c r="F129" s="159"/>
-      <c r="G129" s="159"/>
-      <c r="H129" s="159"/>
-      <c r="I129" s="159"/>
-      <c r="J129" s="159"/>
-      <c r="K129" s="159"/>
-      <c r="L129" s="159"/>
-      <c r="M129" s="159"/>
-      <c r="N129" s="159"/>
-      <c r="O129" s="159"/>
-      <c r="P129" s="160"/>
+      <c r="D129" s="143"/>
+      <c r="E129" s="144"/>
+      <c r="F129" s="144"/>
+      <c r="G129" s="144"/>
+      <c r="H129" s="144"/>
+      <c r="I129" s="144"/>
+      <c r="J129" s="144"/>
+      <c r="K129" s="144"/>
+      <c r="L129" s="144"/>
+      <c r="M129" s="144"/>
+      <c r="N129" s="144"/>
+      <c r="O129" s="144"/>
+      <c r="P129" s="145"/>
     </row>
     <row r="130" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D130" s="158"/>
-      <c r="E130" s="159"/>
-      <c r="F130" s="159"/>
-      <c r="G130" s="159"/>
-      <c r="H130" s="159"/>
-      <c r="I130" s="159"/>
-      <c r="J130" s="159"/>
-      <c r="K130" s="159"/>
-      <c r="L130" s="159"/>
-      <c r="M130" s="159"/>
-      <c r="N130" s="159"/>
-      <c r="O130" s="159"/>
-      <c r="P130" s="160"/>
+      <c r="D130" s="143"/>
+      <c r="E130" s="144"/>
+      <c r="F130" s="144"/>
+      <c r="G130" s="144"/>
+      <c r="H130" s="144"/>
+      <c r="I130" s="144"/>
+      <c r="J130" s="144"/>
+      <c r="K130" s="144"/>
+      <c r="L130" s="144"/>
+      <c r="M130" s="144"/>
+      <c r="N130" s="144"/>
+      <c r="O130" s="144"/>
+      <c r="P130" s="145"/>
     </row>
     <row r="131" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D131" s="158"/>
-      <c r="E131" s="159"/>
-      <c r="F131" s="159"/>
-      <c r="G131" s="159"/>
-      <c r="H131" s="159"/>
-      <c r="I131" s="159"/>
-      <c r="J131" s="159"/>
-      <c r="K131" s="159"/>
-      <c r="L131" s="159"/>
-      <c r="M131" s="159"/>
-      <c r="N131" s="159"/>
-      <c r="O131" s="159"/>
-      <c r="P131" s="160"/>
+      <c r="D131" s="143"/>
+      <c r="E131" s="144"/>
+      <c r="F131" s="144"/>
+      <c r="G131" s="144"/>
+      <c r="H131" s="144"/>
+      <c r="I131" s="144"/>
+      <c r="J131" s="144"/>
+      <c r="K131" s="144"/>
+      <c r="L131" s="144"/>
+      <c r="M131" s="144"/>
+      <c r="N131" s="144"/>
+      <c r="O131" s="144"/>
+      <c r="P131" s="145"/>
     </row>
     <row r="132" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D132" s="158"/>
-      <c r="E132" s="159"/>
-      <c r="F132" s="159"/>
-      <c r="G132" s="159"/>
-      <c r="H132" s="159"/>
-      <c r="I132" s="159"/>
-      <c r="J132" s="159"/>
-      <c r="K132" s="159"/>
-      <c r="L132" s="159"/>
-      <c r="M132" s="159"/>
-      <c r="N132" s="159"/>
-      <c r="O132" s="159"/>
-      <c r="P132" s="160"/>
+      <c r="D132" s="143"/>
+      <c r="E132" s="144"/>
+      <c r="F132" s="144"/>
+      <c r="G132" s="144"/>
+      <c r="H132" s="144"/>
+      <c r="I132" s="144"/>
+      <c r="J132" s="144"/>
+      <c r="K132" s="144"/>
+      <c r="L132" s="144"/>
+      <c r="M132" s="144"/>
+      <c r="N132" s="144"/>
+      <c r="O132" s="144"/>
+      <c r="P132" s="145"/>
     </row>
     <row r="133" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D133" s="158"/>
-      <c r="E133" s="159"/>
-      <c r="F133" s="159"/>
-      <c r="G133" s="159"/>
-      <c r="H133" s="159"/>
-      <c r="I133" s="159"/>
-      <c r="J133" s="159"/>
-      <c r="K133" s="159"/>
-      <c r="L133" s="159"/>
-      <c r="M133" s="159"/>
-      <c r="N133" s="159"/>
-      <c r="O133" s="159"/>
-      <c r="P133" s="160"/>
+      <c r="D133" s="143"/>
+      <c r="E133" s="144"/>
+      <c r="F133" s="144"/>
+      <c r="G133" s="144"/>
+      <c r="H133" s="144"/>
+      <c r="I133" s="144"/>
+      <c r="J133" s="144"/>
+      <c r="K133" s="144"/>
+      <c r="L133" s="144"/>
+      <c r="M133" s="144"/>
+      <c r="N133" s="144"/>
+      <c r="O133" s="144"/>
+      <c r="P133" s="145"/>
     </row>
     <row r="134" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D134" s="158"/>
-      <c r="E134" s="159"/>
-      <c r="F134" s="159"/>
-      <c r="G134" s="159"/>
-      <c r="H134" s="159"/>
-      <c r="I134" s="159"/>
-      <c r="J134" s="159"/>
-      <c r="K134" s="159"/>
-      <c r="L134" s="159"/>
-      <c r="M134" s="159"/>
-      <c r="N134" s="159"/>
-      <c r="O134" s="159"/>
-      <c r="P134" s="160"/>
+      <c r="D134" s="143"/>
+      <c r="E134" s="144"/>
+      <c r="F134" s="144"/>
+      <c r="G134" s="144"/>
+      <c r="H134" s="144"/>
+      <c r="I134" s="144"/>
+      <c r="J134" s="144"/>
+      <c r="K134" s="144"/>
+      <c r="L134" s="144"/>
+      <c r="M134" s="144"/>
+      <c r="N134" s="144"/>
+      <c r="O134" s="144"/>
+      <c r="P134" s="145"/>
     </row>
     <row r="135" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D135" s="158"/>
-      <c r="E135" s="159"/>
-      <c r="F135" s="159"/>
-      <c r="G135" s="159"/>
-      <c r="H135" s="159"/>
-      <c r="I135" s="159"/>
-      <c r="J135" s="159"/>
-      <c r="K135" s="159"/>
-      <c r="L135" s="159"/>
-      <c r="M135" s="159"/>
-      <c r="N135" s="159"/>
-      <c r="O135" s="159"/>
-      <c r="P135" s="160"/>
+      <c r="D135" s="143"/>
+      <c r="E135" s="144"/>
+      <c r="F135" s="144"/>
+      <c r="G135" s="144"/>
+      <c r="H135" s="144"/>
+      <c r="I135" s="144"/>
+      <c r="J135" s="144"/>
+      <c r="K135" s="144"/>
+      <c r="L135" s="144"/>
+      <c r="M135" s="144"/>
+      <c r="N135" s="144"/>
+      <c r="O135" s="144"/>
+      <c r="P135" s="145"/>
     </row>
     <row r="136" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D136" s="161"/>
-      <c r="E136" s="162"/>
-      <c r="F136" s="162"/>
-      <c r="G136" s="162"/>
-      <c r="H136" s="162"/>
-      <c r="I136" s="162"/>
-      <c r="J136" s="162"/>
-      <c r="K136" s="162"/>
-      <c r="L136" s="162"/>
-      <c r="M136" s="162"/>
-      <c r="N136" s="162"/>
-      <c r="O136" s="162"/>
-      <c r="P136" s="163"/>
+      <c r="D136" s="146"/>
+      <c r="E136" s="147"/>
+      <c r="F136" s="147"/>
+      <c r="G136" s="147"/>
+      <c r="H136" s="147"/>
+      <c r="I136" s="147"/>
+      <c r="J136" s="147"/>
+      <c r="K136" s="147"/>
+      <c r="L136" s="147"/>
+      <c r="M136" s="147"/>
+      <c r="N136" s="147"/>
+      <c r="O136" s="147"/>
+      <c r="P136" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="D117:P136"/>
-    <mergeCell ref="F33:N33"/>
-    <mergeCell ref="F35:N35"/>
-    <mergeCell ref="F28:N28"/>
-    <mergeCell ref="F29:N29"/>
-    <mergeCell ref="F30:N30"/>
-    <mergeCell ref="F31:N31"/>
-    <mergeCell ref="F32:N32"/>
-    <mergeCell ref="A23:N23"/>
-    <mergeCell ref="F24:N24"/>
-    <mergeCell ref="F25:N25"/>
-    <mergeCell ref="F26:N26"/>
-    <mergeCell ref="F27:N27"/>
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="F3:N3"/>
-    <mergeCell ref="F4:N4"/>
-    <mergeCell ref="F5:N5"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="F18:N18"/>
+    <mergeCell ref="F19:N19"/>
+    <mergeCell ref="F20:N20"/>
+    <mergeCell ref="F21:N21"/>
     <mergeCell ref="F17:N17"/>
     <mergeCell ref="F6:N6"/>
     <mergeCell ref="F7:N7"/>
@@ -17772,11 +17758,25 @@
     <mergeCell ref="F14:N14"/>
     <mergeCell ref="F15:N15"/>
     <mergeCell ref="F16:N16"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="F18:N18"/>
-    <mergeCell ref="F19:N19"/>
-    <mergeCell ref="F20:N20"/>
-    <mergeCell ref="F21:N21"/>
+    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="F3:N3"/>
+    <mergeCell ref="F4:N4"/>
+    <mergeCell ref="F5:N5"/>
+    <mergeCell ref="A23:N23"/>
+    <mergeCell ref="F24:N24"/>
+    <mergeCell ref="F25:N25"/>
+    <mergeCell ref="F26:N26"/>
+    <mergeCell ref="F27:N27"/>
+    <mergeCell ref="A36:N36"/>
+    <mergeCell ref="D117:P136"/>
+    <mergeCell ref="F33:N33"/>
+    <mergeCell ref="F35:N35"/>
+    <mergeCell ref="F28:N28"/>
+    <mergeCell ref="F29:N29"/>
+    <mergeCell ref="F30:N30"/>
+    <mergeCell ref="F31:N31"/>
+    <mergeCell ref="F32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
